--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074193DB-6841-4875-A4D2-DF20C0BA1FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4B0089-EDE4-4B20-A9EC-28A28DA7C8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="742">
   <si>
     <t>date</t>
   </si>
@@ -252,9 +252,6 @@
     <t>この領域まで侵されて そう プラットフォームは上下する\n新しく記された my バースデイ 今夜 感じて 燃え 悶える\nna, 生々しい艷やかな mad day 秘密めいた ruler loo-la, cool, cool,\n“ようこそ おいでなさい” 告げる 始まりのとき\nねぇ しなやかなつま先が ‘ゆらっ’描き出すわ輪舞曲(ロンド)\n純白のドレスを さあ いま 染めて闇の色\n殺める影よ 舞い上がれ\n見える 見える 見えないものが ほら\n生まれ変わる ああ 本当の私に\nエンジェル・インターセプター concept 混乱のフェーズ 堕ちる術中\nその小さな胸を引き裂いて\nbloody lover, lover, la-la-la, bloody 散らばるよ 擦り切れたフィルム\n場面 場面 蘇る 瞼の裏側で\nねぇ 張り付く夜には また 究極の快楽が\njack-jackie, 邪鬼 zap, zap, でもまだ 足りないよ足りない\n求めて求めて 苛まれて\n馳せる 馳せる 消えてゆく惑星(ほし)が ほら\n宇宙(そら)のリスク 真実を歪めたなら\ncallin' 呼び続けてもまだ darlin' 戻らない\n誰もが 選ばれたパズルのピースに\nこのまま このままでいい 世界をあげるわ\n見える 見える 見えないものが ほら\n生まれ変わる ああ 本当の私に\noh, my..\nblack-black, black, my black birthday</t>
   </si>
   <si>
-    <t>Alea jacta est,Ave Música</t>
-  </si>
-  <si>
     <t>comment_text</t>
   </si>
   <si>
@@ -268,9 +265,6 @@
   </si>
   <si>
     <t>https://natalie.mu/music/pp/avemujica03/page/3</t>
-  </si>
-  <si>
-    <t>Diggy-MO'：我在副歌的乐句中加入了“波浪”这一意象，它也是司掌水的精灵“温蒂妮”的语源。将“月亮”与“地球”相对比，以超然达观的视角进行了唯美的刻画，同时，也是因为我想要描绘出一个具有官能美的世界观。我刻意引入了处于对立面的阳性特质“火”，以此来反衬阴性特质“水”的神秘，使其更为深邃、宏大。内容上，最初我构建了一个从“月之使者降临此大地”开始的故事。我将这个“月之使者”设定成了，比如高维度的存在，掌管着阴性宫位～，诸如此类的感觉。对于高次元的存在而言，人类的历史不过是转瞬即逝的一瞬。于是，她俯视着这个地上——即三维的“Human Race”（人类种族），并将自己曾经历过的那些故事，如同追溯种种回忆一般，由她本人作为“讲述者”亲自道来，我是这样设定的。此外，歌词中也包含了很多跨越时代前后的复合元素，例如我运用了克里姆特“爱欲与死亡共存”这种偏近代的艺术概念，或者也融入了塔罗牌牌组所展现的那种联想空间。通过探索这些不同主题的组合，或许能进一步升华为Ave Mujica式的格调，那便是我的期望。我特意放入“欲望”、“紧张”、或者是“大宇宙”这样直白露骨的词汇，也是出于这一目的。阴性特质将阳性特质包容进去，形成一种宏大的感觉。在表达“两性交融”这一直接含义的同时，另一方面，我也将宗教的根源作为多层面的概念融入其中。阳性宫位之火的“△”与阴性宫位之水的“▽”重合，就会变成“六芒星”的符号，而这正意味着“大宇宙”，因此在第一段副歌中，我试图表达这种宇宙的完满性因果与秩序。而在最后的部分，我的期望是，最终不去描绘那种“大宇宙”般不可估量的宏大事物，而是珍重地描绘活在此刻“生命”中的“最微小的世界”。为了让听众能感受到这一点，我在结尾处忽然将视角拉回，只是从地上仰望这片“天空”。于是，支线故事包含着“生命赞歌”的含义，而我这首歌想要表达的本质依旧是“爱之歌”。</t>
   </si>
   <si>
     <t>https://natalie.mu/music/pp/avemujica02/page/2</t>
@@ -2137,6 +2131,204 @@
   </si>
   <si>
     <t>试运行 意见与建议请联系actury1995@outlook.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふたつの月 ~Deep Into The Forest~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two Moons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/双月.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長谷川大介(SUPA LOVE)</t>
+  </si>
+  <si>
+    <t>Alea jacta est,Ave Música</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alea jacta est</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ああ 深く 深く 迷い込んだ森で\nなぜか私を開いて壊すもの そう そして 感じさせるもの\n木から落ちる leaf に ほらいま 映り込む未来\nこの風 吹き抜けるとき 私は祈り人(prayer)\nおしえてよ おしえてよ こんなに美しいのはなぜ\n惹かれてく 堕ちてく 月が笑う夜\n銀のトレーにフルーツを キャンドルホルダーに火を\nこのまま いくつかの意味をさがすの その幻を暴きたい\n常に終わりは始まりと組まれる 不思議な creation\nこの風 命集めて いま 昇るなら\nおしえてよ おしえてよ こんなに苦しいのはなぜ\n鏡の中の彼女が 嘲笑う夜\n大気の重さで もうひとつの月が顔を出す\n“早く目覚めて ここで眠ってしまわないように”\nおしえてよ おしえてよ こんなに美しいのはなぜ\n惹かれてく 堕ちてく 月が笑う夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47931075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47931075_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47931075_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47931075_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47931075_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47931075_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>——初华和祥子，换句话说也就是 Doloris 和 Oblivionis，在演唱会上也有很多像「双月 ~Deep Into The Forest~」和「Symbol III : ▽」这样成对出现的演出呢。\n高尾：大家也都非常敏锐地感受到了呢。我每次在演唱会上都会想着“请期待动画！”（笑）\n渡濑：初华从动画的先导预告片时期开始，被截取出来的台词就几乎全都和祥子有关呢。我想大家从那个阶段开始，应该就已经察觉到一些端倪了吧（笑）。</t>
+  </si>
+  <si>
+    <t>https://www.lisani.jp/0000274367/4/?show_more=1</t>
+  </si>
+  <si>
+    <t>渡濑结月&amp;高尾奏音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我在副歌的乐句中加入了“波浪”这一意象，它也是司掌水的精灵“温蒂妮”的语源。将“月亮”与“地球”相对比，以超然达观的视角进行了唯美的刻画，同时，也是因为我想要描绘出一个具有官能美的世界观。我刻意引入了处于对立面的阳性特质“火”，以此来反衬阴性特质“水”的神秘，使其更为深邃、宏大。内容上，最初我构建了一个从“月之使者降临此大地”开始的故事。我将这个“月之使者”设定成了，比如高维度的存在，掌管着阴性宫位～，诸如此类的感觉。对于高次元的存在而言，人类的历史不过是转瞬即逝的一瞬。于是，她俯视着这个地上——即三维的“Human Race”（人类种族），并将自己曾经历过的那些故事，如同追溯种种回忆一般，由她本人作为“讲述者”亲自道来，我是这样设定的。此外，歌词中也包含了很多跨越时代前后的复合元素，例如我运用了克里姆特“爱欲与死亡共存”这种偏近代的艺术概念，或者也融入了塔罗牌牌组所展现的那种联想空间。通过探索这些不同主题的组合，或许能进一步升华为Ave Mujica式的格调，那便是我的期望。我特意放入“欲望”、“紧张”、或者是“大宇宙”这样直白露骨的词汇，也是出于这一目的。阴性特质将阳性特质包容进去，形成一种宏大的感觉。在表达“两性交融”这一直接含义的同时，另一方面，我也将宗教的根源作为多层面的概念融入其中。阳性宫位之火的“△”与阴性宫位之水的“▽”重合，就会变成“六芒星”的符号，而这正意味着“大宇宙”，因此在第一段副歌中，我试图表达这种宇宙的完满性因果与秩序。而在最后的部分，我的期望是，最终不去描绘那种“大宇宙”般不可估量的宏大事物，而是珍重地描绘活在此刻“生命”中的“最微小的世界”。为了让听众能感受到这一点，我在结尾处忽然将视角拉回，只是从地上仰望这片“天空”。于是，支线故事包含着“生命赞歌”的含义，而我这首歌想要表达的本质依旧是“爱之歌”。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「Choir 'S' Choir」公开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角本麻衣(SUPA LOVE)</t>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101</t>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac47935101_10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac48752881</t>
+  </si>
+  <si>
+    <t>https://www.acfun.cn/v/ac48752881_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.oricon.co.jp/news/2294611/full/</t>
+  </si>
+  <si>
+    <t>冈田梦以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我觉得比较棘手的一首歌是「Choir ‘S’ Choir」。在大家都在踩正拍节奏的时候，唯独贝斯走的是反拍。此外，由于曲速很快、乐句也很细密，实际上在曲子中，我需要不断切换使用下拨和交替拨弦。虽然像这样极具挑战性的曲子有很多，但弹奏「Ave Mujica」总之就是非常开心（笑）。尤其喜欢变成三拍子那一段的乐句。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>——接下来请谈谈迷你专辑「Alea jacta est」。这张专辑收录了以重型乐器编排打造的硬核金属音效为主轴的共6首歌曲，能请各位说说各自最推的歌曲吗？\n
+渡濑：刚才我们也稍微聊到了推的歌曲，当时めいしゃん（冈田）提到的「Choir ‘S’ Choir」我也很喜欢。虽然还不能详细透露，其实Ave Mujica的每首歌都有各自的主题元素（Theme），在看到0th LIVE的演出时，我发现这首歌正是沿着那个主题展开的，就觉得“就是这个！”而感觉很感动。从那以后一下子就喜欢上了。\n
+佐佐木：我录音的时候也被告知了每首歌的母题（Motif），是注意着那种意象和世界观去演唱的。歌词里，Diggy-MO’先生独特的措辞和故事之中，也散落着与那个主题相关的关键词，希望大家一定要去考察解读。\n
+渡濑：めいしゃん为什么最推「Choir ‘S’ Choir」？\n
+冈田：因为这首的贝斯在原创曲里是最难的，跟它较劲的时间也比较长，还有就是我在这首歌里很喜欢李子酱的演唱。我觉得她对声音的运用以及演唱技巧的储备极其丰富，比如还加入了一点嘶吼式的唱法。\n
+佐佐木：诶——好开心！不过「Choir ‘S’ Choir」里大家的和声也很多，所以完成得非常华丽呢。\n
+冈田：のんたん（高尾）的念白也很棒。\n
+高尾：谢谢！其他还有「Mas?uerade Rhapsody Re?uest」里也有念白，祥子在歌曲里就会突然开始说英语（笑）。而且「Choir ‘S’ Choir」里的rap部分还是拉丁语。还有，这个可能谁都没有注意到，在「神さま、バカ」副歌结尾的“神さま、バカ”那里，用耳语声加入了一句“神さま、バカ”的念白，其实那也是我（笑）。\n
+（中略）\n
+米泽：我也推「Choir ‘S’ Choir」当作推的歌曲。除此之外，「Ave Mujica」是我们最早拿到的歌曲，单纯是听得最多的一首，而且乐队名直接就是歌名，所以觉得这是很能代表我们的歌，感情很深。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.animatetimes.com/news/details.php?id=1711341820&amp;p=3</t>
+  </si>
+  <si>
+    <t>全员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高尾：（笑）。比如说，「Choir ‘S’ Choir」的话，就是想象着在草原上弹奏的感觉。我会在自己心里变换场景意象来演奏，所以刚才被你说中，吓了一跳。\n
+佐佐木：我一直都感觉得到哦！\n
+高尾：好厉害！我们心意相通了啊！\n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佐佐木李子&amp;高尾奏音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黒のバースデイ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>——感觉还能通宵畅聊呢（笑）。那么，如果要选一首特别有感情的乐曲的话？\n
+高尾：真的很难选……我可能会选「黒のバースデイ」。因为它是0th LIVE上第一首演奏的歌曲，演奏的时候会有一种瞬间回到那个时候的感觉。或者说，能让我找回初心。\n
+米泽：我懂！有一种穿着黑袍的感觉。\n
+渡濑：确实（笑）。对观众来说，如果要说Ave Mujica的代表曲可能会想到「Ave Mujica」，但对我们来说，「黒のバースデイ」才是真正开始的曲子。最早练习的也是这首歌。\n
+佐佐木：而且，它也是一首仿佛在为 Mujica 的诞生送上祝福的歌曲。\n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lisani.jp/0000271996/2/?show_more=1</t>
+  </si>
+  <si>
+    <t>连此领域也被侵蚀 是的 舞台升起降下\n被重新记载的 my 诞生日 今晚 去感受 燃烧着 痛苦挣扎\nna, 鲜活妖艳的 mad day 充斥秘密的 ruler loo-la, cool, cool, \n“欢迎前来 请过来这里” 宣告着 起始之时刻\n呐啊 柔软优美的足尖 摇荡勾勒轮舞曲\n将那纯白的礼服 来吧 此刻 染上黑暗之色\n杀戮的暗影啊 升腾而起吧 \n看见了 看见了 本不可见之物 看啊\n重获新生 啊啊 成为真正的我\n天使拦截者 concept 混乱的局面 堕入陷阱之中\n将那小小的胸膛撕裂\nbloody lover, lover, la-la-la, bloody 散落一地啊 磨损的胶片\n一幕幕场景 重新浮现 在眼帘之后\n呐啊 在这黏着不去的夜里 再一次 极致的快感…\njack-jackie, 邪鬼 zap, zap, 但还不够啊 还远远不够啊\n追求着渴望着 被折磨着\n奔驰着 奔驰着 逐渐消逝的行星 看啊\n若要扭曲真实 则将承受宇宙的风险\ncallin' 即使不断呼喊 darlin' 也不会回来\n无论是谁 都会被选中成为拼图的碎片\n这样就好 维持这样就好 我会给你整个世界\n看见了 看见了 本不可见之物 看啊\n重获新生 啊啊 成为真正的我\noh, my..\nblack-black, black, my black birthday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊啊 深深地 深深地 迷失在森林中\n某物莫名将我剖开破坏 是啊 而后又让我有所感受\n从树上落下的 leaf 上 看吧 此刻 正映照着未来\n当这阵风吹过时 我即是祈祷者（prayer）\n请告诉我 请告诉我吧 为何如此美丽动人\n渐受蛊惑 步步坠落 月亮嗤笑之夜\n将果实盛入银盘 为烛台点燃火焰\n就这样 寻找种种意义 渴望揭穿那重幻象\n结束总与开始交织纠缠 不可思议的 creation\n这阵风 汇聚生命 现在 若能升腾而起\n请告诉我 请告诉我吧 为何如此痛苦难耐\n镜中的她 嘲弄之夜\n大气的重压之下 另一轮月亮显露真容\n“快快醒来 可不要在此处沉睡”\n请告诉我 请告诉我吧 为何如此美丽动人\n渐受蛊惑 步步坠落 月亮嗤笑之夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[daa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa]\nChoir Choir, Choir Choir ‘S’ Choir\nそう サジェスチョンなら Spade 彷徨うスペクター [Spiritual, So Spiritual]\nイミテーションやら聖なる讃美歌 [Sensual, So Sensual]\nサディスティック サディスティック 堕天使\nヒステリック ヒステリック 宿る刻\n[look, 歌う胸像 the show must go on ルカ 精霊 精霊 ghost, oh, it's comin']\n‘信じる？ 信じない？’ いないいないばあ\n感情の万華鏡 引きずり込むのは\nねぇ誰？ ねぇ誰？ 叫ぶ声が\n夜に酔えば 真っ赤に腫れた唇がわたしを貪るの\n‘S’ カレート ‘S’ カレート 忍び寄るわ mysterious\n目眩く描くほどに 狂い咲くカーニヴァル\nChoir Choir, Choir Choir ‘S’ Choir\noh, イリュージョンなら左手のジェスチャー [Spiritual, So Spiritual]\nテンプテーション 神話にはつづきが [Sensual, So Sensual]\nサタニック サタニック マジェスティ\nヒプノティック ヒプノティック 裁く刻\n[see, 'il giudizio, la giustizia' 下る極彩色 shockin' psychic]\n‘感じる？ 感じない？’ お気に召す mo'\n触れてみて 触れてみて 試されてもいい\nねぇ誰？ ねぇ誰？ 甘い夢が\n闇に占う カードの悪魔 誘う魂の行方 今\n‘S’ カレート ‘S’ カレート 気の触れた my desire\n鼓膜を劈くほどに 咽び泣くアリア\n[daa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa,\ndaa-mennus, daa-menn, philis-poliaa, daa-la-la-daa-daa]\nああ ワルツに身を委ねて ゆらゆらゆら\n誰？ ねぇ誰？ 叫ぶ声が\n夜に酔えば 真っ赤に腫れた唇がわたしを貪るの\n‘S’ カレート ‘S’ カレート 忍び寄るわ mysterious\n目眩く描くほどに 狂い咲くカーニヴァル\n[daa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa,\ndaa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa]\nChoir Choir, Choir Choir ‘S’ Choir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[daa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa]\nChoir Choir, Choir Choir ‘S’ Choir\n是的 若要给出暗示 Spade 彷徨的幽灵 [Spiritual, So Spiritual]\n赝品亦或是神圣的赞美歌 [Sensual, So Sensual]\n嗜虐的 嗜虐的 堕天使\n癔病的 癔病的 附身之时\n[look, 歌唱的胸像 the show must go on 路加 精灵 精灵 ghost, oh, it's comin']\n‘相信？ 不相信’ 不在、不在、在这里\n感情的万华镜 被卷入其中的是\n是谁？ 是谁？ 是谁正在呼喊\n沉醉于夜晚 鲜红肿胀的嘴唇将我贪婪吞噬\n‘S’calate ‘S’calate 悄然接近的 mysterious\n勾勒到目眩神迷 癫狂盛放的狂欢\nChoir Choir, Choir Choir ‘S’ Choir\noh, 若是幻觉则用左手的手势 [Spiritual, So Spiritual]\n诱惑 神话仍未终结 [Sensual, So Sensual]\n恶魔般的 恶魔般的 无上威严\n催眠的 催眠的 裁决之时\n[see, 'il giudizio, la giustizia' 降临的绚丽色彩 shockin' psychic]\n‘感觉到？ 感觉不到？’如你所愿 mo'\n试着触摸 试着触摸 即使受到考验也无妨\n是谁？ 是谁？ 将这甜美的梦…\n向黑暗问卜 卡牌的恶魔 引诱灵魂的去向 此刻\n‘S’calate ‘S’calate 陷入疯狂的 my desire\n似要刺破鼓膜一般 呜咽的咏叹调\n[daa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa,\ndaa-mennus, daa-menn, philis-poliaa, daa-la-la-daa-daa]\n啊啊 委身于华尔兹吧 摇摇晃晃\n是谁？ 是谁？ 是谁正在呼喊\n沉醉于夜晚 鲜红肿胀的嘴唇将我贪婪吞噬\n‘S’calate ‘S’calate 悄然接近的 mysterious\n勾勒到目眩神迷 癫狂盛放的狂欢\n[daa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa,\ndaa-mennus, daa-menn, philis-poliaa, taa-mennus, taa-menn, jealis-moliaa]\nChoir Choir, Choir Choir ‘S’ Choir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choir 'S' Choir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.浏览器性能优化 2.Songs更新黒のバースデイ、ふたつの月 ~Deep Into The Forest~、Choir 'S' Choir 3.日常BUG维护</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2147,7 +2339,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2161,6 +2353,21 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2180,15 +2387,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2488,11 +2702,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="96.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="117.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2508,10 +2722,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B2" t="s">
         <v>693</v>
-      </c>
-      <c r="B2" t="s">
-        <v>695</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -2522,9 +2736,20 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>741</v>
+      </c>
+      <c r="C4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2536,8 +2761,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="51.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="50.6328125" customWidth="1"/>
+    <col min="15" max="15" width="35.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2552,7 +2792,7 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F1" t="s">
@@ -2599,7 +2839,7 @@
       <c r="D2">
         <v>2025</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="3">
         <v>45672</v>
       </c>
       <c r="F2" t="s">
@@ -2646,7 +2886,7 @@
       <c r="D3">
         <v>2024</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <v>45458</v>
       </c>
       <c r="F3" t="s">
@@ -2693,7 +2933,7 @@
       <c r="D4">
         <v>2025</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="3">
         <v>46001</v>
       </c>
       <c r="F4" t="s">
@@ -2740,7 +2980,7 @@
       <c r="D5">
         <v>2026</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="3">
         <v>46190</v>
       </c>
       <c r="F5" t="s">
@@ -2787,7 +3027,7 @@
       <c r="D6">
         <v>2025</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
         <v>45904</v>
       </c>
       <c r="F6" t="s">
@@ -2826,7 +3066,7 @@
         <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>733</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -2834,7 +3074,7 @@
       <c r="D7">
         <v>2023</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="3">
         <v>45026</v>
       </c>
       <c r="F7" t="s">
@@ -2861,8 +3101,105 @@
       <c r="M7" t="s">
         <v>73</v>
       </c>
+      <c r="N7" t="s">
+        <v>736</v>
+      </c>
       <c r="O7" t="s">
-        <v>74</v>
+        <v>698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>2023</v>
+      </c>
+      <c r="E8" s="3">
+        <v>45032</v>
+      </c>
+      <c r="F8" t="s">
+        <v>696</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>697</v>
+      </c>
+      <c r="J8" t="s">
+        <v>697</v>
+      </c>
+      <c r="K8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" t="s">
+        <v>444</v>
+      </c>
+      <c r="M8" t="s">
+        <v>700</v>
+      </c>
+      <c r="N8" t="s">
+        <v>737</v>
+      </c>
+      <c r="O8" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" t="s">
+        <v>740</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>2023</v>
+      </c>
+      <c r="E9" s="3">
+        <v>45039</v>
+      </c>
+      <c r="F9" t="s">
+        <v>449</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>712</v>
+      </c>
+      <c r="J9" t="s">
+        <v>712</v>
+      </c>
+      <c r="K9" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" t="s">
+        <v>451</v>
+      </c>
+      <c r="M9" t="s">
+        <v>738</v>
+      </c>
+      <c r="N9" t="s">
+        <v>739</v>
+      </c>
+      <c r="O9" t="s">
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -2873,21 +3210,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="63.08984375" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" t="s">
         <v>75</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>76</v>
-      </c>
-      <c r="D1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2895,10 +3238,10 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
         <v>78</v>
-      </c>
-      <c r="C2" t="s">
-        <v>79</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -2909,10 +3252,10 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>710</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
@@ -2923,10 +3266,10 @@
         <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -2937,13 +3280,13 @@
         <v>42</v>
       </c>
       <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
         <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2951,13 +3294,13 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
         <v>87</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2965,10 +3308,10 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2976,10 +3319,80 @@
         <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>695</v>
+      </c>
+      <c r="B9" t="s">
+        <v>707</v>
+      </c>
+      <c r="C9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D9" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" t="s">
+        <v>727</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="D10" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B11" t="s">
+        <v>728</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" t="s">
+        <v>731</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D12" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>734</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="D13" t="s">
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -2990,1221 +3403,1827 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.26953125" customWidth="1"/>
+    <col min="6" max="6" width="39.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>95</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>96</v>
-      </c>
-      <c r="E1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>45682</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="3">
         <v>45690</v>
       </c>
       <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" t="s">
         <v>102</v>
-      </c>
-      <c r="D3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>45773</v>
       </c>
       <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
         <v>105</v>
-      </c>
-      <c r="D4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>45774</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="3">
         <v>45782</v>
       </c>
       <c r="C6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
         <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="3">
         <v>45815</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="3">
         <v>45941</v>
       </c>
       <c r="C8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" t="s">
         <v>115</v>
-      </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>45942</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>46193</v>
       </c>
       <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
         <v>120</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="3">
         <v>46243</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="3">
         <v>46250</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="3">
         <v>45480</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="3">
         <v>45578</v>
       </c>
       <c r="C14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" t="s">
         <v>129</v>
-      </c>
-      <c r="D14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="3">
         <v>45640</v>
       </c>
       <c r="C15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" t="s">
         <v>132</v>
-      </c>
-      <c r="D15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="3">
         <v>45641</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="3">
         <v>45690</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="3">
         <v>45864</v>
       </c>
       <c r="C18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
         <v>138</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="3">
         <v>45865</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="3">
         <v>46193</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="3">
         <v>46242</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="3">
         <v>46005</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D22" t="s">
         <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="3">
         <v>46037</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="3">
         <v>46081</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="3">
         <v>46082</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="3">
         <v>46101</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="3">
         <v>46116</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="3">
         <v>46123</v>
       </c>
       <c r="C28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="3">
         <v>46129</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="3">
         <v>46138</v>
       </c>
       <c r="C30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="3">
         <v>46143</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="3">
         <v>46146</v>
       </c>
       <c r="C32" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="3">
         <v>46192</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="3">
         <v>46193</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="3">
         <v>46242</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="3">
         <v>46243</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="3">
         <v>46250</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="3">
         <v>46005</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F38" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="3">
         <v>46037</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="3">
         <v>46193</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="3">
         <v>45081</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D41" t="s">
         <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="3">
         <v>45318</v>
       </c>
       <c r="C42" t="s">
+        <v>172</v>
+      </c>
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" t="s">
+        <v>98</v>
+      </c>
+      <c r="F42" t="s">
         <v>174</v>
-      </c>
-      <c r="D42" t="s">
-        <v>175</v>
-      </c>
-      <c r="E42" t="s">
-        <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="3">
         <v>45360</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E43" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>67</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="3">
         <v>45451</v>
       </c>
       <c r="C44" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" t="s">
         <v>178</v>
-      </c>
-      <c r="D44" t="s">
-        <v>179</v>
-      </c>
-      <c r="E44" t="s">
-        <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="3">
         <v>45480</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="3">
         <v>45486</v>
       </c>
       <c r="C46" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D46" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E46" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>67</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="3">
         <v>45487</v>
       </c>
       <c r="C47" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" t="s">
         <v>181</v>
       </c>
-      <c r="D47" t="s">
-        <v>183</v>
-      </c>
       <c r="E47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="3">
         <v>45578</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E48" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="3">
         <v>45641</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F49" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>67</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="3">
         <v>45682</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="3">
         <v>45690</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E51" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="3">
         <v>45864</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F52" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="3">
         <v>45865</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F53" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="3">
         <v>46005</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
         <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F54" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="3">
         <v>46037</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="3">
         <v>46082</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F56" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="3">
         <v>46123</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>67</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="3">
         <v>46129</v>
       </c>
       <c r="C58" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="3">
         <v>46138</v>
       </c>
       <c r="C59" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E59" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="3">
         <v>46143</v>
       </c>
       <c r="C60" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="3">
         <v>46146</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E61" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="3">
         <v>46192</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F62" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>67</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="3">
         <v>46193</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E63" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F63" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="3">
         <v>46242</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="3">
         <v>46243</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E65" t="s">
-        <v>112</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>695</v>
+      </c>
+      <c r="B66" s="3">
+        <v>45081</v>
+      </c>
+      <c r="C66" t="s">
+        <v>170</v>
+      </c>
+      <c r="D66" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" t="s">
+        <v>98</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>695</v>
+      </c>
+      <c r="B67" s="3">
+        <v>45318</v>
+      </c>
+      <c r="C67" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" t="s">
+        <v>98</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>695</v>
+      </c>
+      <c r="B68" s="3">
+        <v>45360</v>
+      </c>
+      <c r="C68" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" t="s">
+        <v>175</v>
+      </c>
+      <c r="E68" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>695</v>
+      </c>
+      <c r="B69" s="3">
+        <v>45451</v>
+      </c>
+      <c r="C69" t="s">
+        <v>176</v>
+      </c>
+      <c r="D69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E69" t="s">
+        <v>98</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>695</v>
+      </c>
+      <c r="B70" s="3">
+        <v>45480</v>
+      </c>
+      <c r="C70" t="s">
+        <v>125</v>
+      </c>
+      <c r="D70" t="s">
+        <v>126</v>
+      </c>
+      <c r="E70" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>695</v>
+      </c>
+      <c r="B71" s="3">
+        <v>45578</v>
+      </c>
+      <c r="C71" t="s">
+        <v>127</v>
+      </c>
+      <c r="D71" t="s">
+        <v>128</v>
+      </c>
+      <c r="E71" t="s">
+        <v>98</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>695</v>
+      </c>
+      <c r="B72" s="3">
+        <v>45641</v>
+      </c>
+      <c r="C72" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" t="s">
+        <v>133</v>
+      </c>
+      <c r="E72" t="s">
+        <v>98</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>695</v>
+      </c>
+      <c r="B73" s="3">
+        <v>46005</v>
+      </c>
+      <c r="C73" t="s">
+        <v>143</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73" t="s">
+        <v>98</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>695</v>
+      </c>
+      <c r="B74" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C74" t="s">
+        <v>145</v>
+      </c>
+      <c r="D74" t="s">
+        <v>146</v>
+      </c>
+      <c r="E74" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>225</v>
+      </c>
+      <c r="B75" s="3">
+        <v>45081</v>
+      </c>
+      <c r="C75" t="s">
+        <v>170</v>
+      </c>
+      <c r="D75" t="s">
+        <v>71</v>
+      </c>
+      <c r="E75" t="s">
+        <v>98</v>
+      </c>
+      <c r="F75" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>225</v>
+      </c>
+      <c r="B76" s="3">
+        <v>45318</v>
+      </c>
+      <c r="C76" t="s">
+        <v>172</v>
+      </c>
+      <c r="D76" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" t="s">
+        <v>98</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" s="3">
+        <v>45360</v>
+      </c>
+      <c r="C77" t="s">
+        <v>151</v>
+      </c>
+      <c r="D77" t="s">
+        <v>175</v>
+      </c>
+      <c r="E77" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" s="3">
+        <v>45451</v>
+      </c>
+      <c r="C78" t="s">
+        <v>176</v>
+      </c>
+      <c r="D78" t="s">
+        <v>177</v>
+      </c>
+      <c r="E78" t="s">
+        <v>98</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>225</v>
+      </c>
+      <c r="B79" s="3">
+        <v>45480</v>
+      </c>
+      <c r="C79" t="s">
+        <v>125</v>
+      </c>
+      <c r="D79" t="s">
+        <v>126</v>
+      </c>
+      <c r="E79" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" s="3">
+        <v>45578</v>
+      </c>
+      <c r="C80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" t="s">
+        <v>98</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>225</v>
+      </c>
+      <c r="B81" s="3">
+        <v>45641</v>
+      </c>
+      <c r="C81" t="s">
+        <v>130</v>
+      </c>
+      <c r="D81" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>225</v>
+      </c>
+      <c r="B82" s="3">
+        <v>45690</v>
+      </c>
+      <c r="C82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" t="s">
+        <v>101</v>
+      </c>
+      <c r="E82" t="s">
+        <v>98</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>225</v>
+      </c>
+      <c r="B83" s="3">
+        <v>45864</v>
+      </c>
+      <c r="C83" t="s">
+        <v>136</v>
+      </c>
+      <c r="D83" t="s">
+        <v>137</v>
+      </c>
+      <c r="E83" t="s">
+        <v>98</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>225</v>
+      </c>
+      <c r="B84" s="3">
+        <v>45865</v>
+      </c>
+      <c r="C84" t="s">
+        <v>136</v>
+      </c>
+      <c r="D84" t="s">
+        <v>139</v>
+      </c>
+      <c r="E84" t="s">
+        <v>98</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>225</v>
+      </c>
+      <c r="B85" s="3">
+        <v>46005</v>
+      </c>
+      <c r="C85" t="s">
+        <v>143</v>
+      </c>
+      <c r="D85" t="s">
+        <v>46</v>
+      </c>
+      <c r="E85" t="s">
+        <v>98</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>225</v>
+      </c>
+      <c r="B86" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C86" t="s">
+        <v>145</v>
+      </c>
+      <c r="D86" t="s">
+        <v>146</v>
+      </c>
+      <c r="E86" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>225</v>
+      </c>
+      <c r="B87" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C87" t="s">
+        <v>103</v>
+      </c>
+      <c r="D87" t="s">
+        <v>149</v>
+      </c>
+      <c r="E87" t="s">
+        <v>98</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>225</v>
+      </c>
+      <c r="B88" s="3">
+        <v>46123</v>
+      </c>
+      <c r="C88" t="s">
+        <v>155</v>
+      </c>
+      <c r="D88" t="s">
+        <v>156</v>
+      </c>
+      <c r="E88" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>225</v>
+      </c>
+      <c r="B89" s="3">
+        <v>46129</v>
+      </c>
+      <c r="C89" t="s">
+        <v>157</v>
+      </c>
+      <c r="D89" t="s">
+        <v>158</v>
+      </c>
+      <c r="E89" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>225</v>
+      </c>
+      <c r="B90" s="3">
+        <v>46138</v>
+      </c>
+      <c r="C90" t="s">
+        <v>159</v>
+      </c>
+      <c r="D90" t="s">
+        <v>160</v>
+      </c>
+      <c r="E90" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>225</v>
+      </c>
+      <c r="B91" s="3">
+        <v>46143</v>
+      </c>
+      <c r="C91" t="s">
+        <v>161</v>
+      </c>
+      <c r="D91" t="s">
+        <v>162</v>
+      </c>
+      <c r="E91" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>225</v>
+      </c>
+      <c r="B92" s="3">
+        <v>46146</v>
+      </c>
+      <c r="C92" t="s">
+        <v>163</v>
+      </c>
+      <c r="D92" t="s">
+        <v>164</v>
+      </c>
+      <c r="E92" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>225</v>
+      </c>
+      <c r="B93" s="3">
+        <v>46192</v>
+      </c>
+      <c r="C93" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93" t="s">
+        <v>165</v>
+      </c>
+      <c r="E93" t="s">
+        <v>98</v>
+      </c>
+      <c r="F93" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>225</v>
+      </c>
+      <c r="B94" s="3">
+        <v>46193</v>
+      </c>
+      <c r="C94" t="s">
+        <v>118</v>
+      </c>
+      <c r="D94" t="s">
+        <v>119</v>
+      </c>
+      <c r="E94" t="s">
+        <v>98</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>225</v>
+      </c>
+      <c r="B95" s="3">
+        <v>46242</v>
+      </c>
+      <c r="C95" t="s">
+        <v>121</v>
+      </c>
+      <c r="D95" t="s">
+        <v>142</v>
+      </c>
+      <c r="E95" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>225</v>
+      </c>
+      <c r="B96" s="3">
+        <v>46243</v>
+      </c>
+      <c r="C96" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" t="s">
+        <v>122</v>
+      </c>
+      <c r="E96" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F66" r:id="rId1" xr:uid="{F96252D1-7391-4035-9C6B-65974F46A039}"/>
+    <hyperlink ref="F67" r:id="rId2" xr:uid="{7D355A3D-CDF7-4F54-BD3D-532EF9592C40}"/>
+    <hyperlink ref="F69" r:id="rId3" xr:uid="{344962B3-28C2-4E81-9EE6-222657122F63}"/>
+    <hyperlink ref="F71" r:id="rId4" xr:uid="{8784786D-B9E4-4488-B143-B8EE64AABC18}"/>
+    <hyperlink ref="F72" r:id="rId5" xr:uid="{78BF8598-2FDB-4812-9F7E-17D5A315B0A1}"/>
+    <hyperlink ref="F73" r:id="rId6" xr:uid="{98299038-AA55-4AB7-9457-BBA606487D4D}"/>
+    <hyperlink ref="F76" r:id="rId7" xr:uid="{3C9C6896-C338-4C88-9338-54BF284C5083}"/>
+    <hyperlink ref="F78" r:id="rId8" xr:uid="{598E8CE7-F92A-4554-8209-B9FF58341ECB}"/>
+    <hyperlink ref="F80" r:id="rId9" xr:uid="{26925AE0-416E-4139-8B45-DF2735B8CB9B}"/>
+    <hyperlink ref="F81" r:id="rId10" xr:uid="{05C23CC5-7E2B-4344-AED9-0D74302EBD3D}"/>
+    <hyperlink ref="F82" r:id="rId11" xr:uid="{11DB7730-B225-44ED-BD29-F37560C5A87F}"/>
+    <hyperlink ref="F83" r:id="rId12" xr:uid="{A4BC8A76-F879-4A89-B752-BAA50A3D25D4}"/>
+    <hyperlink ref="F84" r:id="rId13" xr:uid="{FCE5C466-2ACC-4548-8A6D-01D646CF502D}"/>
+    <hyperlink ref="F85" r:id="rId14" xr:uid="{31D86C89-E8FA-418C-95B7-4AC96C3471F6}"/>
+    <hyperlink ref="F87" r:id="rId15" xr:uid="{C865D614-0653-429B-BDE4-3A9206FC48BF}"/>
+    <hyperlink ref="F94" r:id="rId16" xr:uid="{A1563D3E-434D-4978-99F7-06BB0D2A0F5E}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4216,48 +5235,48 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>193</v>
-      </c>
-      <c r="E1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B2" s="1">
         <v>45081</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" t="s">
         <v>197</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>198</v>
-      </c>
-      <c r="F2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G2" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4281,272 +5300,272 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" t="s">
         <v>201</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>202</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>203</v>
-      </c>
-      <c r="E1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" t="s">
         <v>210</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>211</v>
-      </c>
-      <c r="D4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" t="s">
         <v>214</v>
-      </c>
-      <c r="D5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E7" t="s">
         <v>219</v>
-      </c>
-      <c r="C7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E7" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" t="s">
         <v>222</v>
-      </c>
-      <c r="C8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E11" t="s">
         <v>228</v>
-      </c>
-      <c r="C11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" t="s">
         <v>240</v>
-      </c>
-      <c r="C18" t="s">
-        <v>241</v>
-      </c>
-      <c r="D18" t="s">
-        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4562,232 +5581,232 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1" t="s">
         <v>243</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>244</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>245</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>246</v>
-      </c>
-      <c r="F1" t="s">
-        <v>247</v>
-      </c>
-      <c r="G1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D2" t="s">
         <v>249</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>250</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>251</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>252</v>
-      </c>
-      <c r="F2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" t="s">
         <v>250</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>251</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>252</v>
-      </c>
-      <c r="F3" t="s">
-        <v>253</v>
-      </c>
-      <c r="G3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E4" t="s">
         <v>250</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>251</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>252</v>
-      </c>
-      <c r="F4" t="s">
-        <v>253</v>
-      </c>
-      <c r="G4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E5" t="s">
         <v>250</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>251</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>252</v>
-      </c>
-      <c r="F5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G5" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" t="s">
         <v>250</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>251</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>252</v>
-      </c>
-      <c r="F6" t="s">
-        <v>253</v>
-      </c>
-      <c r="G6" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" t="s">
         <v>250</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>251</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>252</v>
-      </c>
-      <c r="F7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G7" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" t="s">
         <v>250</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>251</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>252</v>
-      </c>
-      <c r="F8" t="s">
-        <v>253</v>
-      </c>
-      <c r="G8" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" t="s">
         <v>250</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>251</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>252</v>
-      </c>
-      <c r="F9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G9" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" t="s">
         <v>250</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>251</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>252</v>
-      </c>
-      <c r="F10" t="s">
-        <v>253</v>
-      </c>
-      <c r="G10" t="s">
-        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -4803,1041 +5822,1041 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" t="s">
         <v>266</v>
-      </c>
-      <c r="C2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D3" t="s">
         <v>266</v>
-      </c>
-      <c r="C3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" t="s">
         <v>266</v>
-      </c>
-      <c r="C4" t="s">
-        <v>267</v>
-      </c>
-      <c r="D4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" t="s">
         <v>266</v>
-      </c>
-      <c r="C5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" t="s">
         <v>266</v>
-      </c>
-      <c r="C6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" t="s">
         <v>266</v>
-      </c>
-      <c r="C7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D7" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" t="s">
         <v>266</v>
-      </c>
-      <c r="C8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D8" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" t="s">
         <v>266</v>
-      </c>
-      <c r="C9" t="s">
-        <v>267</v>
-      </c>
-      <c r="D9" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" t="s">
         <v>266</v>
-      </c>
-      <c r="C10" t="s">
-        <v>267</v>
-      </c>
-      <c r="D10" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C13" t="s">
         <v>272</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>273</v>
-      </c>
-      <c r="C13" t="s">
-        <v>274</v>
-      </c>
-      <c r="D13" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D14" t="s">
         <v>276</v>
-      </c>
-      <c r="B14" t="s">
-        <v>277</v>
-      </c>
-      <c r="C14" t="s">
-        <v>274</v>
-      </c>
-      <c r="D14" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>277</v>
+      </c>
+      <c r="B15" t="s">
+        <v>278</v>
+      </c>
+      <c r="C15" t="s">
         <v>279</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>280</v>
-      </c>
-      <c r="C15" t="s">
-        <v>281</v>
-      </c>
-      <c r="D15" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B16" t="s">
+        <v>282</v>
+      </c>
+      <c r="C16" t="s">
+        <v>279</v>
+      </c>
+      <c r="D16" t="s">
         <v>283</v>
-      </c>
-      <c r="B16" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>284</v>
+      </c>
+      <c r="B17" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" t="s">
         <v>286</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>287</v>
-      </c>
-      <c r="C17" t="s">
-        <v>288</v>
-      </c>
-      <c r="D17" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" t="s">
         <v>290</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>291</v>
-      </c>
-      <c r="C18" t="s">
-        <v>292</v>
-      </c>
-      <c r="D18" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C19" t="s">
+        <v>290</v>
+      </c>
+      <c r="D19" t="s">
         <v>294</v>
-      </c>
-      <c r="B19" t="s">
-        <v>295</v>
-      </c>
-      <c r="C19" t="s">
-        <v>292</v>
-      </c>
-      <c r="D19" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" t="s">
         <v>297</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>298</v>
-      </c>
-      <c r="C20" t="s">
-        <v>299</v>
-      </c>
-      <c r="D20" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>299</v>
+      </c>
+      <c r="B21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D21" t="s">
         <v>301</v>
-      </c>
-      <c r="B21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C21" t="s">
-        <v>299</v>
-      </c>
-      <c r="D21" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" t="s">
         <v>304</v>
-      </c>
-      <c r="B22" t="s">
-        <v>305</v>
-      </c>
-      <c r="C22" t="s">
-        <v>281</v>
-      </c>
-      <c r="D22" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D23" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B25" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D27" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B28" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D28" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D29" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D30" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D31" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>315</v>
+      </c>
+      <c r="B32" t="s">
+        <v>316</v>
+      </c>
+      <c r="C32" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" t="s">
         <v>317</v>
-      </c>
-      <c r="B32" t="s">
-        <v>318</v>
-      </c>
-      <c r="C32" t="s">
-        <v>292</v>
-      </c>
-      <c r="D32" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C33" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C34" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C36" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D36" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C37" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D37" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C38" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D38" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D39" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>325</v>
+      </c>
+      <c r="B40" t="s">
+        <v>326</v>
+      </c>
+      <c r="C40" t="s">
         <v>327</v>
       </c>
-      <c r="B40" t="s">
-        <v>328</v>
-      </c>
-      <c r="C40" t="s">
-        <v>329</v>
-      </c>
       <c r="D40" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D41" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C42" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D42" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C43" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D43" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>331</v>
+      </c>
+      <c r="B44" t="s">
+        <v>332</v>
+      </c>
+      <c r="C44" t="s">
+        <v>297</v>
+      </c>
+      <c r="D44" t="s">
         <v>333</v>
-      </c>
-      <c r="B44" t="s">
-        <v>334</v>
-      </c>
-      <c r="C44" t="s">
-        <v>299</v>
-      </c>
-      <c r="D44" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C45" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C46" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D46" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>336</v>
+      </c>
+      <c r="B47" t="s">
+        <v>337</v>
+      </c>
+      <c r="C47" t="s">
         <v>338</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47" t="s">
         <v>339</v>
-      </c>
-      <c r="C47" t="s">
-        <v>340</v>
-      </c>
-      <c r="D47" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>340</v>
+      </c>
+      <c r="B48" t="s">
+        <v>341</v>
+      </c>
+      <c r="C48" t="s">
         <v>342</v>
       </c>
-      <c r="B48" t="s">
-        <v>343</v>
-      </c>
-      <c r="C48" t="s">
-        <v>344</v>
-      </c>
       <c r="D48" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>343</v>
+      </c>
+      <c r="B49" t="s">
+        <v>344</v>
+      </c>
+      <c r="C49" t="s">
         <v>345</v>
       </c>
-      <c r="B49" t="s">
-        <v>346</v>
-      </c>
-      <c r="C49" t="s">
-        <v>347</v>
-      </c>
       <c r="D49" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C50" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D50" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>348</v>
+      </c>
+      <c r="B51" t="s">
+        <v>349</v>
+      </c>
+      <c r="C51" t="s">
         <v>350</v>
       </c>
-      <c r="B51" t="s">
-        <v>351</v>
-      </c>
-      <c r="C51" t="s">
-        <v>352</v>
-      </c>
       <c r="D51" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C52" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D52" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>353</v>
+      </c>
+      <c r="B53" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" t="s">
         <v>355</v>
       </c>
-      <c r="B53" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" t="s">
-        <v>357</v>
-      </c>
       <c r="D53" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C54" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D54" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B55" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C55" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D55" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C56" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D56" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C57" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D57" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C58" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D58" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B59" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C59" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D59" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>368</v>
+      </c>
+      <c r="B60" t="s">
+        <v>369</v>
+      </c>
+      <c r="C60" t="s">
         <v>370</v>
       </c>
-      <c r="B60" t="s">
+      <c r="D60" t="s">
         <v>371</v>
-      </c>
-      <c r="C60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D60" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B61" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C61" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D61" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B62" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C62" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D62" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B63" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C63" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D63" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>378</v>
+      </c>
+      <c r="B64" t="s">
+        <v>379</v>
+      </c>
+      <c r="C64" t="s">
         <v>380</v>
       </c>
-      <c r="B64" t="s">
-        <v>381</v>
-      </c>
-      <c r="C64" t="s">
-        <v>382</v>
-      </c>
       <c r="D64" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C65" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D65" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D66" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>385</v>
+      </c>
+      <c r="B67" t="s">
+        <v>386</v>
+      </c>
+      <c r="C67" t="s">
         <v>387</v>
       </c>
-      <c r="B67" t="s">
-        <v>388</v>
-      </c>
-      <c r="C67" t="s">
-        <v>389</v>
-      </c>
       <c r="D67" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B68" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C68" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D68" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>390</v>
+      </c>
+      <c r="B69" t="s">
+        <v>391</v>
+      </c>
+      <c r="C69" t="s">
         <v>392</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
         <v>393</v>
-      </c>
-      <c r="C69" t="s">
-        <v>394</v>
-      </c>
-      <c r="D69" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>394</v>
+      </c>
+      <c r="B70" t="s">
+        <v>395</v>
+      </c>
+      <c r="C70" t="s">
         <v>396</v>
       </c>
-      <c r="B70" t="s">
+      <c r="D70" t="s">
         <v>397</v>
-      </c>
-      <c r="C70" t="s">
-        <v>398</v>
-      </c>
-      <c r="D70" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>398</v>
+      </c>
+      <c r="B71" t="s">
+        <v>399</v>
+      </c>
+      <c r="C71" t="s">
         <v>400</v>
       </c>
-      <c r="B71" t="s">
-        <v>401</v>
-      </c>
-      <c r="C71" t="s">
-        <v>402</v>
-      </c>
       <c r="D71" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>401</v>
+      </c>
+      <c r="B72" t="s">
+        <v>402</v>
+      </c>
+      <c r="C72" t="s">
         <v>403</v>
       </c>
-      <c r="B72" t="s">
-        <v>404</v>
-      </c>
-      <c r="C72" t="s">
-        <v>405</v>
-      </c>
       <c r="D72" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>404</v>
+      </c>
+      <c r="B73" t="s">
+        <v>405</v>
+      </c>
+      <c r="C73" t="s">
         <v>406</v>
       </c>
-      <c r="B73" t="s">
-        <v>407</v>
-      </c>
-      <c r="C73" t="s">
-        <v>408</v>
-      </c>
       <c r="D73" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>407</v>
+      </c>
+      <c r="B74" t="s">
+        <v>408</v>
+      </c>
+      <c r="C74" t="s">
         <v>409</v>
       </c>
-      <c r="B74" t="s">
-        <v>410</v>
-      </c>
-      <c r="C74" t="s">
-        <v>411</v>
-      </c>
       <c r="D74" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5850,1680 +6869,1683 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K126"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="71.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F1" t="s">
         <v>412</v>
       </c>
-      <c r="D1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>413</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>414</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>415</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>416</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>417</v>
-      </c>
-      <c r="J1" t="s">
-        <v>418</v>
-      </c>
-      <c r="K1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F2" t="s">
         <v>420</v>
       </c>
-      <c r="D2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>421</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>422</v>
-      </c>
-      <c r="G2" t="s">
-        <v>423</v>
-      </c>
-      <c r="H2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J3" t="s">
         <v>425</v>
-      </c>
-      <c r="I3" t="s">
-        <v>426</v>
-      </c>
-      <c r="J3" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C4" t="s">
+        <v>418</v>
+      </c>
+      <c r="D4" t="s">
         <v>428</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>419</v>
+      </c>
+      <c r="F4" t="s">
+        <v>420</v>
+      </c>
+      <c r="G4" t="s">
         <v>429</v>
       </c>
-      <c r="C4" t="s">
-        <v>420</v>
-      </c>
-      <c r="D4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E4" t="s">
-        <v>421</v>
-      </c>
-      <c r="F4" t="s">
-        <v>422</v>
-      </c>
-      <c r="G4" t="s">
-        <v>431</v>
-      </c>
       <c r="H4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D5" t="s">
         <v>428</v>
       </c>
-      <c r="B5" t="s">
-        <v>429</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F5" t="s">
         <v>420</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>430</v>
       </c>
-      <c r="E5" t="s">
-        <v>421</v>
-      </c>
-      <c r="F5" t="s">
-        <v>422</v>
-      </c>
-      <c r="G5" t="s">
-        <v>432</v>
-      </c>
       <c r="H5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" t="s">
         <v>428</v>
       </c>
-      <c r="B6" t="s">
-        <v>429</v>
-      </c>
-      <c r="C6" t="s">
-        <v>420</v>
-      </c>
-      <c r="D6" t="s">
-        <v>430</v>
-      </c>
       <c r="E6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F6" t="s">
+        <v>423</v>
+      </c>
+      <c r="I6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J6" t="s">
         <v>425</v>
-      </c>
-      <c r="I6" t="s">
-        <v>434</v>
-      </c>
-      <c r="J6" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>433</v>
+      </c>
+      <c r="B7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D7" t="s">
         <v>435</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>436</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>420</v>
-      </c>
-      <c r="D7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E7" t="s">
-        <v>438</v>
-      </c>
-      <c r="F7" t="s">
-        <v>422</v>
       </c>
       <c r="G7" t="s">
         <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C8" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" t="s">
         <v>435</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>436</v>
       </c>
-      <c r="C8" t="s">
-        <v>420</v>
-      </c>
-      <c r="D8" t="s">
-        <v>437</v>
-      </c>
-      <c r="E8" t="s">
-        <v>438</v>
-      </c>
       <c r="F8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I8" t="s">
         <v>72</v>
       </c>
       <c r="J8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" t="s">
+        <v>440</v>
+      </c>
+      <c r="C9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D9" t="s">
         <v>441</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
+        <v>436</v>
+      </c>
+      <c r="F9" t="s">
+        <v>420</v>
+      </c>
+      <c r="G9" t="s">
         <v>442</v>
       </c>
-      <c r="C9" t="s">
-        <v>420</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="H9" t="s">
         <v>443</v>
-      </c>
-      <c r="E9" t="s">
-        <v>438</v>
-      </c>
-      <c r="F9" t="s">
-        <v>422</v>
-      </c>
-      <c r="G9" t="s">
-        <v>444</v>
-      </c>
-      <c r="H9" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B10" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" t="s">
+        <v>418</v>
+      </c>
+      <c r="D10" t="s">
         <v>441</v>
       </c>
-      <c r="B10" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10" t="s">
-        <v>420</v>
-      </c>
-      <c r="D10" t="s">
-        <v>443</v>
-      </c>
       <c r="E10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" t="s">
+        <v>711</v>
+      </c>
+      <c r="C11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D11" t="s">
         <v>448</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
+        <v>436</v>
+      </c>
+      <c r="F11" t="s">
+        <v>420</v>
+      </c>
+      <c r="G11" t="s">
         <v>449</v>
       </c>
-      <c r="C11" t="s">
-        <v>420</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="H11" t="s">
         <v>450</v>
-      </c>
-      <c r="E11" t="s">
-        <v>438</v>
-      </c>
-      <c r="F11" t="s">
-        <v>422</v>
-      </c>
-      <c r="G11" t="s">
-        <v>451</v>
-      </c>
-      <c r="H11" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" t="s">
+        <v>447</v>
+      </c>
+      <c r="C12" t="s">
+        <v>418</v>
+      </c>
+      <c r="D12" t="s">
         <v>448</v>
       </c>
-      <c r="B12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D12" t="s">
-        <v>450</v>
-      </c>
       <c r="E12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>453</v>
+      </c>
+      <c r="B13" t="s">
+        <v>454</v>
+      </c>
+      <c r="C13" t="s">
+        <v>418</v>
+      </c>
+      <c r="D13" t="s">
         <v>455</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F13" t="s">
+        <v>420</v>
+      </c>
+      <c r="G13" t="s">
         <v>456</v>
       </c>
-      <c r="C13" t="s">
-        <v>420</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="H13" t="s">
         <v>457</v>
-      </c>
-      <c r="E13" t="s">
-        <v>438</v>
-      </c>
-      <c r="F13" t="s">
-        <v>422</v>
-      </c>
-      <c r="G13" t="s">
-        <v>458</v>
-      </c>
-      <c r="H13" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>453</v>
+      </c>
+      <c r="B14" t="s">
+        <v>454</v>
+      </c>
+      <c r="C14" t="s">
+        <v>418</v>
+      </c>
+      <c r="D14" t="s">
         <v>455</v>
       </c>
-      <c r="B14" t="s">
-        <v>456</v>
-      </c>
-      <c r="C14" t="s">
-        <v>420</v>
-      </c>
-      <c r="D14" t="s">
-        <v>457</v>
-      </c>
       <c r="E14" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I14" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>460</v>
+      </c>
+      <c r="B15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C15" t="s">
+        <v>418</v>
+      </c>
+      <c r="D15" t="s">
         <v>462</v>
       </c>
-      <c r="B15" t="s">
+      <c r="E15" t="s">
+        <v>436</v>
+      </c>
+      <c r="F15" t="s">
+        <v>420</v>
+      </c>
+      <c r="G15" t="s">
         <v>463</v>
       </c>
-      <c r="C15" t="s">
-        <v>420</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="H15" t="s">
         <v>464</v>
-      </c>
-      <c r="E15" t="s">
-        <v>438</v>
-      </c>
-      <c r="F15" t="s">
-        <v>422</v>
-      </c>
-      <c r="G15" t="s">
-        <v>465</v>
-      </c>
-      <c r="H15" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>460</v>
+      </c>
+      <c r="B16" t="s">
+        <v>461</v>
+      </c>
+      <c r="C16" t="s">
+        <v>418</v>
+      </c>
+      <c r="D16" t="s">
         <v>462</v>
       </c>
-      <c r="B16" t="s">
-        <v>463</v>
-      </c>
-      <c r="C16" t="s">
-        <v>420</v>
-      </c>
-      <c r="D16" t="s">
-        <v>464</v>
-      </c>
       <c r="E16" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I16" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J16" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B17" t="s">
+        <v>468</v>
+      </c>
+      <c r="C17" t="s">
+        <v>418</v>
+      </c>
+      <c r="D17" t="s">
         <v>469</v>
-      </c>
-      <c r="B17" t="s">
-        <v>470</v>
-      </c>
-      <c r="C17" t="s">
-        <v>420</v>
-      </c>
-      <c r="D17" t="s">
-        <v>471</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G17" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>467</v>
+      </c>
+      <c r="B18" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" t="s">
+        <v>418</v>
+      </c>
+      <c r="D18" t="s">
         <v>469</v>
-      </c>
-      <c r="B18" t="s">
-        <v>470</v>
-      </c>
-      <c r="C18" t="s">
-        <v>420</v>
-      </c>
-      <c r="D18" t="s">
-        <v>471</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G18" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H18" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>467</v>
+      </c>
+      <c r="B19" t="s">
+        <v>468</v>
+      </c>
+      <c r="C19" t="s">
+        <v>418</v>
+      </c>
+      <c r="D19" t="s">
         <v>469</v>
-      </c>
-      <c r="B19" t="s">
-        <v>470</v>
-      </c>
-      <c r="C19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D19" t="s">
-        <v>471</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I19" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J19" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B20" t="s">
+        <v>476</v>
+      </c>
+      <c r="C20" t="s">
+        <v>477</v>
+      </c>
+      <c r="D20" t="s">
         <v>478</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>479</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
+        <v>420</v>
+      </c>
+      <c r="G20" t="s">
         <v>480</v>
-      </c>
-      <c r="E20" t="s">
-        <v>481</v>
-      </c>
-      <c r="F20" t="s">
-        <v>422</v>
-      </c>
-      <c r="G20" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B21" t="s">
+        <v>476</v>
+      </c>
+      <c r="C21" t="s">
+        <v>477</v>
+      </c>
+      <c r="D21" t="s">
         <v>478</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>479</v>
       </c>
-      <c r="D21" t="s">
-        <v>480</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>420</v>
+      </c>
+      <c r="G21" t="s">
         <v>481</v>
-      </c>
-      <c r="F21" t="s">
-        <v>422</v>
-      </c>
-      <c r="G21" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B22" t="s">
+        <v>476</v>
+      </c>
+      <c r="C22" t="s">
+        <v>477</v>
+      </c>
+      <c r="D22" t="s">
         <v>478</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>479</v>
       </c>
-      <c r="D22" t="s">
-        <v>480</v>
-      </c>
-      <c r="E22" t="s">
-        <v>481</v>
-      </c>
       <c r="F22" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I22" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J22" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B23" t="s">
+        <v>484</v>
+      </c>
+      <c r="C23" t="s">
+        <v>477</v>
+      </c>
+      <c r="D23" t="s">
+        <v>485</v>
+      </c>
+      <c r="E23" t="s">
+        <v>479</v>
+      </c>
+      <c r="F23" t="s">
+        <v>420</v>
+      </c>
+      <c r="G23" t="s">
         <v>486</v>
-      </c>
-      <c r="C23" t="s">
-        <v>479</v>
-      </c>
-      <c r="D23" t="s">
-        <v>487</v>
-      </c>
-      <c r="E23" t="s">
-        <v>481</v>
-      </c>
-      <c r="F23" t="s">
-        <v>422</v>
-      </c>
-      <c r="G23" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B24" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C24" t="s">
+        <v>477</v>
+      </c>
+      <c r="D24" t="s">
+        <v>485</v>
+      </c>
+      <c r="E24" t="s">
         <v>479</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
+        <v>420</v>
+      </c>
+      <c r="G24" t="s">
         <v>487</v>
-      </c>
-      <c r="E24" t="s">
-        <v>481</v>
-      </c>
-      <c r="F24" t="s">
-        <v>422</v>
-      </c>
-      <c r="G24" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C25" t="s">
+        <v>477</v>
+      </c>
+      <c r="D25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E25" t="s">
         <v>479</v>
       </c>
-      <c r="D25" t="s">
-        <v>487</v>
-      </c>
-      <c r="E25" t="s">
-        <v>481</v>
-      </c>
       <c r="F25" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G25" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C26" t="s">
+        <v>477</v>
+      </c>
+      <c r="D26" t="s">
+        <v>485</v>
+      </c>
+      <c r="E26" t="s">
         <v>479</v>
       </c>
-      <c r="D26" t="s">
-        <v>487</v>
-      </c>
-      <c r="E26" t="s">
-        <v>481</v>
-      </c>
       <c r="F26" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G26" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C27" t="s">
+        <v>477</v>
+      </c>
+      <c r="D27" t="s">
+        <v>485</v>
+      </c>
+      <c r="E27" t="s">
         <v>479</v>
       </c>
-      <c r="D27" t="s">
-        <v>487</v>
-      </c>
-      <c r="E27" t="s">
-        <v>481</v>
-      </c>
       <c r="F27" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G27" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C28" t="s">
+        <v>477</v>
+      </c>
+      <c r="D28" t="s">
+        <v>485</v>
+      </c>
+      <c r="E28" t="s">
         <v>479</v>
       </c>
-      <c r="D28" t="s">
-        <v>487</v>
-      </c>
-      <c r="E28" t="s">
-        <v>481</v>
-      </c>
       <c r="F28" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G28" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C29" t="s">
+        <v>477</v>
+      </c>
+      <c r="D29" t="s">
+        <v>485</v>
+      </c>
+      <c r="E29" t="s">
         <v>479</v>
       </c>
-      <c r="D29" t="s">
-        <v>487</v>
-      </c>
-      <c r="E29" t="s">
-        <v>481</v>
-      </c>
       <c r="F29" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G29" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C30" t="s">
+        <v>477</v>
+      </c>
+      <c r="D30" t="s">
+        <v>485</v>
+      </c>
+      <c r="E30" t="s">
         <v>479</v>
       </c>
-      <c r="D30" t="s">
-        <v>487</v>
-      </c>
-      <c r="E30" t="s">
-        <v>481</v>
-      </c>
       <c r="F30" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I30" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J30" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C31" t="s">
+        <v>477</v>
+      </c>
+      <c r="E31" t="s">
         <v>479</v>
       </c>
-      <c r="E31" t="s">
-        <v>481</v>
-      </c>
       <c r="F31" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G31" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s">
+        <v>494</v>
+      </c>
+      <c r="C32" t="s">
+        <v>477</v>
+      </c>
+      <c r="E32" t="s">
+        <v>479</v>
+      </c>
+      <c r="F32" t="s">
+        <v>420</v>
+      </c>
+      <c r="G32" t="s">
         <v>496</v>
-      </c>
-      <c r="C32" t="s">
-        <v>479</v>
-      </c>
-      <c r="E32" t="s">
-        <v>481</v>
-      </c>
-      <c r="F32" t="s">
-        <v>422</v>
-      </c>
-      <c r="G32" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C33" t="s">
+        <v>477</v>
+      </c>
+      <c r="E33" t="s">
         <v>479</v>
       </c>
-      <c r="E33" t="s">
-        <v>481</v>
-      </c>
       <c r="F33" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G33" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C34" t="s">
+        <v>477</v>
+      </c>
+      <c r="E34" t="s">
         <v>479</v>
       </c>
-      <c r="E34" t="s">
-        <v>481</v>
-      </c>
       <c r="F34" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G34" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E35" t="s">
         <v>479</v>
       </c>
-      <c r="E35" t="s">
-        <v>481</v>
-      </c>
       <c r="F35" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G35" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C36" t="s">
+        <v>477</v>
+      </c>
+      <c r="E36" t="s">
         <v>479</v>
       </c>
-      <c r="E36" t="s">
-        <v>481</v>
-      </c>
       <c r="F36" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G36" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C37" t="s">
+        <v>477</v>
+      </c>
+      <c r="E37" t="s">
         <v>479</v>
       </c>
-      <c r="E37" t="s">
-        <v>481</v>
-      </c>
       <c r="F37" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G37" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C38" t="s">
+        <v>477</v>
+      </c>
+      <c r="E38" t="s">
         <v>479</v>
       </c>
-      <c r="E38" t="s">
-        <v>481</v>
-      </c>
       <c r="F38" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G38" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C39" t="s">
+        <v>477</v>
+      </c>
+      <c r="E39" t="s">
         <v>479</v>
       </c>
-      <c r="E39" t="s">
-        <v>481</v>
-      </c>
       <c r="F39" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I39" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J39" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>504</v>
+      </c>
+      <c r="B40" t="s">
+        <v>505</v>
+      </c>
+      <c r="C40" t="s">
+        <v>477</v>
+      </c>
+      <c r="D40" t="s">
         <v>506</v>
       </c>
-      <c r="B40" t="s">
-        <v>507</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="E40" t="s">
         <v>479</v>
-      </c>
-      <c r="D40" t="s">
-        <v>508</v>
-      </c>
-      <c r="E40" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C41" t="s">
+        <v>477</v>
+      </c>
+      <c r="E41" t="s">
         <v>479</v>
       </c>
-      <c r="E41" t="s">
-        <v>481</v>
-      </c>
       <c r="F41" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G41" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s">
+        <v>507</v>
+      </c>
+      <c r="C42" t="s">
+        <v>477</v>
+      </c>
+      <c r="E42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F42" t="s">
+        <v>420</v>
+      </c>
+      <c r="G42" t="s">
         <v>509</v>
-      </c>
-      <c r="C42" t="s">
-        <v>479</v>
-      </c>
-      <c r="E42" t="s">
-        <v>481</v>
-      </c>
-      <c r="F42" t="s">
-        <v>422</v>
-      </c>
-      <c r="G42" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C43" t="s">
+        <v>477</v>
+      </c>
+      <c r="E43" t="s">
         <v>479</v>
       </c>
-      <c r="E43" t="s">
-        <v>481</v>
-      </c>
       <c r="F43" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G43" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C44" t="s">
+        <v>477</v>
+      </c>
+      <c r="E44" t="s">
         <v>479</v>
       </c>
-      <c r="E44" t="s">
-        <v>481</v>
-      </c>
       <c r="F44" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G44" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C45" t="s">
+        <v>477</v>
+      </c>
+      <c r="E45" t="s">
         <v>479</v>
       </c>
-      <c r="E45" t="s">
-        <v>481</v>
-      </c>
       <c r="F45" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I45" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="J45" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>513</v>
+      </c>
+      <c r="B46" t="s">
+        <v>514</v>
+      </c>
+      <c r="C46" t="s">
+        <v>477</v>
+      </c>
+      <c r="D46" t="s">
         <v>515</v>
       </c>
-      <c r="B46" t="s">
+      <c r="E46" t="s">
+        <v>479</v>
+      </c>
+      <c r="F46" t="s">
+        <v>420</v>
+      </c>
+      <c r="G46" t="s">
         <v>516</v>
-      </c>
-      <c r="C46" t="s">
-        <v>479</v>
-      </c>
-      <c r="D46" t="s">
-        <v>517</v>
-      </c>
-      <c r="E46" t="s">
-        <v>481</v>
-      </c>
-      <c r="F46" t="s">
-        <v>422</v>
-      </c>
-      <c r="G46" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>513</v>
+      </c>
+      <c r="B47" t="s">
+        <v>514</v>
+      </c>
+      <c r="C47" t="s">
+        <v>477</v>
+      </c>
+      <c r="D47" t="s">
         <v>515</v>
       </c>
-      <c r="B47" t="s">
-        <v>516</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="E47" t="s">
         <v>479</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
+        <v>423</v>
+      </c>
+      <c r="I47" t="s">
         <v>517</v>
       </c>
-      <c r="E47" t="s">
-        <v>481</v>
-      </c>
-      <c r="F47" t="s">
-        <v>425</v>
-      </c>
-      <c r="I47" t="s">
-        <v>519</v>
-      </c>
       <c r="J47" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>518</v>
+      </c>
+      <c r="B48" t="s">
+        <v>519</v>
+      </c>
+      <c r="C48" t="s">
+        <v>477</v>
+      </c>
+      <c r="D48" t="s">
         <v>520</v>
       </c>
-      <c r="B48" t="s">
+      <c r="E48" t="s">
+        <v>479</v>
+      </c>
+      <c r="F48" t="s">
+        <v>420</v>
+      </c>
+      <c r="G48" t="s">
         <v>521</v>
-      </c>
-      <c r="C48" t="s">
-        <v>479</v>
-      </c>
-      <c r="D48" t="s">
-        <v>522</v>
-      </c>
-      <c r="E48" t="s">
-        <v>481</v>
-      </c>
-      <c r="F48" t="s">
-        <v>422</v>
-      </c>
-      <c r="G48" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>518</v>
+      </c>
+      <c r="B49" t="s">
+        <v>519</v>
+      </c>
+      <c r="C49" t="s">
+        <v>477</v>
+      </c>
+      <c r="D49" t="s">
         <v>520</v>
       </c>
-      <c r="B49" t="s">
-        <v>521</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="E49" t="s">
         <v>479</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>420</v>
+      </c>
+      <c r="G49" t="s">
         <v>522</v>
-      </c>
-      <c r="E49" t="s">
-        <v>481</v>
-      </c>
-      <c r="F49" t="s">
-        <v>422</v>
-      </c>
-      <c r="G49" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>518</v>
+      </c>
+      <c r="B50" t="s">
+        <v>519</v>
+      </c>
+      <c r="C50" t="s">
+        <v>477</v>
+      </c>
+      <c r="D50" t="s">
         <v>520</v>
       </c>
-      <c r="B50" t="s">
-        <v>521</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="E50" t="s">
         <v>479</v>
       </c>
-      <c r="D50" t="s">
-        <v>522</v>
-      </c>
-      <c r="E50" t="s">
-        <v>481</v>
-      </c>
       <c r="F50" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G50" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>518</v>
+      </c>
+      <c r="B51" t="s">
+        <v>519</v>
+      </c>
+      <c r="C51" t="s">
+        <v>477</v>
+      </c>
+      <c r="D51" t="s">
         <v>520</v>
       </c>
-      <c r="B51" t="s">
-        <v>521</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>479</v>
       </c>
-      <c r="D51" t="s">
-        <v>522</v>
-      </c>
-      <c r="E51" t="s">
-        <v>481</v>
-      </c>
       <c r="F51" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G51" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>518</v>
+      </c>
+      <c r="B52" t="s">
+        <v>519</v>
+      </c>
+      <c r="C52" t="s">
+        <v>477</v>
+      </c>
+      <c r="D52" t="s">
         <v>520</v>
       </c>
-      <c r="B52" t="s">
-        <v>521</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="E52" t="s">
         <v>479</v>
       </c>
-      <c r="D52" t="s">
-        <v>522</v>
-      </c>
-      <c r="E52" t="s">
-        <v>481</v>
-      </c>
       <c r="F52" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I52" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J52" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>526</v>
+      </c>
+      <c r="B53" t="s">
+        <v>527</v>
+      </c>
+      <c r="C53" t="s">
+        <v>477</v>
+      </c>
+      <c r="D53" t="s">
         <v>528</v>
       </c>
-      <c r="B53" t="s">
+      <c r="E53" t="s">
+        <v>479</v>
+      </c>
+      <c r="F53" t="s">
+        <v>420</v>
+      </c>
+      <c r="G53" t="s">
         <v>529</v>
-      </c>
-      <c r="C53" t="s">
-        <v>479</v>
-      </c>
-      <c r="D53" t="s">
-        <v>530</v>
-      </c>
-      <c r="E53" t="s">
-        <v>481</v>
-      </c>
-      <c r="F53" t="s">
-        <v>422</v>
-      </c>
-      <c r="G53" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>526</v>
+      </c>
+      <c r="B54" t="s">
+        <v>527</v>
+      </c>
+      <c r="C54" t="s">
+        <v>477</v>
+      </c>
+      <c r="D54" t="s">
         <v>528</v>
       </c>
-      <c r="B54" t="s">
-        <v>529</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="E54" t="s">
         <v>479</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
+        <v>423</v>
+      </c>
+      <c r="I54" t="s">
         <v>530</v>
       </c>
-      <c r="E54" t="s">
-        <v>481</v>
-      </c>
-      <c r="F54" t="s">
-        <v>425</v>
-      </c>
-      <c r="I54" t="s">
-        <v>532</v>
-      </c>
       <c r="J54" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B55" t="s">
+        <v>531</v>
+      </c>
+      <c r="C55" t="s">
+        <v>477</v>
+      </c>
+      <c r="D55" t="s">
+        <v>532</v>
+      </c>
+      <c r="E55" t="s">
+        <v>479</v>
+      </c>
+      <c r="F55" t="s">
+        <v>420</v>
+      </c>
+      <c r="G55" t="s">
         <v>533</v>
-      </c>
-      <c r="C55" t="s">
-        <v>479</v>
-      </c>
-      <c r="D55" t="s">
-        <v>534</v>
-      </c>
-      <c r="E55" t="s">
-        <v>481</v>
-      </c>
-      <c r="F55" t="s">
-        <v>422</v>
-      </c>
-      <c r="G55" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B56" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C56" t="s">
+        <v>477</v>
+      </c>
+      <c r="D56" t="s">
+        <v>532</v>
+      </c>
+      <c r="E56" t="s">
         <v>479</v>
       </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
+        <v>420</v>
+      </c>
+      <c r="G56" t="s">
         <v>534</v>
-      </c>
-      <c r="E56" t="s">
-        <v>481</v>
-      </c>
-      <c r="F56" t="s">
-        <v>422</v>
-      </c>
-      <c r="G56" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B57" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C57" t="s">
+        <v>477</v>
+      </c>
+      <c r="D57" t="s">
+        <v>532</v>
+      </c>
+      <c r="E57" t="s">
         <v>479</v>
       </c>
-      <c r="D57" t="s">
-        <v>534</v>
-      </c>
-      <c r="E57" t="s">
-        <v>481</v>
-      </c>
       <c r="F57" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G57" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B58" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C58" t="s">
+        <v>477</v>
+      </c>
+      <c r="D58" t="s">
+        <v>532</v>
+      </c>
+      <c r="E58" t="s">
         <v>479</v>
       </c>
-      <c r="D58" t="s">
-        <v>534</v>
-      </c>
-      <c r="E58" t="s">
-        <v>481</v>
-      </c>
       <c r="F58" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I58" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J58" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>537</v>
+      </c>
+      <c r="B59" t="s">
+        <v>538</v>
+      </c>
+      <c r="C59" t="s">
+        <v>477</v>
+      </c>
+      <c r="D59" t="s">
         <v>539</v>
       </c>
-      <c r="B59" t="s">
+      <c r="E59" t="s">
+        <v>479</v>
+      </c>
+      <c r="F59" t="s">
+        <v>420</v>
+      </c>
+      <c r="G59" t="s">
         <v>540</v>
-      </c>
-      <c r="C59" t="s">
-        <v>479</v>
-      </c>
-      <c r="D59" t="s">
-        <v>541</v>
-      </c>
-      <c r="E59" t="s">
-        <v>481</v>
-      </c>
-      <c r="F59" t="s">
-        <v>422</v>
-      </c>
-      <c r="G59" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>537</v>
+      </c>
+      <c r="B60" t="s">
+        <v>538</v>
+      </c>
+      <c r="C60" t="s">
+        <v>477</v>
+      </c>
+      <c r="D60" t="s">
         <v>539</v>
       </c>
-      <c r="B60" t="s">
-        <v>540</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>479</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
+        <v>420</v>
+      </c>
+      <c r="G60" t="s">
         <v>541</v>
-      </c>
-      <c r="E60" t="s">
-        <v>481</v>
-      </c>
-      <c r="F60" t="s">
-        <v>422</v>
-      </c>
-      <c r="G60" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>537</v>
+      </c>
+      <c r="B61" t="s">
+        <v>538</v>
+      </c>
+      <c r="C61" t="s">
+        <v>477</v>
+      </c>
+      <c r="D61" t="s">
         <v>539</v>
       </c>
-      <c r="B61" t="s">
-        <v>540</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="E61" t="s">
         <v>479</v>
       </c>
-      <c r="D61" t="s">
-        <v>541</v>
-      </c>
-      <c r="E61" t="s">
-        <v>481</v>
-      </c>
       <c r="F61" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G61" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>537</v>
+      </c>
+      <c r="B62" t="s">
+        <v>538</v>
+      </c>
+      <c r="C62" t="s">
+        <v>477</v>
+      </c>
+      <c r="D62" t="s">
         <v>539</v>
       </c>
-      <c r="B62" t="s">
-        <v>540</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="E62" t="s">
         <v>479</v>
       </c>
-      <c r="D62" t="s">
-        <v>541</v>
-      </c>
-      <c r="E62" t="s">
-        <v>481</v>
-      </c>
       <c r="F62" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G62" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>537</v>
+      </c>
+      <c r="B63" t="s">
+        <v>538</v>
+      </c>
+      <c r="C63" t="s">
+        <v>477</v>
+      </c>
+      <c r="D63" t="s">
         <v>539</v>
       </c>
-      <c r="B63" t="s">
-        <v>540</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="E63" t="s">
         <v>479</v>
       </c>
-      <c r="D63" t="s">
-        <v>541</v>
-      </c>
-      <c r="E63" t="s">
-        <v>481</v>
-      </c>
       <c r="F63" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>544</v>
+      </c>
+      <c r="B64" t="s">
+        <v>545</v>
+      </c>
+      <c r="C64" t="s">
+        <v>477</v>
+      </c>
+      <c r="D64" t="s">
         <v>546</v>
       </c>
-      <c r="B64" t="s">
+      <c r="E64" t="s">
+        <v>479</v>
+      </c>
+      <c r="F64" t="s">
+        <v>420</v>
+      </c>
+      <c r="G64" t="s">
         <v>547</v>
-      </c>
-      <c r="C64" t="s">
-        <v>479</v>
-      </c>
-      <c r="D64" t="s">
-        <v>548</v>
-      </c>
-      <c r="E64" t="s">
-        <v>481</v>
-      </c>
-      <c r="F64" t="s">
-        <v>422</v>
-      </c>
-      <c r="G64" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>544</v>
+      </c>
+      <c r="B65" t="s">
+        <v>545</v>
+      </c>
+      <c r="C65" t="s">
+        <v>477</v>
+      </c>
+      <c r="D65" t="s">
         <v>546</v>
       </c>
-      <c r="B65" t="s">
-        <v>547</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="E65" t="s">
         <v>479</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>420</v>
+      </c>
+      <c r="G65" t="s">
         <v>548</v>
-      </c>
-      <c r="E65" t="s">
-        <v>481</v>
-      </c>
-      <c r="F65" t="s">
-        <v>422</v>
-      </c>
-      <c r="G65" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>544</v>
+      </c>
+      <c r="B66" t="s">
+        <v>545</v>
+      </c>
+      <c r="C66" t="s">
+        <v>477</v>
+      </c>
+      <c r="D66" t="s">
         <v>546</v>
       </c>
-      <c r="B66" t="s">
-        <v>547</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="E66" t="s">
         <v>479</v>
       </c>
-      <c r="D66" t="s">
-        <v>548</v>
-      </c>
-      <c r="E66" t="s">
-        <v>481</v>
-      </c>
       <c r="F66" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G66" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>544</v>
+      </c>
+      <c r="B67" t="s">
+        <v>545</v>
+      </c>
+      <c r="C67" t="s">
+        <v>477</v>
+      </c>
+      <c r="D67" t="s">
         <v>546</v>
       </c>
-      <c r="B67" t="s">
-        <v>547</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="E67" t="s">
         <v>479</v>
       </c>
-      <c r="D67" t="s">
-        <v>548</v>
-      </c>
-      <c r="E67" t="s">
-        <v>481</v>
-      </c>
       <c r="F67" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G67" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>544</v>
+      </c>
+      <c r="B68" t="s">
+        <v>545</v>
+      </c>
+      <c r="C68" t="s">
+        <v>477</v>
+      </c>
+      <c r="D68" t="s">
         <v>546</v>
       </c>
-      <c r="B68" t="s">
-        <v>547</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="E68" t="s">
         <v>479</v>
       </c>
-      <c r="D68" t="s">
-        <v>548</v>
-      </c>
-      <c r="E68" t="s">
-        <v>481</v>
-      </c>
       <c r="F68" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G68" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>544</v>
+      </c>
+      <c r="B69" t="s">
+        <v>545</v>
+      </c>
+      <c r="C69" t="s">
+        <v>477</v>
+      </c>
+      <c r="D69" t="s">
         <v>546</v>
       </c>
-      <c r="B69" t="s">
-        <v>547</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="E69" t="s">
         <v>479</v>
       </c>
-      <c r="D69" t="s">
-        <v>548</v>
-      </c>
-      <c r="E69" t="s">
-        <v>481</v>
-      </c>
       <c r="F69" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G69" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>544</v>
+      </c>
+      <c r="B70" t="s">
+        <v>545</v>
+      </c>
+      <c r="C70" t="s">
+        <v>477</v>
+      </c>
+      <c r="D70" t="s">
         <v>546</v>
       </c>
-      <c r="B70" t="s">
-        <v>547</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="E70" t="s">
         <v>479</v>
       </c>
-      <c r="D70" t="s">
-        <v>548</v>
-      </c>
-      <c r="E70" t="s">
-        <v>481</v>
-      </c>
       <c r="F70" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I70" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="J70" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B71" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C71" t="s">
+        <v>477</v>
+      </c>
+      <c r="E71" t="s">
         <v>479</v>
       </c>
-      <c r="E71" t="s">
-        <v>481</v>
-      </c>
       <c r="F71" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I71" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J71" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -7531,25 +8553,25 @@
         <v>45652</v>
       </c>
       <c r="B72" t="s">
+        <v>556</v>
+      </c>
+      <c r="C72" t="s">
+        <v>477</v>
+      </c>
+      <c r="D72" t="s">
+        <v>557</v>
+      </c>
+      <c r="E72" t="s">
         <v>558</v>
       </c>
-      <c r="C72" t="s">
-        <v>479</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="F72" t="s">
         <v>559</v>
       </c>
-      <c r="E72" t="s">
+      <c r="G72" t="s">
         <v>560</v>
       </c>
-      <c r="F72" t="s">
+      <c r="H72" t="s">
         <v>561</v>
-      </c>
-      <c r="G72" t="s">
-        <v>562</v>
-      </c>
-      <c r="H72" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -7557,25 +8579,25 @@
         <v>45652</v>
       </c>
       <c r="B73" t="s">
+        <v>556</v>
+      </c>
+      <c r="C73" t="s">
+        <v>477</v>
+      </c>
+      <c r="D73" t="s">
+        <v>557</v>
+      </c>
+      <c r="E73" t="s">
         <v>558</v>
       </c>
-      <c r="C73" t="s">
-        <v>479</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="F73" t="s">
         <v>559</v>
       </c>
-      <c r="E73" t="s">
-        <v>560</v>
-      </c>
-      <c r="F73" t="s">
-        <v>561</v>
-      </c>
       <c r="G73" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H73" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -7583,25 +8605,25 @@
         <v>45652</v>
       </c>
       <c r="B74" t="s">
+        <v>556</v>
+      </c>
+      <c r="C74" t="s">
+        <v>477</v>
+      </c>
+      <c r="D74" t="s">
+        <v>557</v>
+      </c>
+      <c r="E74" t="s">
         <v>558</v>
       </c>
-      <c r="C74" t="s">
-        <v>479</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="F74" t="s">
         <v>559</v>
       </c>
-      <c r="E74" t="s">
-        <v>560</v>
-      </c>
-      <c r="F74" t="s">
-        <v>561</v>
-      </c>
       <c r="G74" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H74" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -7609,25 +8631,25 @@
         <v>45652</v>
       </c>
       <c r="B75" t="s">
+        <v>556</v>
+      </c>
+      <c r="C75" t="s">
+        <v>477</v>
+      </c>
+      <c r="D75" t="s">
+        <v>557</v>
+      </c>
+      <c r="E75" t="s">
         <v>558</v>
       </c>
-      <c r="C75" t="s">
-        <v>479</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="F75" t="s">
         <v>559</v>
       </c>
-      <c r="E75" t="s">
-        <v>560</v>
-      </c>
-      <c r="F75" t="s">
-        <v>561</v>
-      </c>
       <c r="G75" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H75" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -7635,22 +8657,22 @@
         <v>45301</v>
       </c>
       <c r="B76" t="s">
+        <v>568</v>
+      </c>
+      <c r="C76" t="s">
+        <v>477</v>
+      </c>
+      <c r="D76" t="s">
+        <v>569</v>
+      </c>
+      <c r="E76" t="s">
+        <v>479</v>
+      </c>
+      <c r="F76" t="s">
+        <v>420</v>
+      </c>
+      <c r="G76" t="s">
         <v>570</v>
-      </c>
-      <c r="C76" t="s">
-        <v>479</v>
-      </c>
-      <c r="D76" t="s">
-        <v>571</v>
-      </c>
-      <c r="E76" t="s">
-        <v>481</v>
-      </c>
-      <c r="F76" t="s">
-        <v>422</v>
-      </c>
-      <c r="G76" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -7658,22 +8680,22 @@
         <v>45301</v>
       </c>
       <c r="B77" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C77" t="s">
+        <v>477</v>
+      </c>
+      <c r="D77" t="s">
+        <v>569</v>
+      </c>
+      <c r="E77" t="s">
         <v>479</v>
       </c>
-      <c r="D77" t="s">
+      <c r="F77" t="s">
+        <v>420</v>
+      </c>
+      <c r="G77" t="s">
         <v>571</v>
-      </c>
-      <c r="E77" t="s">
-        <v>481</v>
-      </c>
-      <c r="F77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G77" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -7681,25 +8703,25 @@
         <v>45301</v>
       </c>
       <c r="B78" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C78" t="s">
+        <v>477</v>
+      </c>
+      <c r="D78" t="s">
+        <v>569</v>
+      </c>
+      <c r="E78" t="s">
         <v>479</v>
       </c>
-      <c r="D78" t="s">
-        <v>571</v>
-      </c>
-      <c r="E78" t="s">
-        <v>481</v>
-      </c>
       <c r="F78" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I78" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J78" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -7707,25 +8729,25 @@
         <v>45290</v>
       </c>
       <c r="B79" t="s">
+        <v>573</v>
+      </c>
+      <c r="C79" t="s">
+        <v>418</v>
+      </c>
+      <c r="D79" t="s">
+        <v>574</v>
+      </c>
+      <c r="E79" t="s">
+        <v>436</v>
+      </c>
+      <c r="F79" t="s">
+        <v>420</v>
+      </c>
+      <c r="G79" t="s">
         <v>575</v>
       </c>
-      <c r="C79" t="s">
-        <v>420</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="H79" t="s">
         <v>576</v>
-      </c>
-      <c r="E79" t="s">
-        <v>438</v>
-      </c>
-      <c r="F79" t="s">
-        <v>422</v>
-      </c>
-      <c r="G79" t="s">
-        <v>577</v>
-      </c>
-      <c r="H79" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -7733,25 +8755,25 @@
         <v>45290</v>
       </c>
       <c r="B80" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C80" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D80" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E80" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F80" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I80" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J80" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -7759,25 +8781,25 @@
         <v>45298</v>
       </c>
       <c r="B81" t="s">
+        <v>579</v>
+      </c>
+      <c r="C81" t="s">
+        <v>418</v>
+      </c>
+      <c r="D81" t="s">
+        <v>580</v>
+      </c>
+      <c r="E81" t="s">
+        <v>436</v>
+      </c>
+      <c r="F81" t="s">
+        <v>420</v>
+      </c>
+      <c r="G81" t="s">
         <v>581</v>
       </c>
-      <c r="C81" t="s">
-        <v>420</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="H81" t="s">
         <v>582</v>
-      </c>
-      <c r="E81" t="s">
-        <v>438</v>
-      </c>
-      <c r="F81" t="s">
-        <v>422</v>
-      </c>
-      <c r="G81" t="s">
-        <v>583</v>
-      </c>
-      <c r="H81" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -7785,25 +8807,25 @@
         <v>45298</v>
       </c>
       <c r="B82" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C82" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D82" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E82" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F82" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I82" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J82" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -7811,25 +8833,25 @@
         <v>45406</v>
       </c>
       <c r="B83" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C83" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D83" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G83" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="H83" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -7837,25 +8859,25 @@
         <v>45406</v>
       </c>
       <c r="B84" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C84" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D84" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G84" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H84" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -7863,25 +8885,25 @@
         <v>45406</v>
       </c>
       <c r="B85" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C85" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D85" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I85" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J85" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -7889,25 +8911,25 @@
         <v>45451</v>
       </c>
       <c r="B86" t="s">
+        <v>592</v>
+      </c>
+      <c r="C86" t="s">
+        <v>418</v>
+      </c>
+      <c r="D86" t="s">
+        <v>593</v>
+      </c>
+      <c r="E86" t="s">
+        <v>419</v>
+      </c>
+      <c r="F86" t="s">
+        <v>420</v>
+      </c>
+      <c r="G86" t="s">
         <v>594</v>
       </c>
-      <c r="C86" t="s">
-        <v>420</v>
-      </c>
-      <c r="D86" t="s">
-        <v>595</v>
-      </c>
-      <c r="E86" t="s">
-        <v>421</v>
-      </c>
-      <c r="F86" t="s">
-        <v>422</v>
-      </c>
-      <c r="G86" t="s">
-        <v>596</v>
-      </c>
       <c r="H86" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -7915,25 +8937,25 @@
         <v>45451</v>
       </c>
       <c r="B87" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C87" t="s">
+        <v>418</v>
+      </c>
+      <c r="D87" t="s">
+        <v>593</v>
+      </c>
+      <c r="E87" t="s">
+        <v>419</v>
+      </c>
+      <c r="F87" t="s">
         <v>420</v>
       </c>
-      <c r="D87" t="s">
+      <c r="G87" t="s">
         <v>595</v>
       </c>
-      <c r="E87" t="s">
-        <v>421</v>
-      </c>
-      <c r="F87" t="s">
-        <v>422</v>
-      </c>
-      <c r="G87" t="s">
-        <v>597</v>
-      </c>
       <c r="H87" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -7941,25 +8963,25 @@
         <v>45451</v>
       </c>
       <c r="B88" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C88" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D88" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E88" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F88" t="s">
+        <v>423</v>
+      </c>
+      <c r="I88" t="s">
+        <v>597</v>
+      </c>
+      <c r="J88" t="s">
         <v>425</v>
-      </c>
-      <c r="I88" t="s">
-        <v>599</v>
-      </c>
-      <c r="J88" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -7967,25 +8989,25 @@
         <v>45480</v>
       </c>
       <c r="B89" t="s">
+        <v>598</v>
+      </c>
+      <c r="C89" t="s">
+        <v>418</v>
+      </c>
+      <c r="D89" t="s">
+        <v>599</v>
+      </c>
+      <c r="E89" t="s">
+        <v>419</v>
+      </c>
+      <c r="F89" t="s">
+        <v>420</v>
+      </c>
+      <c r="G89" t="s">
         <v>600</v>
       </c>
-      <c r="C89" t="s">
-        <v>420</v>
-      </c>
-      <c r="D89" t="s">
-        <v>601</v>
-      </c>
-      <c r="E89" t="s">
-        <v>421</v>
-      </c>
-      <c r="F89" t="s">
-        <v>422</v>
-      </c>
-      <c r="G89" t="s">
-        <v>602</v>
-      </c>
       <c r="H89" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -7993,25 +9015,25 @@
         <v>45578</v>
       </c>
       <c r="B90" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C90" t="s">
+        <v>418</v>
+      </c>
+      <c r="D90" t="s">
+        <v>601</v>
+      </c>
+      <c r="E90" t="s">
+        <v>419</v>
+      </c>
+      <c r="F90" t="s">
         <v>420</v>
       </c>
-      <c r="D90" t="s">
-        <v>603</v>
-      </c>
-      <c r="E90" t="s">
-        <v>421</v>
-      </c>
-      <c r="F90" t="s">
-        <v>422</v>
-      </c>
       <c r="G90" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H90" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -8019,25 +9041,25 @@
         <v>45578</v>
       </c>
       <c r="B91" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C91" t="s">
+        <v>418</v>
+      </c>
+      <c r="D91" t="s">
+        <v>601</v>
+      </c>
+      <c r="E91" t="s">
+        <v>419</v>
+      </c>
+      <c r="F91" t="s">
         <v>420</v>
       </c>
-      <c r="D91" t="s">
+      <c r="G91" t="s">
         <v>603</v>
       </c>
-      <c r="E91" t="s">
-        <v>421</v>
-      </c>
-      <c r="F91" t="s">
-        <v>422</v>
-      </c>
-      <c r="G91" t="s">
-        <v>605</v>
-      </c>
       <c r="H91" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -8045,25 +9067,25 @@
         <v>45578</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C92" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D92" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E92" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F92" t="s">
+        <v>423</v>
+      </c>
+      <c r="I92" t="s">
+        <v>605</v>
+      </c>
+      <c r="J92" t="s">
         <v>425</v>
-      </c>
-      <c r="I92" t="s">
-        <v>607</v>
-      </c>
-      <c r="J92" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -8071,22 +9093,22 @@
         <v>45360</v>
       </c>
       <c r="B93" t="s">
+        <v>606</v>
+      </c>
+      <c r="C93" t="s">
+        <v>418</v>
+      </c>
+      <c r="E93" t="s">
+        <v>607</v>
+      </c>
+      <c r="F93" t="s">
+        <v>420</v>
+      </c>
+      <c r="G93" t="s">
         <v>608</v>
       </c>
-      <c r="C93" t="s">
-        <v>420</v>
-      </c>
-      <c r="E93" t="s">
+      <c r="H93" t="s">
         <v>609</v>
-      </c>
-      <c r="F93" t="s">
-        <v>422</v>
-      </c>
-      <c r="G93" t="s">
-        <v>610</v>
-      </c>
-      <c r="H93" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -8094,28 +9116,28 @@
         <v>45486</v>
       </c>
       <c r="B94" t="s">
+        <v>610</v>
+      </c>
+      <c r="C94" t="s">
+        <v>418</v>
+      </c>
+      <c r="D94" t="s">
+        <v>611</v>
+      </c>
+      <c r="E94" t="s">
+        <v>607</v>
+      </c>
+      <c r="F94" t="s">
+        <v>420</v>
+      </c>
+      <c r="G94" t="s">
         <v>612</v>
       </c>
-      <c r="C94" t="s">
-        <v>420</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="H94" t="s">
+        <v>402</v>
+      </c>
+      <c r="K94" t="s">
         <v>613</v>
-      </c>
-      <c r="E94" t="s">
-        <v>609</v>
-      </c>
-      <c r="F94" t="s">
-        <v>422</v>
-      </c>
-      <c r="G94" t="s">
-        <v>614</v>
-      </c>
-      <c r="H94" t="s">
-        <v>404</v>
-      </c>
-      <c r="K94" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -8123,28 +9145,28 @@
         <v>45486</v>
       </c>
       <c r="B95" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C95" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D95" t="s">
+        <v>611</v>
+      </c>
+      <c r="E95" t="s">
+        <v>607</v>
+      </c>
+      <c r="F95" t="s">
+        <v>423</v>
+      </c>
+      <c r="I95" t="s">
+        <v>614</v>
+      </c>
+      <c r="J95" t="s">
+        <v>615</v>
+      </c>
+      <c r="K95" t="s">
         <v>613</v>
-      </c>
-      <c r="E95" t="s">
-        <v>609</v>
-      </c>
-      <c r="F95" t="s">
-        <v>425</v>
-      </c>
-      <c r="I95" t="s">
-        <v>616</v>
-      </c>
-      <c r="J95" t="s">
-        <v>617</v>
-      </c>
-      <c r="K95" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -8152,19 +9174,19 @@
         <v>45487</v>
       </c>
       <c r="B96" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C96" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D96" t="s">
+        <v>611</v>
+      </c>
+      <c r="E96" t="s">
+        <v>607</v>
+      </c>
+      <c r="K96" t="s">
         <v>613</v>
-      </c>
-      <c r="E96" t="s">
-        <v>609</v>
-      </c>
-      <c r="K96" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -8172,25 +9194,25 @@
         <v>45534</v>
       </c>
       <c r="B97" t="s">
+        <v>616</v>
+      </c>
+      <c r="C97" t="s">
+        <v>418</v>
+      </c>
+      <c r="D97" t="s">
+        <v>617</v>
+      </c>
+      <c r="E97" t="s">
+        <v>607</v>
+      </c>
+      <c r="F97" t="s">
+        <v>420</v>
+      </c>
+      <c r="G97" t="s">
         <v>618</v>
       </c>
-      <c r="C97" t="s">
-        <v>420</v>
-      </c>
-      <c r="D97" t="s">
-        <v>619</v>
-      </c>
-      <c r="E97" t="s">
-        <v>609</v>
-      </c>
-      <c r="F97" t="s">
-        <v>422</v>
-      </c>
-      <c r="G97" t="s">
-        <v>620</v>
-      </c>
       <c r="H97" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -8198,25 +9220,25 @@
         <v>45534</v>
       </c>
       <c r="B98" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C98" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D98" t="s">
+        <v>617</v>
+      </c>
+      <c r="E98" t="s">
+        <v>607</v>
+      </c>
+      <c r="F98" t="s">
+        <v>423</v>
+      </c>
+      <c r="I98" t="s">
         <v>619</v>
       </c>
-      <c r="E98" t="s">
-        <v>609</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="J98" t="s">
         <v>425</v>
-      </c>
-      <c r="I98" t="s">
-        <v>621</v>
-      </c>
-      <c r="J98" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -8224,25 +9246,25 @@
         <v>45186</v>
       </c>
       <c r="B99" t="s">
+        <v>620</v>
+      </c>
+      <c r="C99" t="s">
+        <v>418</v>
+      </c>
+      <c r="D99" t="s">
+        <v>621</v>
+      </c>
+      <c r="E99" t="s">
         <v>622</v>
       </c>
-      <c r="C99" t="s">
+      <c r="F99" t="s">
         <v>420</v>
       </c>
-      <c r="D99" t="s">
+      <c r="G99" t="s">
         <v>623</v>
       </c>
-      <c r="E99" t="s">
+      <c r="H99" t="s">
         <v>624</v>
-      </c>
-      <c r="F99" t="s">
-        <v>422</v>
-      </c>
-      <c r="G99" t="s">
-        <v>625</v>
-      </c>
-      <c r="H99" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -8250,25 +9272,25 @@
         <v>45186</v>
       </c>
       <c r="B100" t="s">
+        <v>620</v>
+      </c>
+      <c r="C100" t="s">
+        <v>418</v>
+      </c>
+      <c r="D100" t="s">
+        <v>621</v>
+      </c>
+      <c r="E100" t="s">
         <v>622</v>
       </c>
-      <c r="C100" t="s">
-        <v>420</v>
-      </c>
-      <c r="D100" t="s">
-        <v>623</v>
-      </c>
-      <c r="E100" t="s">
-        <v>624</v>
-      </c>
       <c r="F100" t="s">
+        <v>423</v>
+      </c>
+      <c r="I100" t="s">
+        <v>625</v>
+      </c>
+      <c r="J100" t="s">
         <v>425</v>
-      </c>
-      <c r="I100" t="s">
-        <v>627</v>
-      </c>
-      <c r="J100" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -8276,25 +9298,25 @@
         <v>45389</v>
       </c>
       <c r="B101" t="s">
+        <v>626</v>
+      </c>
+      <c r="C101" t="s">
+        <v>418</v>
+      </c>
+      <c r="D101" t="s">
+        <v>627</v>
+      </c>
+      <c r="E101" t="s">
+        <v>436</v>
+      </c>
+      <c r="F101" t="s">
+        <v>420</v>
+      </c>
+      <c r="G101" t="s">
         <v>628</v>
       </c>
-      <c r="C101" t="s">
-        <v>420</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="H101" t="s">
         <v>629</v>
-      </c>
-      <c r="E101" t="s">
-        <v>438</v>
-      </c>
-      <c r="F101" t="s">
-        <v>422</v>
-      </c>
-      <c r="G101" t="s">
-        <v>630</v>
-      </c>
-      <c r="H101" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -8302,25 +9324,25 @@
         <v>45389</v>
       </c>
       <c r="B102" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C102" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D102" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E102" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F102" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I102" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="J102" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -8328,25 +9350,25 @@
         <v>45430</v>
       </c>
       <c r="B103" t="s">
+        <v>632</v>
+      </c>
+      <c r="C103" t="s">
+        <v>418</v>
+      </c>
+      <c r="D103" t="s">
+        <v>633</v>
+      </c>
+      <c r="E103" t="s">
+        <v>436</v>
+      </c>
+      <c r="F103" t="s">
+        <v>420</v>
+      </c>
+      <c r="G103" t="s">
         <v>634</v>
       </c>
-      <c r="C103" t="s">
-        <v>420</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="H103" t="s">
         <v>635</v>
-      </c>
-      <c r="E103" t="s">
-        <v>438</v>
-      </c>
-      <c r="F103" t="s">
-        <v>422</v>
-      </c>
-      <c r="G103" t="s">
-        <v>636</v>
-      </c>
-      <c r="H103" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -8354,25 +9376,25 @@
         <v>45430</v>
       </c>
       <c r="B104" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C104" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D104" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E104" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F104" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I104" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="J104" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -8380,25 +9402,25 @@
         <v>45458</v>
       </c>
       <c r="B105" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C105" t="s">
+        <v>418</v>
+      </c>
+      <c r="D105" t="s">
+        <v>639</v>
+      </c>
+      <c r="E105" t="s">
+        <v>436</v>
+      </c>
+      <c r="F105" t="s">
         <v>420</v>
-      </c>
-      <c r="D105" t="s">
-        <v>641</v>
-      </c>
-      <c r="E105" t="s">
-        <v>438</v>
-      </c>
-      <c r="F105" t="s">
-        <v>422</v>
       </c>
       <c r="G105" t="s">
         <v>34</v>
       </c>
       <c r="H105" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -8406,25 +9428,25 @@
         <v>45458</v>
       </c>
       <c r="B106" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C106" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D106" t="s">
+        <v>639</v>
+      </c>
+      <c r="E106" t="s">
+        <v>436</v>
+      </c>
+      <c r="F106" t="s">
+        <v>423</v>
+      </c>
+      <c r="I106" t="s">
         <v>641</v>
       </c>
-      <c r="E106" t="s">
-        <v>438</v>
-      </c>
-      <c r="F106" t="s">
-        <v>425</v>
-      </c>
-      <c r="I106" t="s">
-        <v>643</v>
-      </c>
       <c r="J106" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -8432,25 +9454,25 @@
         <v>45481</v>
       </c>
       <c r="B107" t="s">
+        <v>643</v>
+      </c>
+      <c r="C107" t="s">
+        <v>418</v>
+      </c>
+      <c r="D107" t="s">
+        <v>644</v>
+      </c>
+      <c r="E107" t="s">
+        <v>436</v>
+      </c>
+      <c r="F107" t="s">
+        <v>420</v>
+      </c>
+      <c r="G107" t="s">
         <v>645</v>
       </c>
-      <c r="C107" t="s">
-        <v>420</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="H107" t="s">
         <v>646</v>
-      </c>
-      <c r="E107" t="s">
-        <v>438</v>
-      </c>
-      <c r="F107" t="s">
-        <v>422</v>
-      </c>
-      <c r="G107" t="s">
-        <v>647</v>
-      </c>
-      <c r="H107" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -8458,25 +9480,25 @@
         <v>45481</v>
       </c>
       <c r="B108" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C108" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D108" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E108" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F108" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I108" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="J108" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -8484,25 +9506,25 @@
         <v>45534</v>
       </c>
       <c r="B109" t="s">
+        <v>649</v>
+      </c>
+      <c r="C109" t="s">
+        <v>418</v>
+      </c>
+      <c r="D109" t="s">
+        <v>650</v>
+      </c>
+      <c r="E109" t="s">
+        <v>436</v>
+      </c>
+      <c r="F109" t="s">
+        <v>420</v>
+      </c>
+      <c r="G109" t="s">
         <v>651</v>
       </c>
-      <c r="C109" t="s">
-        <v>420</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="H109" t="s">
         <v>652</v>
-      </c>
-      <c r="E109" t="s">
-        <v>438</v>
-      </c>
-      <c r="F109" t="s">
-        <v>422</v>
-      </c>
-      <c r="G109" t="s">
-        <v>653</v>
-      </c>
-      <c r="H109" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -8510,25 +9532,25 @@
         <v>45534</v>
       </c>
       <c r="B110" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C110" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D110" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E110" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F110" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I110" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="J110" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -8536,25 +9558,25 @@
         <v>45567</v>
       </c>
       <c r="B111" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C111" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D111" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
       </c>
       <c r="F111" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G111" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H111" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -8562,25 +9584,25 @@
         <v>45567</v>
       </c>
       <c r="B112" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C112" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D112" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
       </c>
       <c r="F112" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G112" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H112" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -8588,25 +9610,25 @@
         <v>45567</v>
       </c>
       <c r="B113" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C113" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D113" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
       </c>
       <c r="F113" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G113" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H113" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -8614,25 +9636,25 @@
         <v>45567</v>
       </c>
       <c r="B114" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C114" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D114" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
       </c>
       <c r="F114" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G114" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H114" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -8640,25 +9662,25 @@
         <v>45567</v>
       </c>
       <c r="B115" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C115" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D115" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
       </c>
       <c r="F115" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I115" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J115" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -8666,25 +9688,25 @@
         <v>45483</v>
       </c>
       <c r="B116" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C116" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D116" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
       </c>
       <c r="F116" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G116" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H116" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -8692,25 +9714,25 @@
         <v>45483</v>
       </c>
       <c r="B117" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C117" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D117" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
       </c>
       <c r="F117" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G117" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H117" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -8718,25 +9740,25 @@
         <v>45483</v>
       </c>
       <c r="B118" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C118" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D118" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
       </c>
       <c r="F118" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I118" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="J118" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -8744,25 +9766,25 @@
         <v>45640</v>
       </c>
       <c r="B119" t="s">
+        <v>675</v>
+      </c>
+      <c r="C119" t="s">
+        <v>418</v>
+      </c>
+      <c r="D119" t="s">
+        <v>676</v>
+      </c>
+      <c r="E119" t="s">
+        <v>622</v>
+      </c>
+      <c r="F119" t="s">
+        <v>420</v>
+      </c>
+      <c r="G119" t="s">
         <v>677</v>
       </c>
-      <c r="C119" t="s">
-        <v>420</v>
-      </c>
-      <c r="D119" t="s">
-        <v>678</v>
-      </c>
-      <c r="E119" t="s">
-        <v>624</v>
-      </c>
-      <c r="F119" t="s">
-        <v>422</v>
-      </c>
-      <c r="G119" t="s">
-        <v>679</v>
-      </c>
       <c r="H119" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -8770,25 +9792,25 @@
         <v>45640</v>
       </c>
       <c r="B120" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C120" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D120" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E120" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F120" t="s">
+        <v>423</v>
+      </c>
+      <c r="I120" t="s">
+        <v>619</v>
+      </c>
+      <c r="J120" t="s">
         <v>425</v>
-      </c>
-      <c r="I120" t="s">
-        <v>621</v>
-      </c>
-      <c r="J120" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -8796,25 +9818,25 @@
         <v>45641</v>
       </c>
       <c r="B121" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C121" t="s">
+        <v>418</v>
+      </c>
+      <c r="D121" t="s">
+        <v>678</v>
+      </c>
+      <c r="E121" t="s">
+        <v>419</v>
+      </c>
+      <c r="F121" t="s">
         <v>420</v>
       </c>
-      <c r="D121" t="s">
-        <v>680</v>
-      </c>
-      <c r="E121" t="s">
-        <v>421</v>
-      </c>
-      <c r="F121" t="s">
-        <v>422</v>
-      </c>
       <c r="G121" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H121" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -8822,25 +9844,25 @@
         <v>45641</v>
       </c>
       <c r="B122" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C122" t="s">
+        <v>418</v>
+      </c>
+      <c r="D122" t="s">
+        <v>678</v>
+      </c>
+      <c r="E122" t="s">
+        <v>419</v>
+      </c>
+      <c r="F122" t="s">
         <v>420</v>
       </c>
-      <c r="D122" t="s">
+      <c r="G122" t="s">
         <v>680</v>
       </c>
-      <c r="E122" t="s">
-        <v>421</v>
-      </c>
-      <c r="F122" t="s">
-        <v>422</v>
-      </c>
-      <c r="G122" t="s">
-        <v>682</v>
-      </c>
       <c r="H122" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8848,25 +9870,25 @@
         <v>45641</v>
       </c>
       <c r="B123" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C123" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D123" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E123" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F123" t="s">
+        <v>423</v>
+      </c>
+      <c r="I123" t="s">
+        <v>682</v>
+      </c>
+      <c r="J123" t="s">
         <v>425</v>
-      </c>
-      <c r="I123" t="s">
-        <v>684</v>
-      </c>
-      <c r="J123" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -8874,22 +9896,22 @@
         <v>45619</v>
       </c>
       <c r="B124" t="s">
+        <v>683</v>
+      </c>
+      <c r="C124" t="s">
+        <v>418</v>
+      </c>
+      <c r="E124" t="s">
+        <v>607</v>
+      </c>
+      <c r="F124" t="s">
+        <v>420</v>
+      </c>
+      <c r="G124" t="s">
+        <v>684</v>
+      </c>
+      <c r="H124" t="s">
         <v>685</v>
-      </c>
-      <c r="C124" t="s">
-        <v>420</v>
-      </c>
-      <c r="E124" t="s">
-        <v>609</v>
-      </c>
-      <c r="F124" t="s">
-        <v>422</v>
-      </c>
-      <c r="G124" t="s">
-        <v>686</v>
-      </c>
-      <c r="H124" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -8897,22 +9919,22 @@
         <v>45619</v>
       </c>
       <c r="B125" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C125" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E125" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F125" t="s">
+        <v>423</v>
+      </c>
+      <c r="I125" t="s">
+        <v>619</v>
+      </c>
+      <c r="J125" t="s">
         <v>425</v>
-      </c>
-      <c r="I125" t="s">
-        <v>621</v>
-      </c>
-      <c r="J125" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -8920,25 +9942,25 @@
         <v>45627</v>
       </c>
       <c r="B126" t="s">
+        <v>686</v>
+      </c>
+      <c r="C126" t="s">
+        <v>418</v>
+      </c>
+      <c r="D126" t="s">
+        <v>687</v>
+      </c>
+      <c r="E126" t="s">
         <v>688</v>
       </c>
-      <c r="C126" t="s">
+      <c r="F126" t="s">
         <v>420</v>
       </c>
-      <c r="D126" t="s">
+      <c r="G126" t="s">
         <v>689</v>
       </c>
-      <c r="E126" t="s">
+      <c r="H126" t="s">
         <v>690</v>
-      </c>
-      <c r="F126" t="s">
-        <v>422</v>
-      </c>
-      <c r="G126" t="s">
-        <v>691</v>
-      </c>
-      <c r="H126" t="s">
-        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153B4516-B678-428E-8048-1D88C410FDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="announcements" sheetId="1" r:id="rId1"/>
@@ -3520,7 +3520,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -3677,7 +3677,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>

--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yumin\web\MujicaTimeLineWeb\_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F5335E-E849-495A-AACA-0868230B3ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="announcements" sheetId="1" r:id="rId1"/>
@@ -21,30 +22,18 @@
     <sheet name="backstage" sheetId="7" r:id="rId7"/>
     <sheet name="gallery_images" sheetId="8" r:id="rId8"/>
     <sheet name="timeline" sheetId="9" r:id="rId9"/>
+    <sheet name="interview" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">song_live_history!$A$1:$F$280</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">timeline!$A$1:$K$126</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2873" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2885" uniqueCount="939">
   <si>
     <t>date</t>
   </si>
@@ -2967,19 +2956,45 @@
   <si>
     <t>动画 Logo</t>
   </si>
+  <si>
+    <t>interviewee</t>
+  </si>
+  <si>
+    <t>md_path</t>
+  </si>
+  <si>
+    <t>../images/弄和藤都子2.webp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤都子 x 高尾奏音</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦限大对谈采访连载「ゆめみたの WA ！」 第2回</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>mc/弄和藤都子.md</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.26</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.LIVE logo样式厕所 2.公告样式变更 3.interview开放&amp;内容测试</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3005,7 +3020,7 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -3024,340 +3039,33 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="initial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3365,265 +3073,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3633,62 +3102,20 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3973,17 +3400,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="117.181818181818" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="117.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4063,32 +3490,94 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="13" t="s">
+        <v>937</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>938</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>931</v>
+      </c>
+      <c r="D1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E1" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="13" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>934</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>935</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>936</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="29.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="31.0909090909091" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
+    <col min="1" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="31.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
     <col min="5" max="5" width="20" style="10" customWidth="1"/>
-    <col min="6" max="6" width="23.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="5.27272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="38.3636363636364" customWidth="1"/>
-    <col min="10" max="10" width="35.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="55.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="51.3636363636364" customWidth="1"/>
-    <col min="13" max="14" width="50.6363636363636" customWidth="1"/>
-    <col min="15" max="15" width="51.3636363636364" customWidth="1"/>
-    <col min="16" max="16" width="21.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" customWidth="1"/>
+    <col min="7" max="7" width="5.26953125" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" customWidth="1"/>
+    <col min="9" max="9" width="38.36328125" customWidth="1"/>
+    <col min="10" max="10" width="35.1796875" customWidth="1"/>
+    <col min="11" max="11" width="55.6328125" customWidth="1"/>
+    <col min="12" max="12" width="51.36328125" customWidth="1"/>
+    <col min="13" max="14" width="50.6328125" customWidth="1"/>
+    <col min="15" max="15" width="51.36328125" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4391,7 +3880,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:16">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -4829,7 +4318,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" ht="14.5" customHeight="1">
       <c r="A16" t="s">
         <v>155</v>
       </c>
@@ -4917,7 +4406,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>168</v>
       </c>
@@ -4962,27 +4451,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L12" r:id="rId1" display="https://www.bilibili.com/video/BV1MP411h759"/>
-    <hyperlink ref="L13" r:id="rId2" display="https://www.bilibili.com/video/BV1Xg4y1k7GH"/>
-    <hyperlink ref="L14" r:id="rId3" display="https://www.bilibili.com/video/BV1Ai4y167MU"/>
-    <hyperlink ref="L17" r:id="rId4" display="https://www.bilibili.com/video/BV1Cz421e79N"/>
+    <hyperlink ref="L12" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="L14" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="L17" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D193"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="32.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="67.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="67.54296875" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5091,7 +4579,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:4">
+    <row r="9" spans="1:4" ht="13.5" customHeight="1">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -5301,7 +4789,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:4">
+    <row r="24" spans="1:4" ht="18" customHeight="1">
       <c r="A24" t="s">
         <v>123</v>
       </c>
@@ -5315,7 +4803,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:4">
+    <row r="25" spans="1:4" ht="18" customHeight="1">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -5431,7 +4919,7 @@
       </c>
       <c r="C34" s="9"/>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" ht="15" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>168</v>
       </c>
@@ -5912,37 +5400,37 @@
       <c r="C193" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="C16" r:id="rId2" display="https://www.animatetimes.com/news/details.php?id=1711341102&amp;p=2"/>
-    <hyperlink ref="C17" r:id="rId3" display="https://www.oricon.co.jp/news/2324024/full/"/>
-    <hyperlink ref="C18" r:id="rId4" display="https://www.lisani.jp/0000271996/4/?show_more=1"/>
-    <hyperlink ref="C20" r:id="rId3" display="https://www.oricon.co.jp/news/2324024/full/"/>
-    <hyperlink ref="C22" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="B25" r:id="rId5" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n&#10;佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n&#10;高尾：就像剑一样呢。 \n&#10;佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n&#10;高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n&#10;佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n&#10;——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n&#10;佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n&#10;——也是一首很容易入耳的歌呢。\n&#10;高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n&#10;佐佐木： 谢谢——！"/>
-    <hyperlink ref="C25" r:id="rId5" display="https://www.animatetimes.com/news/details.php?id=1711342991&amp;p=2"/>
-    <hyperlink ref="C26" r:id="rId3" display="https://www.oricon.co.jp/news/2324024/full/"/>
-    <hyperlink ref="C27" r:id="rId6" display="https://www.lisani.jp/0000256138/?show_more=1"/>
-    <hyperlink ref="C28" r:id="rId7" display="https://www.animatetimes.com/news/details.php?id=1711342991"/>
-    <hyperlink ref="C29" r:id="rId3" display="https://www.oricon.co.jp/news/2324024/full/"/>
-    <hyperlink ref="C31" r:id="rId8" display="https://natalie.mu/music/pp/avemujica01/page/2"/>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="C16" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="C17" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="C18" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="C20" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="C22" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="B25" r:id="rId7" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n_x000a_佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n_x000a_高尾：就像剑一样呢。 \n_x000a_佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n_x000a_高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n_x000a_佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n_x000a_——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n_x000a_佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n_x000a_——也是一首很容易入耳的歌呢。\n_x000a_高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n_x000a_佐佐木： 谢谢——！" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="C25" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="C26" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="C27" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="C28" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="C29" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="C31" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F280"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="12.8181818181818" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="69.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="39.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="29.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" customWidth="1"/>
+    <col min="4" max="4" width="69.26953125" customWidth="1"/>
+    <col min="6" max="6" width="39.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5965,7 +5453,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:6">
+    <row r="2" spans="1:6" hidden="1">
       <c r="A2" t="s">
         <v>142</v>
       </c>
@@ -5985,7 +5473,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:6">
+    <row r="3" spans="1:6" hidden="1">
       <c r="A3" t="s">
         <v>142</v>
       </c>
@@ -6005,7 +5493,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:6">
+    <row r="4" spans="1:6" hidden="1">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -6022,7 +5510,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:6">
+    <row r="5" spans="1:6" hidden="1">
       <c r="A5" t="s">
         <v>142</v>
       </c>
@@ -6039,7 +5527,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:6">
+    <row r="6" spans="1:6" hidden="1">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -6056,7 +5544,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:6">
+    <row r="7" spans="1:6" hidden="1">
       <c r="A7" t="s">
         <v>142</v>
       </c>
@@ -6076,7 +5564,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:6">
+    <row r="8" spans="1:6" hidden="1">
       <c r="A8" t="s">
         <v>142</v>
       </c>
@@ -6096,7 +5584,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:6">
+    <row r="9" spans="1:6" hidden="1">
       <c r="A9" t="s">
         <v>142</v>
       </c>
@@ -6116,7 +5604,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:6">
+    <row r="10" spans="1:6" hidden="1">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -6136,7 +5624,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:6">
+    <row r="11" spans="1:6" hidden="1">
       <c r="A11" t="s">
         <v>142</v>
       </c>
@@ -6153,7 +5641,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:6">
+    <row r="12" spans="1:6" hidden="1">
       <c r="A12" t="s">
         <v>142</v>
       </c>
@@ -6173,7 +5661,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:6">
+    <row r="13" spans="1:6" hidden="1">
       <c r="A13" t="s">
         <v>142</v>
       </c>
@@ -6190,7 +5678,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:6">
+    <row r="14" spans="1:6" hidden="1">
       <c r="A14" t="s">
         <v>123</v>
       </c>
@@ -6210,7 +5698,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="16" customHeight="1">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -6230,7 +5718,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:6">
+    <row r="16" spans="1:6" hidden="1">
       <c r="A16" t="s">
         <v>123</v>
       </c>
@@ -6250,7 +5738,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:6">
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -6267,7 +5755,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:6">
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -6287,7 +5775,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:6">
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" t="s">
         <v>123</v>
       </c>
@@ -6304,7 +5792,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:6">
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20" t="s">
         <v>123</v>
       </c>
@@ -6324,7 +5812,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:6">
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" t="s">
         <v>123</v>
       </c>
@@ -6341,7 +5829,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:6">
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" t="s">
         <v>123</v>
       </c>
@@ -6361,7 +5849,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:6">
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" t="s">
         <v>123</v>
       </c>
@@ -6381,7 +5869,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:6">
+    <row r="24" spans="1:6" ht="16" hidden="1" customHeight="1">
       <c r="A24" t="s">
         <v>123</v>
       </c>
@@ -6401,7 +5889,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:6">
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -6421,7 +5909,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:6">
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26" t="s">
         <v>123</v>
       </c>
@@ -6438,7 +5926,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:6">
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27" t="s">
         <v>123</v>
       </c>
@@ -6458,7 +5946,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:6">
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28" t="s">
         <v>123</v>
       </c>
@@ -6478,7 +5966,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:6">
+    <row r="29" spans="1:6" hidden="1">
       <c r="A29" t="s">
         <v>123</v>
       </c>
@@ -6498,7 +5986,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:6">
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30" t="s">
         <v>123</v>
       </c>
@@ -6515,7 +6003,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:6">
+    <row r="31" spans="1:6" hidden="1">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -6535,7 +6023,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:6">
+    <row r="32" spans="1:6" hidden="1">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -6555,7 +6043,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:6">
+    <row r="33" spans="1:6" hidden="1">
       <c r="A33" t="s">
         <v>123</v>
       </c>
@@ -6575,7 +6063,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:6">
+    <row r="34" spans="1:6" hidden="1">
       <c r="A34" t="s">
         <v>123</v>
       </c>
@@ -6595,7 +6083,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:6">
+    <row r="35" spans="1:6" hidden="1">
       <c r="A35" t="s">
         <v>123</v>
       </c>
@@ -6612,7 +6100,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:6">
+    <row r="36" spans="1:6" hidden="1">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -6629,7 +6117,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:6">
+    <row r="37" spans="1:6" hidden="1">
       <c r="A37" t="s">
         <v>123</v>
       </c>
@@ -6646,7 +6134,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:6">
+    <row r="38" spans="1:6" hidden="1">
       <c r="A38" t="s">
         <v>123</v>
       </c>
@@ -6663,7 +6151,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:6">
+    <row r="39" spans="1:6" hidden="1">
       <c r="A39" t="s">
         <v>123</v>
       </c>
@@ -6683,7 +6171,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:6">
+    <row r="40" spans="1:6" hidden="1">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -6700,7 +6188,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:6">
+    <row r="41" spans="1:6" hidden="1">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -6717,7 +6205,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:6">
+    <row r="42" spans="1:6" hidden="1">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -6734,7 +6222,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:6">
+    <row r="43" spans="1:6" hidden="1">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -6754,7 +6242,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:6">
+    <row r="44" spans="1:6" hidden="1">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -6774,7 +6262,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:6">
+    <row r="45" spans="1:6" hidden="1">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -6791,7 +6279,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:6">
+    <row r="46" spans="1:6" hidden="1">
       <c r="A46" t="s">
         <v>82</v>
       </c>
@@ -6811,7 +6299,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:6">
+    <row r="47" spans="1:6" hidden="1">
       <c r="A47" t="s">
         <v>82</v>
       </c>
@@ -6828,7 +6316,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:6">
+    <row r="48" spans="1:6" hidden="1">
       <c r="A48" t="s">
         <v>82</v>
       </c>
@@ -6845,7 +6333,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:6">
+    <row r="49" spans="1:6" hidden="1">
       <c r="A49" t="s">
         <v>82</v>
       </c>
@@ -6862,7 +6350,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="50" ht="13.5" hidden="1" customHeight="1" spans="1:6">
+    <row r="50" spans="1:6" ht="13.5" hidden="1" customHeight="1">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -6882,7 +6370,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:6">
+    <row r="51" spans="1:6" hidden="1">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -6902,7 +6390,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:6">
+    <row r="52" spans="1:6" hidden="1">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -6919,7 +6407,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:6">
+    <row r="53" spans="1:6" hidden="1">
       <c r="A53" t="s">
         <v>82</v>
       </c>
@@ -6939,7 +6427,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:6">
+    <row r="54" spans="1:6" hidden="1">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -6959,7 +6447,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:6">
+    <row r="55" spans="1:6" hidden="1">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -6979,7 +6467,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:6">
+    <row r="56" spans="1:6" hidden="1">
       <c r="A56" t="s">
         <v>82</v>
       </c>
@@ -6999,7 +6487,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:6">
+    <row r="57" spans="1:6" hidden="1">
       <c r="A57" t="s">
         <v>82</v>
       </c>
@@ -7016,7 +6504,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:6">
+    <row r="58" spans="1:6" hidden="1">
       <c r="A58" t="s">
         <v>82</v>
       </c>
@@ -7036,7 +6524,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:6">
+    <row r="59" spans="1:6" hidden="1">
       <c r="A59" t="s">
         <v>82</v>
       </c>
@@ -7053,7 +6541,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:6">
+    <row r="60" spans="1:6" hidden="1">
       <c r="A60" t="s">
         <v>82</v>
       </c>
@@ -7070,7 +6558,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:6">
+    <row r="61" spans="1:6" hidden="1">
       <c r="A61" t="s">
         <v>82</v>
       </c>
@@ -7087,7 +6575,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:6">
+    <row r="62" spans="1:6" hidden="1">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -7104,7 +6592,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:6">
+    <row r="63" spans="1:6" hidden="1">
       <c r="A63" t="s">
         <v>82</v>
       </c>
@@ -7121,7 +6609,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:6">
+    <row r="64" spans="1:6" hidden="1">
       <c r="A64" t="s">
         <v>82</v>
       </c>
@@ -7141,7 +6629,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:6">
+    <row r="65" spans="1:6" hidden="1">
       <c r="A65" t="s">
         <v>82</v>
       </c>
@@ -7161,7 +6649,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:6">
+    <row r="66" spans="1:6" hidden="1">
       <c r="A66" t="s">
         <v>82</v>
       </c>
@@ -7178,7 +6666,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:6">
+    <row r="67" spans="1:6" hidden="1">
       <c r="A67" t="s">
         <v>82</v>
       </c>
@@ -7195,7 +6683,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:6">
+    <row r="68" spans="1:6" hidden="1">
       <c r="A68" t="s">
         <v>101</v>
       </c>
@@ -7215,7 +6703,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:6">
+    <row r="69" spans="1:6" hidden="1">
       <c r="A69" t="s">
         <v>101</v>
       </c>
@@ -7235,7 +6723,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:6">
+    <row r="70" spans="1:6" hidden="1">
       <c r="A70" t="s">
         <v>101</v>
       </c>
@@ -7252,7 +6740,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:6">
+    <row r="71" spans="1:6" hidden="1">
       <c r="A71" t="s">
         <v>101</v>
       </c>
@@ -7272,7 +6760,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:6">
+    <row r="72" spans="1:6" hidden="1">
       <c r="A72" t="s">
         <v>101</v>
       </c>
@@ -7289,7 +6777,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:6">
+    <row r="73" spans="1:6" hidden="1">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -7309,7 +6797,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:6">
+    <row r="74" spans="1:6" hidden="1">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -7329,7 +6817,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:6">
+    <row r="75" spans="1:6" hidden="1">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -7349,7 +6837,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:6">
+    <row r="76" spans="1:6" hidden="1">
       <c r="A76" t="s">
         <v>101</v>
       </c>
@@ -7369,7 +6857,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:6">
+    <row r="77" spans="1:6" hidden="1">
       <c r="A77" t="s">
         <v>101</v>
       </c>
@@ -7389,7 +6877,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:6">
+    <row r="78" spans="1:6" hidden="1">
       <c r="A78" t="s">
         <v>101</v>
       </c>
@@ -7409,7 +6897,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:6">
+    <row r="79" spans="1:6" hidden="1">
       <c r="A79" t="s">
         <v>101</v>
       </c>
@@ -7426,7 +6914,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:6">
+    <row r="80" spans="1:6" hidden="1">
       <c r="A80" t="s">
         <v>101</v>
       </c>
@@ -7446,7 +6934,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:6">
+    <row r="81" spans="1:6" hidden="1">
       <c r="A81" t="s">
         <v>101</v>
       </c>
@@ -7463,7 +6951,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:6">
+    <row r="82" spans="1:6" hidden="1">
       <c r="A82" t="s">
         <v>101</v>
       </c>
@@ -7480,7 +6968,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:6">
+    <row r="83" spans="1:6" hidden="1">
       <c r="A83" t="s">
         <v>101</v>
       </c>
@@ -7497,7 +6985,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:6">
+    <row r="84" spans="1:6" hidden="1">
       <c r="A84" t="s">
         <v>101</v>
       </c>
@@ -7514,7 +7002,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:6">
+    <row r="85" spans="1:6" hidden="1">
       <c r="A85" t="s">
         <v>101</v>
       </c>
@@ -7531,7 +7019,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:6">
+    <row r="86" spans="1:6" hidden="1">
       <c r="A86" t="s">
         <v>101</v>
       </c>
@@ -7551,7 +7039,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:6">
+    <row r="87" spans="1:6" hidden="1">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -7571,7 +7059,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:6">
+    <row r="88" spans="1:6" hidden="1">
       <c r="A88" t="s">
         <v>101</v>
       </c>
@@ -7588,7 +7076,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:6">
+    <row r="89" spans="1:6" hidden="1">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -7605,7 +7093,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:6">
+    <row r="90" spans="1:6" hidden="1">
       <c r="A90" t="s">
         <v>31</v>
       </c>
@@ -7625,7 +7113,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:6">
+    <row r="91" spans="1:6" hidden="1">
       <c r="A91" t="s">
         <v>31</v>
       </c>
@@ -7645,7 +7133,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:6">
+    <row r="92" spans="1:6" hidden="1">
       <c r="A92" t="s">
         <v>31</v>
       </c>
@@ -7665,7 +7153,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:6">
+    <row r="93" spans="1:6" hidden="1">
       <c r="A93" t="s">
         <v>31</v>
       </c>
@@ -7685,7 +7173,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:6">
+    <row r="94" spans="1:6" hidden="1">
       <c r="A94" t="s">
         <v>31</v>
       </c>
@@ -7702,7 +7190,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:6">
+    <row r="95" spans="1:6" hidden="1">
       <c r="A95" t="s">
         <v>31</v>
       </c>
@@ -7719,7 +7207,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:6">
+    <row r="96" spans="1:6" hidden="1">
       <c r="A96" t="s">
         <v>31</v>
       </c>
@@ -7739,7 +7227,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:6">
+    <row r="97" spans="1:6" hidden="1">
       <c r="A97" t="s">
         <v>31</v>
       </c>
@@ -7759,7 +7247,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:6">
+    <row r="98" spans="1:6" hidden="1">
       <c r="A98" t="s">
         <v>31</v>
       </c>
@@ -7779,7 +7267,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:6">
+    <row r="99" spans="1:6" hidden="1">
       <c r="A99" t="s">
         <v>31</v>
       </c>
@@ -7796,7 +7284,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="100" ht="16" hidden="1" customHeight="1" spans="1:6">
+    <row r="100" spans="1:6" ht="16" hidden="1" customHeight="1">
       <c r="A100" t="s">
         <v>31</v>
       </c>
@@ -7813,7 +7301,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:6">
+    <row r="101" spans="1:6" hidden="1">
       <c r="A101" t="s">
         <v>31</v>
       </c>
@@ -7830,7 +7318,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:6">
+    <row r="102" spans="1:6" hidden="1">
       <c r="A102" t="s">
         <v>74</v>
       </c>
@@ -7850,7 +7338,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:6">
+    <row r="103" spans="1:6" hidden="1">
       <c r="A103" t="s">
         <v>74</v>
       </c>
@@ -7867,7 +7355,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:6">
+    <row r="104" spans="1:6" hidden="1">
       <c r="A104" t="s">
         <v>74</v>
       </c>
@@ -7887,7 +7375,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:6">
+    <row r="105" spans="1:6" hidden="1">
       <c r="A105" t="s">
         <v>116</v>
       </c>
@@ -7907,7 +7395,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" ht="16" customHeight="1">
       <c r="A106" t="s">
         <v>116</v>
       </c>
@@ -7927,7 +7415,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:6">
+    <row r="107" spans="1:6" hidden="1">
       <c r="A107" t="s">
         <v>116</v>
       </c>
@@ -7947,7 +7435,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:6">
+    <row r="108" spans="1:6" hidden="1">
       <c r="A108" t="s">
         <v>116</v>
       </c>
@@ -7964,7 +7452,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:6">
+    <row r="109" spans="1:6" hidden="1">
       <c r="A109" t="s">
         <v>116</v>
       </c>
@@ -7984,7 +7472,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:6">
+    <row r="110" spans="1:6" hidden="1">
       <c r="A110" t="s">
         <v>116</v>
       </c>
@@ -8001,7 +7489,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:6">
+    <row r="111" spans="1:6" hidden="1">
       <c r="A111" t="s">
         <v>116</v>
       </c>
@@ -8018,7 +7506,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:6">
+    <row r="112" spans="1:6" hidden="1">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -8035,7 +7523,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:6">
+    <row r="113" spans="1:6" hidden="1">
       <c r="A113" t="s">
         <v>116</v>
       </c>
@@ -8055,7 +7543,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:6">
+    <row r="114" spans="1:6" hidden="1">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -8075,7 +7563,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:6">
+    <row r="115" spans="1:6" hidden="1">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -8095,7 +7583,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:6">
+    <row r="116" spans="1:6" hidden="1">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -8115,7 +7603,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="117" ht="16" hidden="1" customHeight="1" spans="1:6">
+    <row r="117" spans="1:6" ht="16" hidden="1" customHeight="1">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -8132,7 +7620,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:6">
+    <row r="118" spans="1:6" hidden="1">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -8152,7 +7640,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:6">
+    <row r="119" spans="1:6" hidden="1">
       <c r="A119" t="s">
         <v>116</v>
       </c>
@@ -8172,7 +7660,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:6">
+    <row r="120" spans="1:6" hidden="1">
       <c r="A120" t="s">
         <v>116</v>
       </c>
@@ -8192,7 +7680,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:6">
+    <row r="121" spans="1:6" hidden="1">
       <c r="A121" t="s">
         <v>116</v>
       </c>
@@ -8209,7 +7697,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:6">
+    <row r="122" spans="1:6" hidden="1">
       <c r="A122" t="s">
         <v>116</v>
       </c>
@@ -8229,7 +7717,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:6">
+    <row r="123" spans="1:6" hidden="1">
       <c r="A123" t="s">
         <v>116</v>
       </c>
@@ -8246,7 +7734,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:6">
+    <row r="124" spans="1:6" hidden="1">
       <c r="A124" t="s">
         <v>116</v>
       </c>
@@ -8263,7 +7751,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:6">
+    <row r="125" spans="1:6" hidden="1">
       <c r="A125" t="s">
         <v>116</v>
       </c>
@@ -8280,7 +7768,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:6">
+    <row r="126" spans="1:6" hidden="1">
       <c r="A126" t="s">
         <v>116</v>
       </c>
@@ -8297,7 +7785,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:6">
+    <row r="127" spans="1:6" hidden="1">
       <c r="A127" t="s">
         <v>116</v>
       </c>
@@ -8314,7 +7802,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:6">
+    <row r="128" spans="1:6" hidden="1">
       <c r="A128" t="s">
         <v>116</v>
       </c>
@@ -8334,7 +7822,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:6">
+    <row r="129" spans="1:6" hidden="1">
       <c r="A129" t="s">
         <v>116</v>
       </c>
@@ -8354,7 +7842,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:6">
+    <row r="130" spans="1:6" hidden="1">
       <c r="A130" t="s">
         <v>116</v>
       </c>
@@ -8371,7 +7859,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:6">
+    <row r="131" spans="1:6" hidden="1">
       <c r="A131" t="s">
         <v>116</v>
       </c>
@@ -8388,7 +7876,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:6">
+    <row r="132" spans="1:6" hidden="1">
       <c r="A132" t="s">
         <v>116</v>
       </c>
@@ -8405,7 +7893,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:6">
+    <row r="133" spans="1:6" hidden="1">
       <c r="A133" t="s">
         <v>116</v>
       </c>
@@ -8425,7 +7913,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:6">
+    <row r="134" spans="1:6" hidden="1">
       <c r="A134" t="s">
         <v>108</v>
       </c>
@@ -8445,7 +7933,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" ht="16" customHeight="1">
       <c r="A135" t="s">
         <v>108</v>
       </c>
@@ -8465,7 +7953,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:6">
+    <row r="136" spans="1:6" hidden="1">
       <c r="A136" t="s">
         <v>108</v>
       </c>
@@ -8485,7 +7973,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:6">
+    <row r="137" spans="1:6" hidden="1">
       <c r="A137" t="s">
         <v>108</v>
       </c>
@@ -8502,7 +7990,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:6">
+    <row r="138" spans="1:6" hidden="1">
       <c r="A138" t="s">
         <v>108</v>
       </c>
@@ -8522,7 +8010,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:6">
+    <row r="139" spans="1:6" hidden="1">
       <c r="A139" t="s">
         <v>108</v>
       </c>
@@ -8539,7 +8027,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:6">
+    <row r="140" spans="1:6" hidden="1">
       <c r="A140" t="s">
         <v>108</v>
       </c>
@@ -8559,7 +8047,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:6">
+    <row r="141" spans="1:6" hidden="1">
       <c r="A141" t="s">
         <v>108</v>
       </c>
@@ -8579,7 +8067,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:6">
+    <row r="142" spans="1:6" hidden="1">
       <c r="A142" t="s">
         <v>108</v>
       </c>
@@ -8599,7 +8087,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:6">
+    <row r="143" spans="1:6" hidden="1">
       <c r="A143" t="s">
         <v>108</v>
       </c>
@@ -8619,7 +8107,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:6">
+    <row r="144" spans="1:6" hidden="1">
       <c r="A144" t="s">
         <v>108</v>
       </c>
@@ -8636,7 +8124,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:6">
+    <row r="145" spans="1:6" hidden="1">
       <c r="A145" t="s">
         <v>108</v>
       </c>
@@ -8653,7 +8141,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="146" ht="16" hidden="1" customHeight="1" spans="1:6">
+    <row r="146" spans="1:6" ht="16" hidden="1" customHeight="1">
       <c r="A146" t="s">
         <v>108</v>
       </c>
@@ -8670,7 +8158,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="1:6">
+    <row r="147" spans="1:6" hidden="1">
       <c r="A147" t="s">
         <v>108</v>
       </c>
@@ -8687,7 +8175,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:6">
+    <row r="148" spans="1:6" hidden="1">
       <c r="A148" t="s">
         <v>108</v>
       </c>
@@ -8704,7 +8192,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:6">
+    <row r="149" spans="1:6" hidden="1">
       <c r="A149" t="s">
         <v>108</v>
       </c>
@@ -8724,7 +8212,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:6">
+    <row r="150" spans="1:6" hidden="1">
       <c r="A150" t="s">
         <v>108</v>
       </c>
@@ -8741,7 +8229,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:6">
+    <row r="151" spans="1:6" hidden="1">
       <c r="A151" t="s">
         <v>54</v>
       </c>
@@ -8761,7 +8249,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:6">
+    <row r="152" spans="1:6" hidden="1">
       <c r="A152" t="s">
         <v>54</v>
       </c>
@@ -8778,7 +8266,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="153" hidden="1" spans="1:6">
+    <row r="153" spans="1:6" hidden="1">
       <c r="A153" t="s">
         <v>54</v>
       </c>
@@ -8798,7 +8286,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="1:6">
+    <row r="154" spans="1:6" hidden="1">
       <c r="A154" t="s">
         <v>54</v>
       </c>
@@ -8818,7 +8306,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" ht="16" hidden="1" customHeight="1" spans="1:6">
+    <row r="155" spans="1:6" ht="16" hidden="1" customHeight="1">
       <c r="A155" t="s">
         <v>54</v>
       </c>
@@ -8835,7 +8323,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="156" hidden="1" spans="1:6">
+    <row r="156" spans="1:6" hidden="1">
       <c r="A156" t="s">
         <v>54</v>
       </c>
@@ -8855,7 +8343,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="1:6">
+    <row r="157" spans="1:6" hidden="1">
       <c r="A157" t="s">
         <v>54</v>
       </c>
@@ -8872,7 +8360,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="1:6">
+    <row r="158" spans="1:6" hidden="1">
       <c r="A158" t="s">
         <v>54</v>
       </c>
@@ -8889,7 +8377,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="159" hidden="1" spans="1:6">
+    <row r="159" spans="1:6" hidden="1">
       <c r="A159" t="s">
         <v>54</v>
       </c>
@@ -8906,7 +8394,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="160" hidden="1" spans="1:6">
+    <row r="160" spans="1:6" hidden="1">
       <c r="A160" t="s">
         <v>54</v>
       </c>
@@ -8923,7 +8411,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="1:6">
+    <row r="161" spans="1:6" hidden="1">
       <c r="A161" t="s">
         <v>54</v>
       </c>
@@ -8940,7 +8428,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:6">
+    <row r="162" spans="1:6" hidden="1">
       <c r="A162" t="s">
         <v>54</v>
       </c>
@@ -8960,7 +8448,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:6">
+    <row r="163" spans="1:6" hidden="1">
       <c r="A163" t="s">
         <v>54</v>
       </c>
@@ -8980,7 +8468,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="1:6">
+    <row r="164" spans="1:6" hidden="1">
       <c r="A164" t="s">
         <v>54</v>
       </c>
@@ -8997,7 +8485,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="165" hidden="1" spans="1:6">
+    <row r="165" spans="1:6" hidden="1">
       <c r="A165" t="s">
         <v>54</v>
       </c>
@@ -9014,7 +8502,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="1:6">
+    <row r="166" spans="1:6" hidden="1">
       <c r="A166" t="s">
         <v>54</v>
       </c>
@@ -9031,7 +8519,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="1:6">
+    <row r="167" spans="1:6" hidden="1">
       <c r="A167" t="s">
         <v>54</v>
       </c>
@@ -9048,7 +8536,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="168" hidden="1" spans="1:6">
+    <row r="168" spans="1:6" hidden="1">
       <c r="A168" t="s">
         <v>148</v>
       </c>
@@ -9068,7 +8556,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="169" hidden="1" spans="1:6">
+    <row r="169" spans="1:6" hidden="1">
       <c r="A169" t="s">
         <v>148</v>
       </c>
@@ -9085,7 +8573,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:6">
+    <row r="170" spans="1:6" hidden="1">
       <c r="A170" t="s">
         <v>148</v>
       </c>
@@ -9105,7 +8593,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:6">
+    <row r="171" spans="1:6" ht="16" hidden="1" customHeight="1">
       <c r="A171" t="s">
         <v>148</v>
       </c>
@@ -9125,7 +8613,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:6">
+    <row r="172" spans="1:6" hidden="1">
       <c r="A172" t="s">
         <v>148</v>
       </c>
@@ -9145,7 +8633,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:6">
+    <row r="173" spans="1:6" hidden="1">
       <c r="A173" t="s">
         <v>148</v>
       </c>
@@ -9165,7 +8653,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:6">
+    <row r="174" spans="1:6" hidden="1">
       <c r="A174" t="s">
         <v>148</v>
       </c>
@@ -9185,7 +8673,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="1:6">
+    <row r="175" spans="1:6" hidden="1">
       <c r="A175" t="s">
         <v>148</v>
       </c>
@@ -9205,7 +8693,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="1:6">
+    <row r="176" spans="1:6" hidden="1">
       <c r="A176" t="s">
         <v>148</v>
       </c>
@@ -9225,7 +8713,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="1:6">
+    <row r="177" spans="1:6" hidden="1">
       <c r="A177" t="s">
         <v>148</v>
       </c>
@@ -9245,7 +8733,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="178" hidden="1" spans="1:6">
+    <row r="178" spans="1:6" hidden="1">
       <c r="A178" t="s">
         <v>148</v>
       </c>
@@ -9265,7 +8753,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:6">
+    <row r="179" spans="1:6" hidden="1">
       <c r="A179" t="s">
         <v>148</v>
       </c>
@@ -9285,7 +8773,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="180" hidden="1" spans="1:6">
+    <row r="180" spans="1:6" hidden="1">
       <c r="A180" t="s">
         <v>148</v>
       </c>
@@ -9302,7 +8790,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="181" hidden="1" spans="1:6">
+    <row r="181" spans="1:6" hidden="1">
       <c r="A181" t="s">
         <v>148</v>
       </c>
@@ -9322,7 +8810,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="182" hidden="1" spans="1:6">
+    <row r="182" spans="1:6" hidden="1">
       <c r="A182" t="s">
         <v>148</v>
       </c>
@@ -9339,7 +8827,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="183" hidden="1" spans="1:6">
+    <row r="183" spans="1:6" hidden="1">
       <c r="A183" t="s">
         <v>148</v>
       </c>
@@ -9359,7 +8847,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="184" hidden="1" spans="1:6">
+    <row r="184" spans="1:6" hidden="1">
       <c r="A184" t="s">
         <v>148</v>
       </c>
@@ -9379,7 +8867,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="185" hidden="1" spans="1:6">
+    <row r="185" spans="1:6" hidden="1">
       <c r="A185" t="s">
         <v>148</v>
       </c>
@@ -9396,7 +8884,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="186" hidden="1" spans="1:6">
+    <row r="186" spans="1:6" hidden="1">
       <c r="A186" t="s">
         <v>148</v>
       </c>
@@ -9416,7 +8904,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="187" hidden="1" spans="1:6">
+    <row r="187" spans="1:6" hidden="1">
       <c r="A187" t="s">
         <v>148</v>
       </c>
@@ -9433,7 +8921,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="188" hidden="1" spans="1:6">
+    <row r="188" spans="1:6" hidden="1">
       <c r="A188" t="s">
         <v>148</v>
       </c>
@@ -9450,7 +8938,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="189" hidden="1" spans="1:6">
+    <row r="189" spans="1:6" hidden="1">
       <c r="A189" t="s">
         <v>148</v>
       </c>
@@ -9467,7 +8955,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="190" hidden="1" spans="1:6">
+    <row r="190" spans="1:6" hidden="1">
       <c r="A190" t="s">
         <v>148</v>
       </c>
@@ -9484,7 +8972,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="191" hidden="1" spans="1:6">
+    <row r="191" spans="1:6" hidden="1">
       <c r="A191" t="s">
         <v>148</v>
       </c>
@@ -9501,7 +8989,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="192" hidden="1" spans="1:6">
+    <row r="192" spans="1:6" hidden="1">
       <c r="A192" t="s">
         <v>148</v>
       </c>
@@ -9521,7 +9009,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="193" hidden="1" spans="1:6">
+    <row r="193" spans="1:6" hidden="1">
       <c r="A193" t="s">
         <v>148</v>
       </c>
@@ -9541,7 +9029,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="194" hidden="1" spans="1:6">
+    <row r="194" spans="1:6" hidden="1">
       <c r="A194" t="s">
         <v>148</v>
       </c>
@@ -9558,7 +9046,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="195" hidden="1" spans="1:6">
+    <row r="195" spans="1:6" hidden="1">
       <c r="A195" t="s">
         <v>148</v>
       </c>
@@ -9575,7 +9063,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="196" hidden="1" spans="1:6">
+    <row r="196" spans="1:6" hidden="1">
       <c r="A196" t="s">
         <v>148</v>
       </c>
@@ -9592,7 +9080,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="197" hidden="1" spans="1:6">
+    <row r="197" spans="1:6" hidden="1">
       <c r="A197" t="s">
         <v>148</v>
       </c>
@@ -9609,7 +9097,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="198" hidden="1" spans="1:6">
+    <row r="198" spans="1:6" hidden="1">
       <c r="A198" t="s">
         <v>148</v>
       </c>
@@ -9629,7 +9117,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="199" hidden="1" spans="1:6">
+    <row r="199" spans="1:6" hidden="1">
       <c r="A199" t="s">
         <v>155</v>
       </c>
@@ -9649,7 +9137,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="200" hidden="1" spans="1:6">
+    <row r="200" spans="1:6" hidden="1">
       <c r="A200" t="s">
         <v>155</v>
       </c>
@@ -9666,7 +9154,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="201" hidden="1" spans="1:6">
+    <row r="201" spans="1:6" hidden="1">
       <c r="A201" t="s">
         <v>155</v>
       </c>
@@ -9686,7 +9174,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="202" hidden="1" spans="1:6">
+    <row r="202" spans="1:6" hidden="1">
       <c r="A202" t="s">
         <v>155</v>
       </c>
@@ -9706,7 +9194,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="203" hidden="1" spans="1:6">
+    <row r="203" spans="1:6" hidden="1">
       <c r="A203" t="s">
         <v>155</v>
       </c>
@@ -9726,7 +9214,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="204" hidden="1" spans="1:6">
+    <row r="204" spans="1:6" hidden="1">
       <c r="A204" t="s">
         <v>155</v>
       </c>
@@ -9746,7 +9234,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="205" hidden="1" spans="1:6">
+    <row r="205" spans="1:6" hidden="1">
       <c r="A205" t="s">
         <v>155</v>
       </c>
@@ -9763,7 +9251,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="206" hidden="1" spans="1:6">
+    <row r="206" spans="1:6" hidden="1">
       <c r="A206" t="s">
         <v>155</v>
       </c>
@@ -9783,7 +9271,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="207" hidden="1" spans="1:6">
+    <row r="207" spans="1:6" hidden="1">
       <c r="A207" t="s">
         <v>155</v>
       </c>
@@ -9803,7 +9291,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="208" hidden="1" spans="1:6">
+    <row r="208" spans="1:6" hidden="1">
       <c r="A208" t="s">
         <v>155</v>
       </c>
@@ -9823,7 +9311,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="209" hidden="1" spans="1:6">
+    <row r="209" spans="1:6" hidden="1">
       <c r="A209" t="s">
         <v>155</v>
       </c>
@@ -9843,7 +9331,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="210" hidden="1" spans="1:6">
+    <row r="210" spans="1:6" hidden="1">
       <c r="A210" t="s">
         <v>155</v>
       </c>
@@ -9860,7 +9348,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="211" hidden="1" spans="1:6">
+    <row r="211" spans="1:6" hidden="1">
       <c r="A211" t="s">
         <v>155</v>
       </c>
@@ -9880,7 +9368,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="212" hidden="1" spans="1:6">
+    <row r="212" spans="1:6" hidden="1">
       <c r="A212" t="s">
         <v>155</v>
       </c>
@@ -9897,7 +9385,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="213" hidden="1" spans="1:6">
+    <row r="213" spans="1:6" hidden="1">
       <c r="A213" t="s">
         <v>155</v>
       </c>
@@ -9917,7 +9405,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="214" hidden="1" spans="1:6">
+    <row r="214" spans="1:6" hidden="1">
       <c r="A214" t="s">
         <v>155</v>
       </c>
@@ -9934,7 +9422,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="215" hidden="1" spans="1:6">
+    <row r="215" spans="1:6" hidden="1">
       <c r="A215" t="s">
         <v>155</v>
       </c>
@@ -9951,7 +9439,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="216" hidden="1" spans="1:6">
+    <row r="216" spans="1:6" hidden="1">
       <c r="A216" t="s">
         <v>155</v>
       </c>
@@ -9968,7 +9456,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="217" hidden="1" spans="1:6">
+    <row r="217" spans="1:6" hidden="1">
       <c r="A217" t="s">
         <v>155</v>
       </c>
@@ -9985,7 +9473,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="218" hidden="1" spans="1:6">
+    <row r="218" spans="1:6" hidden="1">
       <c r="A218" t="s">
         <v>155</v>
       </c>
@@ -10002,7 +9490,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="219" hidden="1" spans="1:6">
+    <row r="219" spans="1:6" hidden="1">
       <c r="A219" t="s">
         <v>155</v>
       </c>
@@ -10022,7 +9510,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="220" hidden="1" spans="1:6">
+    <row r="220" spans="1:6" hidden="1">
       <c r="A220" t="s">
         <v>155</v>
       </c>
@@ -10042,7 +9530,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="221" hidden="1" spans="1:6">
+    <row r="221" spans="1:6" hidden="1">
       <c r="A221" t="s">
         <v>155</v>
       </c>
@@ -10059,7 +9547,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="222" hidden="1" spans="1:6">
+    <row r="222" spans="1:6" hidden="1">
       <c r="A222" t="s">
         <v>155</v>
       </c>
@@ -10076,7 +9564,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="223" hidden="1" spans="1:6">
+    <row r="223" spans="1:6" hidden="1">
       <c r="A223" t="s">
         <v>155</v>
       </c>
@@ -10093,7 +9581,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="224" hidden="1" spans="1:6">
+    <row r="224" spans="1:6" hidden="1">
       <c r="A224" t="s">
         <v>155</v>
       </c>
@@ -10110,7 +9598,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="225" hidden="1" spans="1:6">
+    <row r="225" spans="1:6" hidden="1">
       <c r="A225" t="s">
         <v>155</v>
       </c>
@@ -10130,7 +9618,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="226" hidden="1" spans="1:6">
+    <row r="226" spans="1:6" hidden="1">
       <c r="A226" t="s">
         <v>43</v>
       </c>
@@ -10147,7 +9635,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="227" hidden="1" spans="1:6">
+    <row r="227" spans="1:6" hidden="1">
       <c r="A227" t="s">
         <v>43</v>
       </c>
@@ -10167,7 +9655,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="228" hidden="1" spans="1:6">
+    <row r="228" spans="1:6" hidden="1">
       <c r="A228" t="s">
         <v>43</v>
       </c>
@@ -10187,7 +9675,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="229" hidden="1" spans="1:6">
+    <row r="229" spans="1:6" hidden="1">
       <c r="A229" t="s">
         <v>43</v>
       </c>
@@ -10207,7 +9695,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="230" hidden="1" spans="1:6">
+    <row r="230" spans="1:6" hidden="1">
       <c r="A230" t="s">
         <v>43</v>
       </c>
@@ -10227,7 +9715,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="231" hidden="1" spans="1:6">
+    <row r="231" spans="1:6" hidden="1">
       <c r="A231" t="s">
         <v>43</v>
       </c>
@@ -10247,7 +9735,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="232" hidden="1" spans="1:6">
+    <row r="232" spans="1:6" hidden="1">
       <c r="A232" t="s">
         <v>43</v>
       </c>
@@ -10267,7 +9755,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="233" hidden="1" spans="1:6">
+    <row r="233" spans="1:6" hidden="1">
       <c r="A233" t="s">
         <v>43</v>
       </c>
@@ -10287,7 +9775,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="234" hidden="1" spans="1:6">
+    <row r="234" spans="1:6" hidden="1">
       <c r="A234" t="s">
         <v>43</v>
       </c>
@@ -10304,7 +9792,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="235" hidden="1" spans="1:6">
+    <row r="235" spans="1:6" hidden="1">
       <c r="A235" t="s">
         <v>92</v>
       </c>
@@ -10324,7 +9812,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="236" hidden="1" spans="1:6">
+    <row r="236" spans="1:6" hidden="1">
       <c r="A236" t="s">
         <v>92</v>
       </c>
@@ -10344,7 +9832,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="237" hidden="1" spans="1:6">
+    <row r="237" spans="1:6" hidden="1">
       <c r="A237" t="s">
         <v>92</v>
       </c>
@@ -10361,7 +9849,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="238" hidden="1" spans="1:6">
+    <row r="238" spans="1:6" hidden="1">
       <c r="A238" t="s">
         <v>92</v>
       </c>
@@ -10381,7 +9869,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="239" hidden="1" spans="1:6">
+    <row r="239" spans="1:6" hidden="1">
       <c r="A239" t="s">
         <v>92</v>
       </c>
@@ -10398,7 +9886,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="240" hidden="1" spans="1:6">
+    <row r="240" spans="1:6" hidden="1">
       <c r="A240" t="s">
         <v>92</v>
       </c>
@@ -10418,7 +9906,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="241" hidden="1" spans="1:6">
+    <row r="241" spans="1:6" hidden="1">
       <c r="A241" t="s">
         <v>92</v>
       </c>
@@ -10438,7 +9926,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="242" hidden="1" spans="1:6">
+    <row r="242" spans="1:6" hidden="1">
       <c r="A242" t="s">
         <v>92</v>
       </c>
@@ -10458,7 +9946,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="243" hidden="1" spans="1:6">
+    <row r="243" spans="1:6" hidden="1">
       <c r="A243" t="s">
         <v>92</v>
       </c>
@@ -10475,7 +9963,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:6">
+    <row r="244" spans="1:6" hidden="1">
       <c r="A244" t="s">
         <v>133</v>
       </c>
@@ -10495,7 +9983,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="245" hidden="1" spans="1:6">
+    <row r="245" spans="1:6" hidden="1">
       <c r="A245" t="s">
         <v>133</v>
       </c>
@@ -10512,7 +10000,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="246" hidden="1" spans="1:6">
+    <row r="246" spans="1:6" hidden="1">
       <c r="A246" t="s">
         <v>133</v>
       </c>
@@ -10532,7 +10020,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="247" hidden="1" spans="1:6">
+    <row r="247" spans="1:6" hidden="1">
       <c r="A247" t="s">
         <v>133</v>
       </c>
@@ -10549,7 +10037,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="248" hidden="1" spans="1:6">
+    <row r="248" spans="1:6" hidden="1">
       <c r="A248" t="s">
         <v>133</v>
       </c>
@@ -10569,7 +10057,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="249" hidden="1" spans="1:6">
+    <row r="249" spans="1:6" hidden="1">
       <c r="A249" t="s">
         <v>133</v>
       </c>
@@ -10589,7 +10077,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="250" hidden="1" spans="1:6">
+    <row r="250" spans="1:6" hidden="1">
       <c r="A250" t="s">
         <v>133</v>
       </c>
@@ -10609,7 +10097,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="251" hidden="1" spans="1:6">
+    <row r="251" spans="1:6" hidden="1">
       <c r="A251" t="s">
         <v>133</v>
       </c>
@@ -10629,7 +10117,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="252" hidden="1" spans="1:6">
+    <row r="252" spans="1:6" hidden="1">
       <c r="A252" t="s">
         <v>133</v>
       </c>
@@ -10649,7 +10137,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="253" hidden="1" spans="1:6">
+    <row r="253" spans="1:6" hidden="1">
       <c r="A253" t="s">
         <v>133</v>
       </c>
@@ -10666,7 +10154,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="254" hidden="1" spans="1:6">
+    <row r="254" spans="1:6" hidden="1">
       <c r="A254" t="s">
         <v>133</v>
       </c>
@@ -10683,7 +10171,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="255" hidden="1" spans="1:6">
+    <row r="255" spans="1:6" hidden="1">
       <c r="A255" t="s">
         <v>133</v>
       </c>
@@ -10700,7 +10188,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="256" hidden="1" spans="1:6">
+    <row r="256" spans="1:6" hidden="1">
       <c r="A256" t="s">
         <v>133</v>
       </c>
@@ -10717,7 +10205,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="257" hidden="1" spans="1:6">
+    <row r="257" spans="1:6" hidden="1">
       <c r="A257" t="s">
         <v>133</v>
       </c>
@@ -10737,7 +10225,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="258" hidden="1" spans="1:6">
+    <row r="258" spans="1:6" hidden="1">
       <c r="A258" t="s">
         <v>133</v>
       </c>
@@ -10754,7 +10242,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="259" hidden="1" spans="1:6">
+    <row r="259" spans="1:6" hidden="1">
       <c r="A259" t="s">
         <v>161</v>
       </c>
@@ -10774,7 +10262,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="260" hidden="1" spans="1:6">
+    <row r="260" spans="1:6" hidden="1">
       <c r="A260" t="s">
         <v>161</v>
       </c>
@@ -10794,7 +10282,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="261" hidden="1" spans="1:6">
+    <row r="261" spans="1:6" hidden="1">
       <c r="A261" t="s">
         <v>161</v>
       </c>
@@ -10814,7 +10302,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="262" hidden="1" spans="1:6">
+    <row r="262" spans="1:6" hidden="1">
       <c r="A262" t="s">
         <v>161</v>
       </c>
@@ -10834,7 +10322,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="263" hidden="1" spans="1:6">
+    <row r="263" spans="1:6" hidden="1">
       <c r="A263" t="s">
         <v>161</v>
       </c>
@@ -10854,7 +10342,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="264" hidden="1" spans="1:6">
+    <row r="264" spans="1:6" hidden="1">
       <c r="A264" t="s">
         <v>161</v>
       </c>
@@ -10874,7 +10362,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="265" hidden="1" spans="1:6">
+    <row r="265" spans="1:6" hidden="1">
       <c r="A265" t="s">
         <v>161</v>
       </c>
@@ -10891,7 +10379,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="266" hidden="1" spans="1:6">
+    <row r="266" spans="1:6" hidden="1">
       <c r="A266" t="s">
         <v>161</v>
       </c>
@@ -10911,7 +10399,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="267" hidden="1" spans="1:6">
+    <row r="267" spans="1:6" hidden="1">
       <c r="A267" t="s">
         <v>161</v>
       </c>
@@ -10928,7 +10416,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="268" hidden="1" spans="1:6">
+    <row r="268" spans="1:6" hidden="1">
       <c r="A268" t="s">
         <v>161</v>
       </c>
@@ -10945,7 +10433,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="269" hidden="1" spans="1:6">
+    <row r="269" spans="1:6" hidden="1">
       <c r="A269" t="s">
         <v>161</v>
       </c>
@@ -10962,7 +10450,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="270" hidden="1" spans="1:6">
+    <row r="270" spans="1:6" hidden="1">
       <c r="A270" t="s">
         <v>161</v>
       </c>
@@ -10979,7 +10467,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="271" hidden="1" spans="1:6">
+    <row r="271" spans="1:6" hidden="1">
       <c r="A271" t="s">
         <v>161</v>
       </c>
@@ -10996,7 +10484,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="272" hidden="1" spans="1:6">
+    <row r="272" spans="1:6" hidden="1">
       <c r="A272" t="s">
         <v>161</v>
       </c>
@@ -11016,7 +10504,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="273" hidden="1" spans="1:6">
+    <row r="273" spans="1:6" hidden="1">
       <c r="A273" t="s">
         <v>161</v>
       </c>
@@ -11033,7 +10521,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="274" hidden="1" spans="1:6">
+    <row r="274" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A274" s="7" t="s">
         <v>168</v>
       </c>
@@ -11053,7 +10541,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="275" hidden="1" spans="1:6">
+    <row r="275" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A275" s="7" t="s">
         <v>168</v>
       </c>
@@ -11073,7 +10561,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="276" hidden="1" spans="1:6">
+    <row r="276" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A276" s="7" t="s">
         <v>168</v>
       </c>
@@ -11093,7 +10581,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="277" hidden="1" spans="1:6">
+    <row r="277" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A277" s="7" t="s">
         <v>168</v>
       </c>
@@ -11113,7 +10601,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="278" hidden="1" spans="1:6">
+    <row r="278" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A278" s="7" t="s">
         <v>168</v>
       </c>
@@ -11133,7 +10621,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="279" hidden="1" spans="1:6">
+    <row r="279" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A279" s="7" t="s">
         <v>168</v>
       </c>
@@ -11153,7 +10641,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="280" hidden="1" spans="1:6">
+    <row r="280" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A280" s="7" t="s">
         <v>168</v>
       </c>
@@ -11171,152 +10659,150 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F280" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:F280" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="3">
       <filters>
         <filter val="Roselia「Farbe」"/>
       </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac47931167" tooltip="https://www.acfun.cn/v/ac47931167"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://www.acfun.cn/v/ac47931167_2"/>
-    <hyperlink ref="F7" r:id="rId3" display="https://www.acfun.cn/v/ac47931167_3"/>
-    <hyperlink ref="F8" r:id="rId4" display="https://www.acfun.cn/v/ac47931167_4"/>
-    <hyperlink ref="F9" r:id="rId5" display="https://www.acfun.cn/v/ac47931167_5"/>
-    <hyperlink ref="F10" r:id="rId6" display="https://www.acfun.cn/v/ac47931167_6"/>
-    <hyperlink ref="F12" r:id="rId7" display="https://www.acfun.cn/v/ac47931167_7"/>
-    <hyperlink ref="F14" r:id="rId8" display="https://www.acfun.cn/v/ac47934758"/>
-    <hyperlink ref="F15" r:id="rId9" display="https://www.acfun.cn/v/ac47934758_2"/>
-    <hyperlink ref="F16" r:id="rId10" display="https://www.acfun.cn/v/ac47934758_3"/>
-    <hyperlink ref="F18" r:id="rId11" display="https://www.acfun.cn/v/ac47934758_4"/>
-    <hyperlink ref="F20" r:id="rId12" display="https://www.acfun.cn/v/ac47934758_5"/>
-    <hyperlink ref="F22" r:id="rId13" display="https://www.acfun.cn/v/ac47934758_6"/>
-    <hyperlink ref="F23" r:id="rId14" display="https://www.acfun.cn/v/ac47934758_7"/>
-    <hyperlink ref="F24" r:id="rId15" display="https://www.acfun.cn/v/ac47934758_8"/>
-    <hyperlink ref="F25" r:id="rId16" display="https://www.acfun.cn/v/ac47934758_9"/>
-    <hyperlink ref="F27" r:id="rId17" display="https://www.acfun.cn/v/ac47934758_10"/>
-    <hyperlink ref="F28" r:id="rId18" display="https://www.acfun.cn/v/ac47934815"/>
-    <hyperlink ref="F29" r:id="rId19" display="https://www.acfun.cn/v/ac47934815_2"/>
-    <hyperlink ref="F31" r:id="rId20" display="https://www.acfun.cn/v/ac47934815_3"/>
-    <hyperlink ref="F32" r:id="rId21" display="https://www.acfun.cn/v/ac47934815_4"/>
-    <hyperlink ref="F33" r:id="rId22" display="https://www.acfun.cn/v/ac47934815_5"/>
-    <hyperlink ref="F34" r:id="rId23" display="https://www.acfun.cn/v/ac47934815_6"/>
-    <hyperlink ref="F39" r:id="rId24" display="https://www.acfun.cn/v/ac47934815_7"/>
-    <hyperlink ref="F69" r:id="rId25" display="https://www.acfun.cn/v/ac47935101_2"/>
-    <hyperlink ref="F71" r:id="rId26" display="https://www.acfun.cn/v/ac47935101_3"/>
-    <hyperlink ref="F73" r:id="rId27" display="https://www.acfun.cn/v/ac47935101_4"/>
-    <hyperlink ref="F74" r:id="rId28" display="https://www.acfun.cn/v/ac47935101_5"/>
-    <hyperlink ref="F75" r:id="rId29" display="https://www.acfun.cn/v/ac47935101_6"/>
-    <hyperlink ref="F76" r:id="rId30" display="https://www.acfun.cn/v/ac47935101_7"/>
-    <hyperlink ref="F77" r:id="rId31" display="https://www.acfun.cn/v/ac47935101_8"/>
-    <hyperlink ref="F78" r:id="rId32" display="https://www.acfun.cn/v/ac47935101_9"/>
-    <hyperlink ref="F80" r:id="rId33" display="https://www.acfun.cn/v/ac47935101_10"/>
-    <hyperlink ref="F87" r:id="rId34" display="https://www.acfun.cn/v/ac48752881_2"/>
-    <hyperlink ref="F105" r:id="rId35" display="https://www.acfun.cn/v/ac47935303"/>
-    <hyperlink ref="F106" r:id="rId36" display="https://www.acfun.cn/v/ac47935303_2"/>
-    <hyperlink ref="F107" r:id="rId37" display="https://www.acfun.cn/v/ac47935303_3"/>
-    <hyperlink ref="F109" r:id="rId38" display="https://www.acfun.cn/v/ac47935303_4"/>
-    <hyperlink ref="F113" r:id="rId39" display="https://www.acfun.cn/v/ac47935303_5"/>
-    <hyperlink ref="F114" r:id="rId40" display="https://www.acfun.cn/v/ac47935303_6"/>
-    <hyperlink ref="F115" r:id="rId41" display="https://www.acfun.cn/v/ac47935303_7"/>
-    <hyperlink ref="F116" r:id="rId42" display="https://www.acfun.cn/v/ac47935303_8"/>
-    <hyperlink ref="F118" r:id="rId43" display="https://www.acfun.cn/v/ac47935303_9"/>
-    <hyperlink ref="F119" r:id="rId44" display="https://www.acfun.cn/v/ac47935303_10"/>
-    <hyperlink ref="F120" r:id="rId45" display="https://www.acfun.cn/v/ac48116488"/>
-    <hyperlink ref="F122" r:id="rId46" display="https://www.acfun.cn/v/ac48116488_2"/>
-    <hyperlink ref="F128" r:id="rId47" display="https://www.acfun.cn/v/ac48116488_3"/>
-    <hyperlink ref="F129" r:id="rId48" display="https://www.acfun.cn/v/ac48116488_4"/>
-    <hyperlink ref="F133" r:id="rId49" display="https://www.acfun.cn/v/ac48116488_5"/>
-    <hyperlink ref="F134" r:id="rId50" display="https://www.acfun.cn/v/ac47934950"/>
-    <hyperlink ref="F135" r:id="rId51" display="https://www.acfun.cn/v/ac47934950_2"/>
-    <hyperlink ref="F136" r:id="rId52" display="https://www.acfun.cn/v/ac47934950_3"/>
-    <hyperlink ref="F138" r:id="rId53" display="https://www.acfun.cn/v/ac47934950_4"/>
-    <hyperlink ref="F140" r:id="rId54" display="https://www.acfun.cn/v/ac47934950_5"/>
-    <hyperlink ref="F141" r:id="rId55" display="https://www.acfun.cn/v/ac47934950_6"/>
-    <hyperlink ref="F142" r:id="rId56" display="https://www.acfun.cn/v/ac47934950_7"/>
-    <hyperlink ref="F143" r:id="rId57" display="https://www.acfun.cn/v/ac47934950_8"/>
-    <hyperlink ref="F149" r:id="rId58" display="https://www.acfun.cn/v/ac47934950_9"/>
-    <hyperlink ref="F168" r:id="rId59" display="https://www.acfun.cn/v/ac47931569" tooltip="https://www.acfun.cn/v/ac47931569"/>
-    <hyperlink ref="F170" r:id="rId60" display="https://www.acfun.cn/v/ac47931569_2"/>
-    <hyperlink ref="F171" r:id="rId61" display="https://www.acfun.cn/v/ac47931569_3"/>
-    <hyperlink ref="F172" r:id="rId62" display="https://www.acfun.cn/v/ac47931569_4"/>
-    <hyperlink ref="F173" r:id="rId63" display="https://www.acfun.cn/v/ac47931569_5"/>
-    <hyperlink ref="F174" r:id="rId64" display="https://www.acfun.cn/v/ac47931569_6"/>
-    <hyperlink ref="F175" r:id="rId65" display="https://www.acfun.cn/v/ac47931569_7"/>
-    <hyperlink ref="F176" r:id="rId66" display="https://www.acfun.cn/v/ac47931569_8"/>
-    <hyperlink ref="F177" r:id="rId67" display="https://www.acfun.cn/v/ac47931569_9"/>
-    <hyperlink ref="F178" r:id="rId68" display="https://www.acfun.cn/v/ac47931569_10"/>
-    <hyperlink ref="F179" r:id="rId69" display="https://www.acfun.cn/v/ac47931603" tooltip="https://www.acfun.cn/v/ac47931603"/>
-    <hyperlink ref="F181" r:id="rId70" display="https://www.acfun.cn/v/ac47931603_2"/>
-    <hyperlink ref="F183" r:id="rId71" display="https://www.acfun.cn/v/ac47931603_3"/>
-    <hyperlink ref="F184" r:id="rId72" display="https://www.acfun.cn/v/ac47931603_4"/>
-    <hyperlink ref="F186" r:id="rId73" display="https://www.acfun.cn/v/ac47931603_5"/>
-    <hyperlink ref="F192" r:id="rId74" display="https://www.acfun.cn/v/ac47931603_6"/>
-    <hyperlink ref="F193" r:id="rId75" display="https://www.acfun.cn/v/ac47931603_7"/>
-    <hyperlink ref="F198" r:id="rId76" display="https://www.acfun.cn/v/ac47931603_8"/>
-    <hyperlink ref="F199" r:id="rId77" display="https://www.acfun.cn/v/ac47933063"/>
-    <hyperlink ref="F201" r:id="rId78" display="https://www.acfun.cn/v/ac47933063_2"/>
-    <hyperlink ref="F202" r:id="rId79" display="https://www.acfun.cn/v/ac47933063_3"/>
-    <hyperlink ref="F203" r:id="rId80" display="https://www.acfun.cn/v/ac47933063_4"/>
-    <hyperlink ref="F204" r:id="rId81" display="https://www.acfun.cn/v/ac47933063_5"/>
-    <hyperlink ref="F206" r:id="rId82" display="https://www.acfun.cn/v/ac47933063_6"/>
-    <hyperlink ref="F207" r:id="rId83" display="https://www.acfun.cn/v/ac47933063_7"/>
-    <hyperlink ref="F208" r:id="rId84" display="https://www.acfun.cn/v/ac47933063_8"/>
-    <hyperlink ref="F209" r:id="rId85" display="https://www.acfun.cn/v/ac47933063_9"/>
-    <hyperlink ref="F211" r:id="rId86" display="https://www.acfun.cn/v/ac47933063_10"/>
-    <hyperlink ref="F213" r:id="rId87" display="https://www.acfun.cn/v/ac48409409_1" tooltip="https://www.acfun.cn/v/ac48409409_1"/>
-    <hyperlink ref="F219" r:id="rId88" display="https://www.acfun.cn/v/ac48409409_2"/>
-    <hyperlink ref="F220" r:id="rId89" display="https://www.acfun.cn/v/ac48409409_3"/>
-    <hyperlink ref="F225" r:id="rId90" display="https://www.acfun.cn/v/ac48409409_4"/>
-    <hyperlink ref="F235" r:id="rId91" display="https://www.acfun.cn/v/ac47931075"/>
-    <hyperlink ref="F236" r:id="rId92" display="https://www.acfun.cn/v/ac47931075_2"/>
-    <hyperlink ref="F238" r:id="rId93" display="https://www.acfun.cn/v/ac47931075_3"/>
-    <hyperlink ref="F240" r:id="rId94" display="https://www.acfun.cn/v/ac47931075_4"/>
-    <hyperlink ref="F241" r:id="rId95" display="https://www.acfun.cn/v/ac47931075_5"/>
-    <hyperlink ref="F242" r:id="rId96" display="https://www.acfun.cn/v/ac47931075_6"/>
-    <hyperlink ref="F244" r:id="rId97" display="https://www.acfun.cn/v/ac47933675"/>
-    <hyperlink ref="F246" r:id="rId98" display="https://www.acfun.cn/v/ac47933675_2"/>
-    <hyperlink ref="F248" r:id="rId99" display="https://www.acfun.cn/v/ac47933675_3"/>
-    <hyperlink ref="F249" r:id="rId100" display="https://www.acfun.cn/v/ac47933675_4"/>
-    <hyperlink ref="F250" r:id="rId101" display="https://www.acfun.cn/v/ac47933675_5"/>
-    <hyperlink ref="F251" r:id="rId102" display="https://www.acfun.cn/v/ac47933675_6"/>
-    <hyperlink ref="F252" r:id="rId103" display="https://www.acfun.cn/v/ac47933675_7"/>
-    <hyperlink ref="F257" r:id="rId104" display="https://www.acfun.cn/v/ac47933675_8"/>
-    <hyperlink ref="F259" r:id="rId105" display="https://www.acfun.cn/v/ac47934854"/>
-    <hyperlink ref="F260" r:id="rId106" display="https://www.acfun.cn/v/ac47934854_2"/>
-    <hyperlink ref="F261" r:id="rId107" display="https://www.acfun.cn/v/ac47934854_3"/>
-    <hyperlink ref="F262" r:id="rId108" display="https://www.acfun.cn/v/ac47934854_4"/>
-    <hyperlink ref="F263" r:id="rId109" display="https://www.acfun.cn/v/ac47934854_5"/>
-    <hyperlink ref="F264" r:id="rId110" display="https://www.acfun.cn/v/ac47934854_6"/>
-    <hyperlink ref="F266" r:id="rId111" display="https://www.acfun.cn/v/ac47934854_7"/>
-    <hyperlink ref="F272" r:id="rId112" display="https://www.acfun.cn/v/ac47934854_8"/>
-    <hyperlink ref="F274" r:id="rId113" display="https://www.acfun.cn/v/ac47933636"/>
-    <hyperlink ref="F275" r:id="rId114" display="https://www.acfun.cn/v/ac47933636_2"/>
-    <hyperlink ref="F276" r:id="rId115" display="https://www.acfun.cn/v/ac47933636_3"/>
-    <hyperlink ref="F277" r:id="rId116" display="https://www.acfun.cn/v/ac47933636_4"/>
-    <hyperlink ref="F278" r:id="rId117" display="https://www.acfun.cn/v/ac47933636_5"/>
-    <hyperlink ref="F279" r:id="rId118" display="https://www.acfun.cn/v/ac47933636_6"/>
+    <hyperlink ref="F2" r:id="rId1" tooltip="https://www.acfun.cn/v/ac47931167" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{00000000-0004-0000-0300-000005000000}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{00000000-0004-0000-0300-000006000000}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{00000000-0004-0000-0300-000007000000}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{00000000-0004-0000-0300-000008000000}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{00000000-0004-0000-0300-000009000000}"/>
+    <hyperlink ref="F18" r:id="rId11" xr:uid="{00000000-0004-0000-0300-00000A000000}"/>
+    <hyperlink ref="F20" r:id="rId12" xr:uid="{00000000-0004-0000-0300-00000B000000}"/>
+    <hyperlink ref="F22" r:id="rId13" xr:uid="{00000000-0004-0000-0300-00000C000000}"/>
+    <hyperlink ref="F23" r:id="rId14" xr:uid="{00000000-0004-0000-0300-00000D000000}"/>
+    <hyperlink ref="F24" r:id="rId15" xr:uid="{00000000-0004-0000-0300-00000E000000}"/>
+    <hyperlink ref="F25" r:id="rId16" xr:uid="{00000000-0004-0000-0300-00000F000000}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{00000000-0004-0000-0300-000010000000}"/>
+    <hyperlink ref="F28" r:id="rId18" xr:uid="{00000000-0004-0000-0300-000011000000}"/>
+    <hyperlink ref="F29" r:id="rId19" xr:uid="{00000000-0004-0000-0300-000012000000}"/>
+    <hyperlink ref="F31" r:id="rId20" xr:uid="{00000000-0004-0000-0300-000013000000}"/>
+    <hyperlink ref="F32" r:id="rId21" xr:uid="{00000000-0004-0000-0300-000014000000}"/>
+    <hyperlink ref="F33" r:id="rId22" xr:uid="{00000000-0004-0000-0300-000015000000}"/>
+    <hyperlink ref="F34" r:id="rId23" xr:uid="{00000000-0004-0000-0300-000016000000}"/>
+    <hyperlink ref="F39" r:id="rId24" xr:uid="{00000000-0004-0000-0300-000017000000}"/>
+    <hyperlink ref="F69" r:id="rId25" xr:uid="{00000000-0004-0000-0300-000018000000}"/>
+    <hyperlink ref="F71" r:id="rId26" xr:uid="{00000000-0004-0000-0300-000019000000}"/>
+    <hyperlink ref="F73" r:id="rId27" xr:uid="{00000000-0004-0000-0300-00001A000000}"/>
+    <hyperlink ref="F74" r:id="rId28" xr:uid="{00000000-0004-0000-0300-00001B000000}"/>
+    <hyperlink ref="F75" r:id="rId29" xr:uid="{00000000-0004-0000-0300-00001C000000}"/>
+    <hyperlink ref="F76" r:id="rId30" xr:uid="{00000000-0004-0000-0300-00001D000000}"/>
+    <hyperlink ref="F77" r:id="rId31" xr:uid="{00000000-0004-0000-0300-00001E000000}"/>
+    <hyperlink ref="F78" r:id="rId32" xr:uid="{00000000-0004-0000-0300-00001F000000}"/>
+    <hyperlink ref="F80" r:id="rId33" xr:uid="{00000000-0004-0000-0300-000020000000}"/>
+    <hyperlink ref="F87" r:id="rId34" xr:uid="{00000000-0004-0000-0300-000021000000}"/>
+    <hyperlink ref="F105" r:id="rId35" xr:uid="{00000000-0004-0000-0300-000022000000}"/>
+    <hyperlink ref="F106" r:id="rId36" xr:uid="{00000000-0004-0000-0300-000023000000}"/>
+    <hyperlink ref="F107" r:id="rId37" xr:uid="{00000000-0004-0000-0300-000024000000}"/>
+    <hyperlink ref="F109" r:id="rId38" xr:uid="{00000000-0004-0000-0300-000025000000}"/>
+    <hyperlink ref="F113" r:id="rId39" xr:uid="{00000000-0004-0000-0300-000026000000}"/>
+    <hyperlink ref="F114" r:id="rId40" xr:uid="{00000000-0004-0000-0300-000027000000}"/>
+    <hyperlink ref="F115" r:id="rId41" xr:uid="{00000000-0004-0000-0300-000028000000}"/>
+    <hyperlink ref="F116" r:id="rId42" xr:uid="{00000000-0004-0000-0300-000029000000}"/>
+    <hyperlink ref="F118" r:id="rId43" xr:uid="{00000000-0004-0000-0300-00002A000000}"/>
+    <hyperlink ref="F119" r:id="rId44" xr:uid="{00000000-0004-0000-0300-00002B000000}"/>
+    <hyperlink ref="F120" r:id="rId45" xr:uid="{00000000-0004-0000-0300-00002C000000}"/>
+    <hyperlink ref="F122" r:id="rId46" xr:uid="{00000000-0004-0000-0300-00002D000000}"/>
+    <hyperlink ref="F128" r:id="rId47" xr:uid="{00000000-0004-0000-0300-00002E000000}"/>
+    <hyperlink ref="F129" r:id="rId48" xr:uid="{00000000-0004-0000-0300-00002F000000}"/>
+    <hyperlink ref="F133" r:id="rId49" xr:uid="{00000000-0004-0000-0300-000030000000}"/>
+    <hyperlink ref="F134" r:id="rId50" xr:uid="{00000000-0004-0000-0300-000031000000}"/>
+    <hyperlink ref="F135" r:id="rId51" xr:uid="{00000000-0004-0000-0300-000032000000}"/>
+    <hyperlink ref="F136" r:id="rId52" xr:uid="{00000000-0004-0000-0300-000033000000}"/>
+    <hyperlink ref="F138" r:id="rId53" xr:uid="{00000000-0004-0000-0300-000034000000}"/>
+    <hyperlink ref="F140" r:id="rId54" xr:uid="{00000000-0004-0000-0300-000035000000}"/>
+    <hyperlink ref="F141" r:id="rId55" xr:uid="{00000000-0004-0000-0300-000036000000}"/>
+    <hyperlink ref="F142" r:id="rId56" xr:uid="{00000000-0004-0000-0300-000037000000}"/>
+    <hyperlink ref="F143" r:id="rId57" xr:uid="{00000000-0004-0000-0300-000038000000}"/>
+    <hyperlink ref="F149" r:id="rId58" xr:uid="{00000000-0004-0000-0300-000039000000}"/>
+    <hyperlink ref="F168" r:id="rId59" tooltip="https://www.acfun.cn/v/ac47931569" xr:uid="{00000000-0004-0000-0300-00003A000000}"/>
+    <hyperlink ref="F170" r:id="rId60" xr:uid="{00000000-0004-0000-0300-00003B000000}"/>
+    <hyperlink ref="F171" r:id="rId61" xr:uid="{00000000-0004-0000-0300-00003C000000}"/>
+    <hyperlink ref="F172" r:id="rId62" xr:uid="{00000000-0004-0000-0300-00003D000000}"/>
+    <hyperlink ref="F173" r:id="rId63" xr:uid="{00000000-0004-0000-0300-00003E000000}"/>
+    <hyperlink ref="F174" r:id="rId64" xr:uid="{00000000-0004-0000-0300-00003F000000}"/>
+    <hyperlink ref="F175" r:id="rId65" xr:uid="{00000000-0004-0000-0300-000040000000}"/>
+    <hyperlink ref="F176" r:id="rId66" xr:uid="{00000000-0004-0000-0300-000041000000}"/>
+    <hyperlink ref="F177" r:id="rId67" xr:uid="{00000000-0004-0000-0300-000042000000}"/>
+    <hyperlink ref="F178" r:id="rId68" xr:uid="{00000000-0004-0000-0300-000043000000}"/>
+    <hyperlink ref="F179" r:id="rId69" tooltip="https://www.acfun.cn/v/ac47931603" xr:uid="{00000000-0004-0000-0300-000044000000}"/>
+    <hyperlink ref="F181" r:id="rId70" xr:uid="{00000000-0004-0000-0300-000045000000}"/>
+    <hyperlink ref="F183" r:id="rId71" xr:uid="{00000000-0004-0000-0300-000046000000}"/>
+    <hyperlink ref="F184" r:id="rId72" xr:uid="{00000000-0004-0000-0300-000047000000}"/>
+    <hyperlink ref="F186" r:id="rId73" xr:uid="{00000000-0004-0000-0300-000048000000}"/>
+    <hyperlink ref="F192" r:id="rId74" xr:uid="{00000000-0004-0000-0300-000049000000}"/>
+    <hyperlink ref="F193" r:id="rId75" xr:uid="{00000000-0004-0000-0300-00004A000000}"/>
+    <hyperlink ref="F198" r:id="rId76" xr:uid="{00000000-0004-0000-0300-00004B000000}"/>
+    <hyperlink ref="F199" r:id="rId77" xr:uid="{00000000-0004-0000-0300-00004C000000}"/>
+    <hyperlink ref="F201" r:id="rId78" xr:uid="{00000000-0004-0000-0300-00004D000000}"/>
+    <hyperlink ref="F202" r:id="rId79" xr:uid="{00000000-0004-0000-0300-00004E000000}"/>
+    <hyperlink ref="F203" r:id="rId80" xr:uid="{00000000-0004-0000-0300-00004F000000}"/>
+    <hyperlink ref="F204" r:id="rId81" xr:uid="{00000000-0004-0000-0300-000050000000}"/>
+    <hyperlink ref="F206" r:id="rId82" xr:uid="{00000000-0004-0000-0300-000051000000}"/>
+    <hyperlink ref="F207" r:id="rId83" xr:uid="{00000000-0004-0000-0300-000052000000}"/>
+    <hyperlink ref="F208" r:id="rId84" xr:uid="{00000000-0004-0000-0300-000053000000}"/>
+    <hyperlink ref="F209" r:id="rId85" xr:uid="{00000000-0004-0000-0300-000054000000}"/>
+    <hyperlink ref="F211" r:id="rId86" xr:uid="{00000000-0004-0000-0300-000055000000}"/>
+    <hyperlink ref="F213" r:id="rId87" tooltip="https://www.acfun.cn/v/ac48409409_1" xr:uid="{00000000-0004-0000-0300-000056000000}"/>
+    <hyperlink ref="F219" r:id="rId88" xr:uid="{00000000-0004-0000-0300-000057000000}"/>
+    <hyperlink ref="F220" r:id="rId89" xr:uid="{00000000-0004-0000-0300-000058000000}"/>
+    <hyperlink ref="F225" r:id="rId90" xr:uid="{00000000-0004-0000-0300-000059000000}"/>
+    <hyperlink ref="F235" r:id="rId91" xr:uid="{00000000-0004-0000-0300-00005A000000}"/>
+    <hyperlink ref="F236" r:id="rId92" xr:uid="{00000000-0004-0000-0300-00005B000000}"/>
+    <hyperlink ref="F238" r:id="rId93" xr:uid="{00000000-0004-0000-0300-00005C000000}"/>
+    <hyperlink ref="F240" r:id="rId94" xr:uid="{00000000-0004-0000-0300-00005D000000}"/>
+    <hyperlink ref="F241" r:id="rId95" xr:uid="{00000000-0004-0000-0300-00005E000000}"/>
+    <hyperlink ref="F242" r:id="rId96" xr:uid="{00000000-0004-0000-0300-00005F000000}"/>
+    <hyperlink ref="F244" r:id="rId97" xr:uid="{00000000-0004-0000-0300-000060000000}"/>
+    <hyperlink ref="F246" r:id="rId98" xr:uid="{00000000-0004-0000-0300-000061000000}"/>
+    <hyperlink ref="F248" r:id="rId99" xr:uid="{00000000-0004-0000-0300-000062000000}"/>
+    <hyperlink ref="F249" r:id="rId100" xr:uid="{00000000-0004-0000-0300-000063000000}"/>
+    <hyperlink ref="F250" r:id="rId101" xr:uid="{00000000-0004-0000-0300-000064000000}"/>
+    <hyperlink ref="F251" r:id="rId102" xr:uid="{00000000-0004-0000-0300-000065000000}"/>
+    <hyperlink ref="F252" r:id="rId103" xr:uid="{00000000-0004-0000-0300-000066000000}"/>
+    <hyperlink ref="F257" r:id="rId104" xr:uid="{00000000-0004-0000-0300-000067000000}"/>
+    <hyperlink ref="F259" r:id="rId105" xr:uid="{00000000-0004-0000-0300-000068000000}"/>
+    <hyperlink ref="F260" r:id="rId106" xr:uid="{00000000-0004-0000-0300-000069000000}"/>
+    <hyperlink ref="F261" r:id="rId107" xr:uid="{00000000-0004-0000-0300-00006A000000}"/>
+    <hyperlink ref="F262" r:id="rId108" xr:uid="{00000000-0004-0000-0300-00006B000000}"/>
+    <hyperlink ref="F263" r:id="rId109" xr:uid="{00000000-0004-0000-0300-00006C000000}"/>
+    <hyperlink ref="F264" r:id="rId110" xr:uid="{00000000-0004-0000-0300-00006D000000}"/>
+    <hyperlink ref="F266" r:id="rId111" xr:uid="{00000000-0004-0000-0300-00006E000000}"/>
+    <hyperlink ref="F272" r:id="rId112" xr:uid="{00000000-0004-0000-0300-00006F000000}"/>
+    <hyperlink ref="F274" r:id="rId113" xr:uid="{00000000-0004-0000-0300-000070000000}"/>
+    <hyperlink ref="F275" r:id="rId114" xr:uid="{00000000-0004-0000-0300-000071000000}"/>
+    <hyperlink ref="F276" r:id="rId115" xr:uid="{00000000-0004-0000-0300-000072000000}"/>
+    <hyperlink ref="F277" r:id="rId116" xr:uid="{00000000-0004-0000-0300-000073000000}"/>
+    <hyperlink ref="F278" r:id="rId117" xr:uid="{00000000-0004-0000-0300-000074000000}"/>
+    <hyperlink ref="F279" r:id="rId118" xr:uid="{00000000-0004-0000-0300-000075000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="52.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="52.453125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="27.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="30.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="28.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="48.0909090909091" customWidth="1"/>
-    <col min="7" max="7" width="13.5454545454545" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" customWidth="1"/>
+    <col min="6" max="6" width="48.08984375" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -11463,7 +10949,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="16" customHeight="1">
       <c r="A7" t="s">
         <v>279</v>
       </c>
@@ -11490,26 +10976,25 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" display="https://www.bilibili.com/video/BV1zPbR6FEo3/"/>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="45.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="10.2727272727273" customWidth="1"/>
-    <col min="3" max="3" width="36.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="16.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="10.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="45.90625" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="45.90625" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -11783,23 +11268,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="45.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="29.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="17.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="13.5454545454545" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="13.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="45.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="45.90625" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -12033,19 +11517,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E115"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="31.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -12648,19 +12131,27 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.9090909090909" style="1" customWidth="1"/>
-    <col min="2" max="2" width="71.8181818181818" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.81640625" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="62.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="111.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -12698,7 +12189,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:11">
+    <row r="2" spans="1:11">
       <c r="A2" s="1">
         <v>45081</v>
       </c>
@@ -12724,7 +12215,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:11">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>674</v>
       </c>
@@ -12750,7 +12241,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:11">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>678</v>
       </c>
@@ -12776,7 +12267,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:11">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>678</v>
       </c>
@@ -12802,7 +12293,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:11">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>678</v>
       </c>
@@ -12828,7 +12319,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:11">
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>685</v>
       </c>
@@ -12854,7 +12345,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:11">
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>685</v>
       </c>
@@ -12880,7 +12371,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:11">
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>691</v>
       </c>
@@ -12906,7 +12397,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:11">
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>691</v>
       </c>
@@ -12932,7 +12423,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:11">
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>696</v>
       </c>
@@ -12958,7 +12449,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:11">
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>696</v>
       </c>
@@ -12984,7 +12475,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:11">
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>701</v>
       </c>
@@ -13010,7 +12501,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:11">
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>701</v>
       </c>
@@ -13036,7 +12527,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:11">
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>706</v>
       </c>
@@ -13062,7 +12553,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:11">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>706</v>
       </c>
@@ -13088,7 +12579,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:10">
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
         <v>711</v>
       </c>
@@ -13114,7 +12605,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:10">
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>711</v>
       </c>
@@ -13140,7 +12631,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:10">
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
         <v>711</v>
       </c>
@@ -13166,7 +12657,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:10">
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
         <v>720</v>
       </c>
@@ -13189,7 +12680,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:10">
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>720</v>
       </c>
@@ -13212,7 +12703,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:10">
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>720</v>
       </c>
@@ -13238,7 +12729,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:10">
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
         <v>729</v>
       </c>
@@ -13261,7 +12752,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:10">
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
         <v>729</v>
       </c>
@@ -13284,7 +12775,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:10">
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
         <v>729</v>
       </c>
@@ -13307,7 +12798,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:10">
+    <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
         <v>729</v>
       </c>
@@ -13330,7 +12821,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:10">
+    <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
         <v>729</v>
       </c>
@@ -13353,7 +12844,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:10">
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
         <v>729</v>
       </c>
@@ -13376,7 +12867,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:10">
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
         <v>729</v>
       </c>
@@ -13399,7 +12890,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:10">
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>729</v>
       </c>
@@ -13425,7 +12916,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:10">
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
         <v>740</v>
       </c>
@@ -13445,7 +12936,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:10">
+    <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
         <v>740</v>
       </c>
@@ -13465,7 +12956,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:10">
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
         <v>740</v>
       </c>
@@ -13485,7 +12976,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:10">
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
         <v>740</v>
       </c>
@@ -13505,7 +12996,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:10">
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
         <v>740</v>
       </c>
@@ -13525,7 +13016,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:10">
+    <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
         <v>740</v>
       </c>
@@ -13545,7 +13036,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:10">
+    <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
         <v>740</v>
       </c>
@@ -13565,7 +13056,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:10">
+    <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
         <v>740</v>
       </c>
@@ -13585,7 +13076,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:10">
+    <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
         <v>740</v>
       </c>
@@ -13608,7 +13099,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:10">
+    <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
         <v>751</v>
       </c>
@@ -13625,7 +13116,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:10">
+    <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
         <v>754</v>
       </c>
@@ -13645,7 +13136,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:10">
+    <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
         <v>754</v>
       </c>
@@ -13665,7 +13156,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:10">
+    <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
         <v>754</v>
       </c>
@@ -13685,7 +13176,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:10">
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>754</v>
       </c>
@@ -13705,7 +13196,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:10">
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
         <v>754</v>
       </c>
@@ -13728,7 +13219,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:10">
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
         <v>761</v>
       </c>
@@ -13751,7 +13242,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:10">
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
         <v>761</v>
       </c>
@@ -13777,7 +13268,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:10">
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
         <v>766</v>
       </c>
@@ -13800,7 +13291,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:10">
+    <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
         <v>766</v>
       </c>
@@ -13823,7 +13314,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:10">
+    <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
         <v>766</v>
       </c>
@@ -13846,7 +13337,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:10">
+    <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
         <v>766</v>
       </c>
@@ -13869,7 +13360,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:10">
+    <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
         <v>766</v>
       </c>
@@ -13895,7 +13386,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:10">
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
         <v>774</v>
       </c>
@@ -13918,7 +13409,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:10">
+    <row r="54" spans="1:10">
       <c r="A54" s="1" t="s">
         <v>774</v>
       </c>
@@ -13944,7 +13435,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:10">
+    <row r="55" spans="1:10">
       <c r="A55" s="1" t="s">
         <v>779</v>
       </c>
@@ -13967,7 +13458,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:10">
+    <row r="56" spans="1:10">
       <c r="A56" s="1" t="s">
         <v>779</v>
       </c>
@@ -13990,7 +13481,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:10">
+    <row r="57" spans="1:10">
       <c r="A57" s="1" t="s">
         <v>779</v>
       </c>
@@ -14013,7 +13504,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:10">
+    <row r="58" spans="1:10">
       <c r="A58" s="1" t="s">
         <v>779</v>
       </c>
@@ -14039,7 +13530,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:10">
+    <row r="59" spans="1:10">
       <c r="A59" s="1" t="s">
         <v>786</v>
       </c>
@@ -14062,7 +13553,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:10">
+    <row r="60" spans="1:10">
       <c r="A60" s="1" t="s">
         <v>786</v>
       </c>
@@ -14085,7 +13576,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:10">
+    <row r="61" spans="1:10">
       <c r="A61" s="1" t="s">
         <v>786</v>
       </c>
@@ -14108,7 +13599,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:10">
+    <row r="62" spans="1:10">
       <c r="A62" s="1" t="s">
         <v>786</v>
       </c>
@@ -14131,7 +13622,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:10">
+    <row r="63" spans="1:10">
       <c r="A63" s="1" t="s">
         <v>786</v>
       </c>
@@ -14151,7 +13642,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:10">
+    <row r="64" spans="1:10">
       <c r="A64" s="1" t="s">
         <v>793</v>
       </c>
@@ -14174,7 +13665,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:10">
+    <row r="65" spans="1:10">
       <c r="A65" s="1" t="s">
         <v>793</v>
       </c>
@@ -14197,7 +13688,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:10">
+    <row r="66" spans="1:10">
       <c r="A66" s="1" t="s">
         <v>793</v>
       </c>
@@ -14220,7 +13711,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:10">
+    <row r="67" spans="1:10">
       <c r="A67" s="1" t="s">
         <v>793</v>
       </c>
@@ -14243,7 +13734,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:10">
+    <row r="68" spans="1:10">
       <c r="A68" s="1" t="s">
         <v>793</v>
       </c>
@@ -14266,7 +13757,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:10">
+    <row r="69" spans="1:10">
       <c r="A69" s="1" t="s">
         <v>793</v>
       </c>
@@ -14289,7 +13780,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:10">
+    <row r="70" spans="1:10">
       <c r="A70" s="1" t="s">
         <v>793</v>
       </c>
@@ -14315,7 +13806,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:10">
+    <row r="71" spans="1:10">
       <c r="A71" s="1" t="s">
         <v>793</v>
       </c>
@@ -14338,7 +13829,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:10">
+    <row r="72" spans="1:10">
       <c r="A72" s="1">
         <v>45652</v>
       </c>
@@ -14364,7 +13855,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:10">
+    <row r="73" spans="1:10">
       <c r="A73" s="1">
         <v>45652</v>
       </c>
@@ -14390,7 +13881,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:10">
+    <row r="74" spans="1:10">
       <c r="A74" s="1">
         <v>45652</v>
       </c>
@@ -14416,7 +13907,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:10">
+    <row r="75" spans="1:10">
       <c r="A75" s="1">
         <v>45652</v>
       </c>
@@ -14442,7 +13933,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:10">
+    <row r="76" spans="1:10">
       <c r="A76" s="1">
         <v>45301</v>
       </c>
@@ -14465,7 +13956,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:10">
+    <row r="77" spans="1:10">
       <c r="A77" s="1">
         <v>45301</v>
       </c>
@@ -14488,7 +13979,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:10">
+    <row r="78" spans="1:10">
       <c r="A78" s="1">
         <v>45301</v>
       </c>
@@ -14514,7 +14005,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:10">
+    <row r="79" spans="1:10">
       <c r="A79" s="1">
         <v>45290</v>
       </c>
@@ -14540,7 +14031,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:10">
+    <row r="80" spans="1:10">
       <c r="A80" s="1">
         <v>45290</v>
       </c>
@@ -14566,7 +14057,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:11">
+    <row r="81" spans="1:11">
       <c r="A81" s="1">
         <v>45298</v>
       </c>
@@ -14592,7 +14083,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:11">
+    <row r="82" spans="1:11">
       <c r="A82" s="1">
         <v>45298</v>
       </c>
@@ -14618,7 +14109,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:11">
+    <row r="83" spans="1:11">
       <c r="A83" s="1">
         <v>45406</v>
       </c>
@@ -14644,7 +14135,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:11">
+    <row r="84" spans="1:11">
       <c r="A84" s="1">
         <v>45406</v>
       </c>
@@ -14670,7 +14161,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:11">
+    <row r="85" spans="1:11">
       <c r="A85" s="1">
         <v>45406</v>
       </c>
@@ -14696,7 +14187,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:11">
+    <row r="86" spans="1:11">
       <c r="A86" s="1">
         <v>45451</v>
       </c>
@@ -14722,7 +14213,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:11">
+    <row r="87" spans="1:11">
       <c r="A87" s="1">
         <v>45451</v>
       </c>
@@ -14748,7 +14239,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:11">
+    <row r="88" spans="1:11">
       <c r="A88" s="1">
         <v>45451</v>
       </c>
@@ -14774,7 +14265,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:11">
+    <row r="89" spans="1:11">
       <c r="A89" s="1">
         <v>45480</v>
       </c>
@@ -14800,7 +14291,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:11">
+    <row r="90" spans="1:11">
       <c r="A90" s="1">
         <v>45578</v>
       </c>
@@ -14826,7 +14317,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:11">
+    <row r="91" spans="1:11">
       <c r="A91" s="1">
         <v>45578</v>
       </c>
@@ -14852,7 +14343,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:11">
+    <row r="92" spans="1:11">
       <c r="A92" s="1">
         <v>45578</v>
       </c>
@@ -14878,7 +14369,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:11">
+    <row r="93" spans="1:11">
       <c r="A93" s="1">
         <v>45360</v>
       </c>
@@ -14901,7 +14392,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:11">
+    <row r="94" spans="1:11">
       <c r="A94" s="1">
         <v>45486</v>
       </c>
@@ -14930,7 +14421,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:11">
+    <row r="95" spans="1:11">
       <c r="A95" s="1">
         <v>45486</v>
       </c>
@@ -14959,7 +14450,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:11">
+    <row r="96" spans="1:11">
       <c r="A96" s="1">
         <v>45487</v>
       </c>
@@ -14979,7 +14470,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:10">
+    <row r="97" spans="1:10">
       <c r="A97" s="1">
         <v>45534</v>
       </c>
@@ -15005,7 +14496,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:10">
+    <row r="98" spans="1:10">
       <c r="A98" s="1">
         <v>45534</v>
       </c>
@@ -15083,7 +14574,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:10">
+    <row r="101" spans="1:10">
       <c r="A101" s="1">
         <v>45389</v>
       </c>
@@ -15109,7 +14600,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:10">
+    <row r="102" spans="1:10">
       <c r="A102" s="1">
         <v>45389</v>
       </c>
@@ -15135,7 +14626,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:10">
+    <row r="103" spans="1:10">
       <c r="A103" s="1">
         <v>45430</v>
       </c>
@@ -15161,7 +14652,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:10">
+    <row r="104" spans="1:10">
       <c r="A104" s="1">
         <v>45430</v>
       </c>
@@ -15187,7 +14678,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:10">
+    <row r="105" spans="1:10">
       <c r="A105" s="1">
         <v>45458</v>
       </c>
@@ -15213,7 +14704,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:10">
+    <row r="106" spans="1:10">
       <c r="A106" s="1">
         <v>45458</v>
       </c>
@@ -15239,7 +14730,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:10">
+    <row r="107" spans="1:10">
       <c r="A107" s="1">
         <v>45481</v>
       </c>
@@ -15265,7 +14756,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:10">
+    <row r="108" spans="1:10">
       <c r="A108" s="1">
         <v>45481</v>
       </c>
@@ -15291,7 +14782,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:10">
+    <row r="109" spans="1:10">
       <c r="A109" s="1">
         <v>45534</v>
       </c>
@@ -15317,7 +14808,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:10">
+    <row r="110" spans="1:10">
       <c r="A110" s="1">
         <v>45534</v>
       </c>
@@ -15343,7 +14834,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:10">
+    <row r="111" spans="1:10">
       <c r="A111" s="1">
         <v>45567</v>
       </c>
@@ -15369,7 +14860,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:10">
+    <row r="112" spans="1:10">
       <c r="A112" s="1">
         <v>45567</v>
       </c>
@@ -15395,7 +14886,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:10">
+    <row r="113" spans="1:10">
       <c r="A113" s="1">
         <v>45567</v>
       </c>
@@ -15421,7 +14912,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:10">
+    <row r="114" spans="1:10">
       <c r="A114" s="1">
         <v>45567</v>
       </c>
@@ -15447,7 +14938,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:10">
+    <row r="115" spans="1:10">
       <c r="A115" s="1">
         <v>45567</v>
       </c>
@@ -15473,7 +14964,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:10">
+    <row r="116" spans="1:10">
       <c r="A116" s="1">
         <v>45483</v>
       </c>
@@ -15499,7 +14990,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:10">
+    <row r="117" spans="1:10">
       <c r="A117" s="1">
         <v>45483</v>
       </c>
@@ -15525,7 +15016,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:10">
+    <row r="118" spans="1:10">
       <c r="A118" s="1">
         <v>45483</v>
       </c>
@@ -15551,7 +15042,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:10">
+    <row r="119" spans="1:10">
       <c r="A119" s="1">
         <v>45640</v>
       </c>
@@ -15577,7 +15068,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:10">
+    <row r="120" spans="1:10">
       <c r="A120" s="1">
         <v>45640</v>
       </c>
@@ -15590,7 +15081,7 @@
       <c r="D120" t="s">
         <v>915</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="13" t="s">
         <v>870</v>
       </c>
       <c r="F120" t="s">
@@ -15603,7 +15094,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:10">
+    <row r="121" spans="1:10">
       <c r="A121" s="1">
         <v>45641</v>
       </c>
@@ -15629,7 +15120,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:10">
+    <row r="122" spans="1:10">
       <c r="A122" s="1">
         <v>45641</v>
       </c>
@@ -15655,7 +15146,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:10">
+    <row r="123" spans="1:10">
       <c r="A123" s="1">
         <v>45641</v>
       </c>
@@ -15681,7 +15172,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:10">
+    <row r="124" spans="1:10">
       <c r="A124" s="1">
         <v>45619</v>
       </c>
@@ -15704,7 +15195,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:10">
+    <row r="125" spans="1:10">
       <c r="A125" s="1">
         <v>45619</v>
       </c>
@@ -15727,7 +15218,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:10">
+    <row r="126" spans="1:10">
       <c r="A126" s="1">
         <v>45627</v>
       </c>
@@ -15754,15 +15245,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K126" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Ave Mujica 作为开场嘉宾出演 Roselia「Farbe」"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:K126" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/_data/data.xlsx
+++ b/_data/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yumin\web\MujicaTimeLineWeb\_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mujicatimelineweb\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51900C3-62B4-4D01-9D56-FB7BD35D4EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="3" activeTab="9"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="announcements" sheetId="1" r:id="rId1"/>
@@ -25,11 +26,12 @@
     <sheet name="discography_releases" sheetId="11" r:id="rId11"/>
     <sheet name="discography_editions" sheetId="12" r:id="rId12"/>
     <sheet name="discography_contents" sheetId="13" r:id="rId13"/>
+    <sheet name="discography_bonus_contents" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">lives!$A$1:$H$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">song_comments!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">song_live_history!$A$1:$F$468</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">lives!$A$1:$H$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">timeline!$A$1:$J$268</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,8 +43,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7087" uniqueCount="1919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6947" uniqueCount="1892">
   <si>
     <t>date</t>
   </si>
@@ -5872,27 +5872,9 @@
     <t>label</t>
   </si>
   <si>
-    <t>chart_first_week</t>
-  </si>
-  <si>
-    <t>chart_peak</t>
-  </si>
-  <si>
-    <t>chart_weeks</t>
-  </si>
-  <si>
-    <t>chart_total</t>
-  </si>
-  <si>
     <t>chart_source</t>
   </si>
   <si>
-    <t>alea-jacta-est</t>
-  </si>
-  <si>
-    <t>2023/09/13</t>
-  </si>
-  <si>
     <t>MINI ALBUM</t>
   </si>
   <si>
@@ -5902,90 +5884,12 @@
     <t>BUSHIROAD MUSIC</t>
   </si>
   <si>
-    <t>Ave Mujica 的首张实体 CD 作品。</t>
-  </si>
-  <si>
-    <t>Alea 首专 mini album</t>
-  </si>
-  <si>
-    <t>4,299</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
     <t>ORICON WEEKLY ALBUM RANKING</t>
   </si>
   <si>
-    <t>elements</t>
-  </si>
-  <si>
-    <t>2024/10/02</t>
-  </si>
-  <si>
-    <t>收录 Symbol 系列与新曲的迷你专辑。</t>
-  </si>
-  <si>
-    <t>元素专 mini album</t>
-  </si>
-  <si>
-    <t>6,940</t>
-  </si>
-  <si>
-    <t>#5</t>
-  </si>
-  <si>
-    <t>completeness</t>
-  </si>
-  <si>
-    <t>2025/04/23</t>
-  </si>
-  <si>
-    <t>1ST ALBUM</t>
-  </si>
-  <si>
-    <t>Ave Mujica 首张专辑。</t>
-  </si>
-  <si>
-    <t>首专 album 完满</t>
-  </si>
-  <si>
-    <t>26,832</t>
-  </si>
-  <si>
-    <t>#7</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>anime-bluray-1</t>
-  </si>
-  <si>
-    <t>TV动画「BanG Dream! Ave Mujica」Blu-ray 上卷</t>
-  </si>
-  <si>
-    <t>TVアニメ「BanG Dream! Ave Mujica」Blu-ray 上巻</t>
-  </si>
-  <si>
-    <t>2025/05/28</t>
-  </si>
-  <si>
-    <t>ANIME BLU-RAY</t>
-  </si>
-  <si>
-    <t>BLU-RAY,CD</t>
-  </si>
-  <si>
-    <t>TV 动画的实体 Blu-ray 发行。</t>
-  </si>
-  <si>
-    <t>images/动画mjcBD.webp</t>
-  </si>
-  <si>
-    <t>动画 blu ray 上卷</t>
-  </si>
-  <si>
     <t>edition_name</t>
   </si>
   <si>
@@ -6025,200 +5929,253 @@
     <t>Blu-ray付生産限定盤</t>
   </si>
   <si>
-    <t>初回限定盘</t>
-  </si>
-  <si>
-    <t>BRMM-10671</t>
-  </si>
-  <si>
-    <t>¥9,900</t>
-  </si>
-  <si>
     <t>CD + Blu-ray</t>
   </si>
   <si>
     <t>一般流通</t>
   </si>
   <si>
-    <t>生产限定</t>
-  </si>
-  <si>
-    <t>0th LIVE 完整影像|Music Video × 2|初回生产限定封入特典</t>
-  </si>
-  <si>
     <t>通常盤</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>disc_no</t>
+  </si>
+  <si>
+    <t>disc_type</t>
+  </si>
+  <si>
+    <t>track_no</t>
+  </si>
+  <si>
+    <t>content_title</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>BLU-RAY</t>
+  </si>
+  <si>
+    <t>kaminonawo</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>以神之名…</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>神の名を</t>
+  </si>
+  <si>
+    <t>收录电影「BanG Dream! Ave Mujica prima aurora」插入歌的迷你专辑</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>release_date</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/神名通常.webp</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>神名 电影</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>chart_first_day_rank</t>
+  </si>
+  <si>
+    <t>chart_first_week_sales</t>
+  </si>
+  <si>
+    <t>chart_first_week_rank</t>
+  </si>
+  <si>
+    <t>chart_total_sales</t>
+  </si>
+  <si>
+    <t>特装盘</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定盘</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
     <t>通常盘</t>
-  </si>
-  <si>
-    <t>BRMM-10672</t>
-  </si>
-  <si>
-    <t>¥2,970</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>初回生产限定封入特典</t>
-  </si>
-  <si>
-    <t>特装限定盤</t>
-  </si>
-  <si>
-    <t>特装限定盘</t>
-  </si>
-  <si>
-    <t>BRMM-10835</t>
-  </si>
-  <si>
-    <t>¥13,200</t>
-  </si>
-  <si>
-    <t>店铺 / 会场限定</t>
-  </si>
-  <si>
-    <t>数量限定</t>
-  </si>
-  <si>
-    <t>特制 BOX|硅胶手环特别色|最速先行抽选申请券</t>
-  </si>
-  <si>
-    <t>BRMM-10836</t>
-  </si>
-  <si>
-    <t>演唱会 Blu-ray|最速先行抽选申请券</t>
-  </si>
-  <si>
-    <t>BRMM-10837</t>
-  </si>
-  <si>
-    <t>¥2,420</t>
-  </si>
-  <si>
-    <t>5000枚限定生産特装盤</t>
-  </si>
-  <si>
-    <t>BRMM-10915</t>
-  </si>
-  <si>
-    <t>¥17,600</t>
-  </si>
-  <si>
-    <t>images/精选特装.webp</t>
-  </si>
-  <si>
-    <t>5,000 枚限定</t>
-  </si>
-  <si>
-    <t>特制收藏 BOX|限定附属物|最速先行抽选申请券</t>
-  </si>
-  <si>
-    <t>BRMM-10916</t>
-  </si>
-  <si>
-    <t>¥10,450</t>
-  </si>
-  <si>
-    <t>images/精选BD.webp</t>
-  </si>
-  <si>
-    <t>BRMM-10917</t>
-  </si>
-  <si>
-    <t>BRMM-10924</t>
-  </si>
-  <si>
-    <t>¥19,800</t>
-  </si>
-  <si>
-    <t>Blu-ray + CD</t>
-  </si>
-  <si>
-    <t>特典 CD|特制小册子|初回生产限定封入特典</t>
-  </si>
-  <si>
-    <t>disc_no</t>
-  </si>
-  <si>
-    <t>disc_type</t>
-  </si>
-  <si>
-    <t>track_no</t>
-  </si>
-  <si>
-    <t>content_title</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRMM-11071</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRMM-11072</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRMM-11073</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/神名5000限.webp</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/神名限定.webp</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/神名通常.webp</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>CD + Blu-ray + Goods</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bushroad Online Shop / 会场限定</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,000枚限定生産特装盤</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,000枚限定</t>
+  </si>
+  <si>
+    <t>新曲「标题未公开」</t>
   </si>
   <si>
     <t>duration</t>
-  </si>
-  <si>
-    <t>note</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>03</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ave Mujica LIVE TOUR 2026「Exitus」-FINAL- DAY2</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>特制立牌5枚|特制BOX|2027春Oml最速先行抽选券|角色卡片|先着购入活动特典CD</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>特制纸套包装|2027春Oml最速先行抽选券|角色卡片|店铺限定特典CD|店铺限定特典Goods</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027春Oml最速先行抽选券|角色卡片|店铺限定特典CD|店铺限定特典Goods</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>cover_gallery</t>
+  </si>
+  <si>
+    <t>bonus_id</t>
+  </si>
+  <si>
+    <t>disc_name</t>
+  </si>
+  <si>
+    <t>先着活动&amp;店铺限定特典CD</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Doloris ver.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>BLU-RAY</t>
-  </si>
-  <si>
-    <t>演唱会影像</t>
-  </si>
-  <si>
-    <t>Symbol I : Earth</t>
-  </si>
-  <si>
-    <t>Symbol III : Water</t>
-  </si>
-  <si>
-    <t>Symbol IV : Fire</t>
-  </si>
-  <si>
-    <t>Ave Mujica 2nd LIVE「Quaerere Lumina」</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>天球のMúsica</t>
-  </si>
-  <si>
-    <t>TV动画 Episodes 01–07</t>
-  </si>
-  <si>
-    <t>Anime Ver.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mortis ver.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Timoris ver.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amoris ver.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oblivionis ver.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ave Mujica(Exitus ver.)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>素晴らしき世界 でも どこにもない場所</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>神さま、バカ</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choir 'S' Choir</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Georgette Me, Georgette You</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>素晴らしき世界 でも どこにもない場所(Exitus ver.)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>神さま、バカ(Exitus ver.)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choir 'S' Choir(Exitus ver.)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Georgette Me, Georgette You(Exitus ver.)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/神名限定.webp|images/神名限定cover.webp</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6246,13 +6203,13 @@
       <sz val="13"/>
       <color rgb="FF0F1419"/>
       <name val="MS Gothic"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -6265,7 +6222,7 @@
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -6283,170 +6240,51 @@
       <sz val="9.75"/>
       <color rgb="FF9599A6"/>
       <name val="Courier New"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="initial"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9.35"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans SC"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF131313"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6465,194 +6303,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -6660,265 +6312,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6937,14 +6350,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6956,7 +6369,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -6976,62 +6389,22 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -7316,17 +6689,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="117.181818181818" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="117.1796875" customWidth="1"/>
     <col min="3" max="3" width="9" style="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7518,22 +6892,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="43.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="24.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="23.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="43.26953125" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
     <col min="4" max="4" width="74" customWidth="1"/>
-    <col min="5" max="5" width="27.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7775,16 +7149,28 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="28.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.26953125" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
@@ -7796,8 +7182,8 @@
       <c r="C1" t="s">
         <v>1804</v>
       </c>
-      <c r="D1" t="s">
-        <v>39</v>
+      <c r="D1" s="37" t="s">
+        <v>1845</v>
       </c>
       <c r="E1" t="s">
         <v>41</v>
@@ -7818,280 +7204,167 @@
         <v>50</v>
       </c>
       <c r="K1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1851</v>
+      </c>
+      <c r="O1" t="s">
         <v>1807</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46316</v>
+      </c>
+      <c r="E2" t="s">
         <v>1808</v>
       </c>
-      <c r="M1" t="s">
+      <c r="F2" t="s">
         <v>1809</v>
       </c>
-      <c r="N1" t="s">
+      <c r="G2" t="s">
         <v>1810</v>
       </c>
-      <c r="O1" t="s">
+      <c r="H2" s="37" t="s">
+        <v>1844</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>1846</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K2" t="s">
         <v>1811</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
+      <c r="L2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="O2" t="s">
         <v>1812</v>
       </c>
-      <c r="B2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1813</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1814</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1815</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1816</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1818</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="N2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="O2" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1814</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1815</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1816</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1824</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1555</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1825</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1826</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1827</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1820</v>
-      </c>
-      <c r="N3" t="s">
-        <v>1820</v>
-      </c>
-      <c r="O3" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1829</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1830</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1815</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1816</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1831</v>
-      </c>
-      <c r="I4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1832</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1833</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1834</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1835</v>
-      </c>
-      <c r="N4" t="s">
-        <v>1820</v>
-      </c>
-      <c r="O4" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1837</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1838</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1839</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1840</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1841</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1816</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1842</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1843</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1844</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="51.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>1803</v>
       </c>
       <c r="B1" t="s">
-        <v>1845</v>
+        <v>1813</v>
       </c>
       <c r="C1" t="s">
-        <v>1846</v>
+        <v>1814</v>
       </c>
       <c r="D1" t="s">
-        <v>1847</v>
+        <v>1815</v>
       </c>
       <c r="E1" t="s">
-        <v>1848</v>
+        <v>1816</v>
       </c>
       <c r="F1" t="s">
         <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>1849</v>
+        <v>1817</v>
       </c>
       <c r="H1" t="s">
-        <v>1850</v>
+        <v>1818</v>
       </c>
       <c r="I1" t="s">
-        <v>1851</v>
+        <v>1819</v>
       </c>
       <c r="J1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>1852</v>
       </c>
-      <c r="K1" t="s">
-        <v>1853</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1854</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="D2" s="37" t="s">
         <v>1855</v>
       </c>
-      <c r="N1" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>1812</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="E2" s="39">
+        <v>18700</v>
+      </c>
+      <c r="F2" s="37" t="s">
         <v>1858</v>
       </c>
-      <c r="D2" t="s">
-        <v>1859</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1860</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1491</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G2" s="37" t="s">
         <v>1861</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="37" t="s">
         <v>1862</v>
       </c>
       <c r="I2" t="s">
-        <v>1863</v>
-      </c>
-      <c r="J2" t="s">
         <v>1864</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>1869</v>
       </c>
       <c r="K2" t="s">
         <v>411</v>
@@ -8100,48 +7373,49 @@
         <v>411</v>
       </c>
       <c r="M2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="N2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>1812</v>
+        <v>411</v>
+      </c>
+      <c r="O2" s="37"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="37" t="s">
+        <v>1841</v>
       </c>
       <c r="B3" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1867</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1868</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1493</v>
+        <v>1825</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E3" s="39">
+        <v>8800</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>1859</v>
       </c>
       <c r="G3" t="s">
-        <v>1869</v>
+        <v>1826</v>
       </c>
       <c r="H3" t="s">
-        <v>1862</v>
+        <v>1827</v>
       </c>
       <c r="I3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="J3" s="37" t="s">
         <v>1870</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1871</v>
       </c>
       <c r="K3" t="s">
         <v>411</v>
       </c>
       <c r="L3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="M3" t="s">
         <v>416</v>
@@ -8149,837 +7423,547 @@
       <c r="N3" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>1822</v>
+      <c r="O3" s="37" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="37" t="s">
+        <v>1841</v>
       </c>
       <c r="B4" t="s">
-        <v>1872</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1873</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1874</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1875</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1549</v>
+        <v>1828</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E4" s="39">
+        <v>2200</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>1860</v>
       </c>
       <c r="G4" t="s">
-        <v>1861</v>
+        <v>1829</v>
       </c>
       <c r="H4" t="s">
-        <v>1876</v>
+        <v>1827</v>
       </c>
       <c r="I4" t="s">
-        <v>1877</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1878</v>
+        <v>1830</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>1871</v>
       </c>
       <c r="K4" t="s">
         <v>411</v>
       </c>
       <c r="L4" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="M4" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="N4" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1879</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1860</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1553</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1861</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1862</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1863</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1880</v>
-      </c>
-      <c r="K5" t="s">
-        <v>411</v>
-      </c>
-      <c r="L5" t="s">
-        <v>411</v>
-      </c>
-      <c r="M5" t="s">
         <v>416</v>
       </c>
-      <c r="N5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1881</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1882</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1555</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1862</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1870</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1871</v>
-      </c>
-      <c r="K6" t="s">
-        <v>411</v>
-      </c>
-      <c r="L6" t="s">
-        <v>416</v>
-      </c>
-      <c r="M6" t="s">
-        <v>416</v>
-      </c>
-      <c r="N6" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1883</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1873</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1884</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1885</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1886</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1861</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1862</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1887</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1888</v>
-      </c>
-      <c r="K7" t="s">
-        <v>411</v>
-      </c>
-      <c r="L7" t="s">
-        <v>411</v>
-      </c>
-      <c r="M7" t="s">
-        <v>411</v>
-      </c>
-      <c r="N7" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1889</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1891</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1861</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1862</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1863</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1880</v>
-      </c>
-      <c r="K8" t="s">
-        <v>411</v>
-      </c>
-      <c r="L8" t="s">
-        <v>411</v>
-      </c>
-      <c r="M8" t="s">
-        <v>416</v>
-      </c>
-      <c r="N8" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1892</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1868</v>
-      </c>
-      <c r="F9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1862</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1870</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1871</v>
-      </c>
-      <c r="K9" t="s">
-        <v>411</v>
-      </c>
-      <c r="L9" t="s">
-        <v>416</v>
-      </c>
-      <c r="M9" t="s">
-        <v>416</v>
-      </c>
-      <c r="N9" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1893</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1894</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1843</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1862</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1870</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1896</v>
-      </c>
-      <c r="K10" t="s">
-        <v>411</v>
-      </c>
-      <c r="L10" t="s">
-        <v>411</v>
-      </c>
-      <c r="M10" t="s">
-        <v>416</v>
-      </c>
-      <c r="N10" t="s">
-        <v>416</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>1803</v>
       </c>
       <c r="B1" t="s">
-        <v>1845</v>
+        <v>1813</v>
       </c>
       <c r="C1" t="s">
-        <v>1897</v>
+        <v>1831</v>
       </c>
       <c r="D1" t="s">
-        <v>1898</v>
+        <v>1832</v>
       </c>
       <c r="E1" t="s">
-        <v>1899</v>
+        <v>1833</v>
       </c>
       <c r="F1" t="s">
         <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>1900</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1901</v>
+        <v>1834</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>1866</v>
       </c>
       <c r="I1" t="s">
-        <v>1902</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>1812</v>
+      <c r="A2" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>1863</v>
       </c>
       <c r="C2" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D2" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E2" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>1812</v>
+      <c r="A3" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>1863</v>
       </c>
       <c r="C3" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D3" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E3" t="s">
-        <v>1904</v>
+        <v>1837</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>1812</v>
+      <c r="A4" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>1863</v>
       </c>
       <c r="C4" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D4" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E4" t="s">
-        <v>1905</v>
+        <v>1838</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>1812</v>
+      <c r="A5" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>1863</v>
       </c>
       <c r="C5" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D5" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E5" t="s">
-        <v>1906</v>
+        <v>1839</v>
       </c>
       <c r="F5" t="s">
-        <v>131</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>1812</v>
+      <c r="A6" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>1863</v>
       </c>
       <c r="C6" t="s">
-        <v>1903</v>
+        <v>1837</v>
       </c>
       <c r="D6" t="s">
-        <v>1869</v>
+        <v>1840</v>
       </c>
       <c r="E6" t="s">
-        <v>1907</v>
-      </c>
-      <c r="F6" t="s">
-        <v>138</v>
+        <v>1836</v>
+      </c>
+      <c r="G6" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>1812</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1903</v>
+      <c r="A7" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>1867</v>
       </c>
       <c r="D7" t="s">
-        <v>1869</v>
+        <v>1840</v>
       </c>
       <c r="E7" t="s">
-        <v>1908</v>
-      </c>
-      <c r="F7" t="s">
-        <v>145</v>
+        <v>1836</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>1868</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>1812</v>
+      <c r="A8" s="37" t="s">
+        <v>1841</v>
       </c>
       <c r="B8" t="s">
-        <v>1857</v>
+        <v>1825</v>
       </c>
       <c r="C8" t="s">
-        <v>1904</v>
+        <v>1836</v>
       </c>
       <c r="D8" t="s">
-        <v>1909</v>
+        <v>1829</v>
       </c>
       <c r="E8" t="s">
-        <v>1903</v>
-      </c>
-      <c r="G8" t="s">
-        <v>437</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1910</v>
+        <v>1836</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1865</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>1822</v>
+      <c r="A9" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1825</v>
       </c>
       <c r="C9" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D9" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E9" t="s">
-        <v>1903</v>
+        <v>1837</v>
       </c>
       <c r="F9" t="s">
-        <v>1911</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>1822</v>
+      <c r="A10" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1825</v>
       </c>
       <c r="C10" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D10" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E10" t="s">
-        <v>1904</v>
+        <v>1838</v>
       </c>
       <c r="F10" t="s">
-        <v>179</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>1822</v>
+      <c r="A11" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1825</v>
       </c>
       <c r="C11" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D11" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E11" t="s">
-        <v>1905</v>
+        <v>1839</v>
       </c>
       <c r="F11" t="s">
-        <v>1912</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>1822</v>
+      <c r="A12" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1825</v>
       </c>
       <c r="C12" t="s">
-        <v>1903</v>
+        <v>1837</v>
       </c>
       <c r="D12" t="s">
-        <v>1869</v>
+        <v>1840</v>
       </c>
       <c r="E12" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1913</v>
+        <v>1836</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>1868</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>1822</v>
+      <c r="A13" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1828</v>
       </c>
       <c r="C13" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D13" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E13" t="s">
-        <v>1907</v>
+        <v>1836</v>
       </c>
       <c r="F13" t="s">
-        <v>196</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>1822</v>
+      <c r="A14" s="37" t="s">
+        <v>1841</v>
       </c>
       <c r="B14" t="s">
-        <v>1857</v>
+        <v>1828</v>
       </c>
       <c r="C14" t="s">
-        <v>1904</v>
+        <v>1836</v>
       </c>
       <c r="D14" t="s">
-        <v>1909</v>
+        <v>1829</v>
       </c>
       <c r="E14" t="s">
-        <v>1903</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1914</v>
-      </c>
-      <c r="I14" t="s">
-        <v>1910</v>
+        <v>1837</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1865</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" t="s">
+      <c r="A15" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B15" t="s">
         <v>1828</v>
       </c>
       <c r="C15" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D15" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E15" t="s">
-        <v>1903</v>
+        <v>1838</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" t="s">
+      <c r="A16" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B16" t="s">
         <v>1828</v>
       </c>
       <c r="C16" t="s">
-        <v>1903</v>
+        <v>1836</v>
       </c>
       <c r="D16" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="E16" t="s">
-        <v>1904</v>
+        <v>1839</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1869</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1905</v>
-      </c>
-      <c r="F17" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1869</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1869</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1907</v>
-      </c>
-      <c r="F19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1869</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1908</v>
-      </c>
-      <c r="F20" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1869</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1915</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1904</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1909</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1903</v>
-      </c>
-      <c r="G22" t="s">
-        <v>213</v>
-      </c>
-      <c r="I22" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1883</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1904</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1909</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1903</v>
-      </c>
-      <c r="G23" t="s">
-        <v>213</v>
-      </c>
-      <c r="I23" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>1836</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1909</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1903</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>1836</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1904</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1869</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1903</v>
-      </c>
-      <c r="F25" t="s">
-        <v>210</v>
-      </c>
-      <c r="I25" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>1836</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1904</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1869</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1904</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1918</v>
+        <v>1865</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="37" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:P32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="29.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="57.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="11.3636363636364" customWidth="1"/>
+    <col min="1" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="57.90625" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
     <col min="5" max="5" width="20" style="17" customWidth="1"/>
-    <col min="6" max="6" width="23.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="9.27272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="38.3636363636364" customWidth="1"/>
-    <col min="10" max="10" width="35.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="55.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="51.3636363636364" customWidth="1"/>
-    <col min="13" max="14" width="50.6363636363636" customWidth="1"/>
-    <col min="15" max="15" width="51.3636363636364" customWidth="1"/>
-    <col min="16" max="16" width="21.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="23.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" customWidth="1"/>
+    <col min="9" max="9" width="38.36328125" customWidth="1"/>
+    <col min="10" max="10" width="35.1796875" customWidth="1"/>
+    <col min="11" max="11" width="55.6328125" customWidth="1"/>
+    <col min="12" max="12" width="51.36328125" customWidth="1"/>
+    <col min="13" max="14" width="50.6328125" customWidth="1"/>
+    <col min="15" max="15" width="51.36328125" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -9036,8 +8020,8 @@
       <c r="A2" t="s">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
-        <v>51</v>
+      <c r="B2" s="37" t="s">
+        <v>1886</v>
       </c>
       <c r="C2" t="s">
         <v>52</v>
@@ -9282,7 +8266,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:16">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -9386,8 +8370,8 @@
       <c r="A9" t="s">
         <v>123</v>
       </c>
-      <c r="B9" t="s">
-        <v>123</v>
+      <c r="B9" s="37" t="s">
+        <v>1885</v>
       </c>
       <c r="C9" t="s">
         <v>65</v>
@@ -9436,8 +8420,8 @@
       <c r="A10" t="s">
         <v>130</v>
       </c>
-      <c r="B10" t="s">
-        <v>131</v>
+      <c r="B10" s="37" t="s">
+        <v>1884</v>
       </c>
       <c r="C10" t="s">
         <v>65</v>
@@ -9586,8 +8570,8 @@
       <c r="A13" t="s">
         <v>155</v>
       </c>
-      <c r="B13" t="s">
-        <v>156</v>
+      <c r="B13" s="37" t="s">
+        <v>1883</v>
       </c>
       <c r="C13" t="s">
         <v>65</v>
@@ -9732,7 +8716,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="16" ht="14.5" customHeight="1" spans="1:16">
+    <row r="16" spans="1:16" ht="14.5" customHeight="1">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -9832,7 +8816,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:16">
+    <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>196</v>
       </c>
@@ -9882,7 +8866,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" ht="14.5">
       <c r="A19" t="s">
         <v>202</v>
       </c>
@@ -9976,7 +8960,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" ht="14.5">
       <c r="A21" t="s">
         <v>218</v>
       </c>
@@ -10126,7 +9110,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" ht="14.5">
       <c r="A24" t="s">
         <v>246</v>
       </c>
@@ -10176,7 +9160,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" ht="14.5">
       <c r="A25" t="s">
         <v>255</v>
       </c>
@@ -10270,7 +9254,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="27" s="26" customFormat="1" ht="15.5" customHeight="1" spans="1:16">
+    <row r="27" spans="1:16" s="26" customFormat="1" ht="15.5" customHeight="1">
       <c r="A27" s="26" t="s">
         <v>268</v>
       </c>
@@ -10317,7 +9301,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" s="26" customFormat="1" spans="1:16">
+    <row r="28" spans="1:16" s="26" customFormat="1">
       <c r="A28" s="26" t="s">
         <v>279</v>
       </c>
@@ -10361,7 +9345,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="29" s="26" customFormat="1" spans="1:16">
+    <row r="29" spans="1:16" s="26" customFormat="1" ht="15">
       <c r="A29" s="26" t="s">
         <v>286</v>
       </c>
@@ -10405,7 +9389,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="30" s="9" customFormat="1" spans="1:16">
+    <row r="30" spans="1:16" s="9" customFormat="1" ht="14.5">
       <c r="A30" s="9" t="s">
         <v>292</v>
       </c>
@@ -10446,7 +9430,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="31" s="9" customFormat="1" spans="1:16">
+    <row r="31" spans="1:16" s="9" customFormat="1" ht="14.5">
       <c r="A31" s="9" t="s">
         <v>301</v>
       </c>
@@ -10490,7 +9474,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="32" s="9" customFormat="1" spans="1:16">
+    <row r="32" spans="1:16" s="9" customFormat="1" ht="14.5">
       <c r="A32" s="9" t="s">
         <v>308</v>
       </c>
@@ -10535,31 +9519,31 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L12" r:id="rId1" display="https://www.bilibili.com/video/BV1MP411h759"/>
-    <hyperlink ref="L13" r:id="rId2" display="https://www.bilibili.com/video/BV1Xg4y1k7GH"/>
-    <hyperlink ref="L14" r:id="rId3" display="https://www.bilibili.com/video/BV1Ai4y167MU"/>
-    <hyperlink ref="L17" r:id="rId4" display="https://www.bilibili.com/video/BV1Cz421e79N"/>
-    <hyperlink ref="L19" r:id="rId5" display="https://www.bilibili.com/video/BV1EvcdenE9h"/>
-    <hyperlink ref="L25" r:id="rId6" display="https://www.bilibili.com/video/BV1RtZmYGE3a"/>
-    <hyperlink ref="L30" r:id="rId7" display="https://www.bilibili.com/video/BV1X58m6AENA"/>
+    <hyperlink ref="L12" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="L14" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="L17" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="L19" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="L25" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="L30" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E193"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="32.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="67.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="27.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="13.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="67.54296875" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10596,7 +9580,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="14.5">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -10683,7 +9667,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="13.5" customHeight="1">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -10893,7 +9877,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:5">
+    <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="A24" t="s">
         <v>145</v>
       </c>
@@ -10907,7 +9891,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:5">
+    <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" t="s">
         <v>155</v>
       </c>
@@ -11005,7 +9989,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" ht="14.5">
       <c r="A32" t="s">
         <v>170</v>
       </c>
@@ -11022,7 +10006,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" ht="14.5">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -11039,7 +10023,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" ht="14.5">
       <c r="A34" t="s">
         <v>187</v>
       </c>
@@ -11056,7 +10040,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="35" ht="15.5" customHeight="1" spans="1:5">
+    <row r="35" spans="1:5" ht="15.5" customHeight="1">
       <c r="A35" s="15" t="s">
         <v>196</v>
       </c>
@@ -11085,7 +10069,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:5">
+    <row r="37" spans="1:5" ht="15" customHeight="1">
       <c r="A37" s="15" t="s">
         <v>210</v>
       </c>
@@ -11102,7 +10086,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:5">
+    <row r="38" spans="1:5" ht="15" customHeight="1">
       <c r="A38" s="15" t="s">
         <v>218</v>
       </c>
@@ -11119,7 +10103,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:5">
+    <row r="39" spans="1:5" ht="14.5" customHeight="1">
       <c r="A39" s="15" t="s">
         <v>227</v>
       </c>
@@ -11136,7 +10120,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:5">
+    <row r="40" spans="1:5" ht="15" customHeight="1">
       <c r="A40" s="15" t="s">
         <v>236</v>
       </c>
@@ -11153,7 +10137,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:5">
+    <row r="41" spans="1:5" ht="15" customHeight="1">
       <c r="A41" s="15" t="s">
         <v>246</v>
       </c>
@@ -11170,7 +10154,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:5">
+    <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="15" t="s">
         <v>255</v>
       </c>
@@ -11704,36 +10688,34 @@
       <c r="C193" s="25"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D49" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:D49" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="C16" r:id="rId2" display="https://www.animatetimes.com/news/details.php?id=1711341102&amp;p=2"/>
-    <hyperlink ref="C18" r:id="rId3" display="https://www.lisani.jp/0000271996/4/?show_more=1"/>
-    <hyperlink ref="C22" r:id="rId1" display="https://www.lisani.jp/0000239390/2/?show_more=1"/>
-    <hyperlink ref="B25" r:id="rId4" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n&#10;佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n&#10;高尾：就像剑一样呢。 \n&#10;佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n&#10;高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n&#10;佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n&#10;——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n&#10;佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n&#10;——也是一首很容易入耳的歌呢。\n&#10;高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n&#10;佐佐木： 谢谢——！"/>
-    <hyperlink ref="C25" r:id="rId4" display="https://www.animatetimes.com/news/details.php?id=1711342991&amp;p=2"/>
-    <hyperlink ref="C27" r:id="rId5" display="https://www.lisani.jp/0000256138/?show_more=1"/>
-    <hyperlink ref="C28" r:id="rId6" display="https://www.animatetimes.com/news/details.php?id=1711342991"/>
-    <hyperlink ref="C31" r:id="rId7" display="https://natalie.mu/music/pp/avemujica01/page/2"/>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="C16" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="C18" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="C22" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="B25" r:id="rId5" display="——这一天也是「素晴らしき世界 でも どこにもない場所」的首次表演呢。\n_x000a_佐佐木： 1st LIVE的故事主轴是“被遗弃的人偶们破坏迄今为止的世界，创造新的世界”，所以我觉得破坏那个世界的第一步就是「素晴らしき世界 でも どこにもない場所」。D段旋律的演奏也有种挥动吉他的感觉。 \n_x000a_高尾：就像剑一样呢。 \n_x000a_佐佐木：没错。我是带着破坏世界的意象去演奏和演唱的。 \n_x000a_高尾：相反，我心中的 Oblivionis 是“世界的使者”的形象，在这首歌的表演中我有意识地保持不动。我心中一直有 Oblivionis 凛然站立着的形象，所以我会一边双手弹奏，一边看着前方，尽量不看键盘去弹。 \n_x000a_佐佐木： ！？你说得轻巧，那可是很厉害的事情哦。简直已经超越人类范畴（笑）。 \n_x000a_——（笑）。那么请再次谈谈关于「素晴らしき世界 でも どこにもない場所」这首歌吧。 \n_x000a_佐佐木：这首歌和1st LIVE非常契合呢。“Perdere Omnia”就是“破坏一切”的意思。「素晴らしき世界 でも どこにもない場所」里也有着〈破坏吧 破坏吧〉这样的歌词，是一首创造新世界的歌。可以说就是“Perdere Omnia”本身吧。我觉得这可以说是破坏一切的起始之曲，所以我将Doloris的觉悟和坚强的意志倾注在歌声中进行了演奏。听着听着我自己也会兴奋起来，如果观众们也能有同样的心情我会很高兴的。作为共犯者，我努力录音，希望能和大家一起破坏世界，把大家拉进新的世界。\n_x000a_——也是一首很容易入耳的歌呢。\n_x000a_高尾： 明明是破坏世界的歌，副歌部分李子亲的歌声却很流畅圆润。我很喜欢这一点……！\n_x000a_佐佐木： 谢谢——！" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="C25" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="C27" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="C28" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="C31" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F468"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="12.8181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="49.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="69.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="39.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="29.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" customWidth="1"/>
+    <col min="4" max="4" width="69.26953125" customWidth="1"/>
+    <col min="6" max="6" width="39.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -12001,7 +10983,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="16" customHeight="1">
       <c r="A15" t="s">
         <v>145</v>
       </c>
@@ -12172,7 +11154,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="16" customHeight="1">
       <c r="A24" t="s">
         <v>145</v>
       </c>
@@ -12653,7 +11635,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:6">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -13587,7 +12569,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1" spans="1:6">
+    <row r="100" spans="1:6" ht="16" customHeight="1">
       <c r="A100" t="s">
         <v>51</v>
       </c>
@@ -13701,7 +12683,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1" spans="1:6">
+    <row r="106" spans="1:6" ht="16" customHeight="1">
       <c r="A106" t="s">
         <v>138</v>
       </c>
@@ -13909,7 +12891,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1" spans="1:6">
+    <row r="117" spans="1:6" ht="16" customHeight="1">
       <c r="A117" t="s">
         <v>138</v>
       </c>
@@ -14239,7 +13221,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1" spans="1:6">
+    <row r="135" spans="1:6" ht="16" customHeight="1">
       <c r="A135" t="s">
         <v>130</v>
       </c>
@@ -14447,7 +13429,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1" spans="1:6">
+    <row r="146" spans="1:6" ht="16" customHeight="1">
       <c r="A146" t="s">
         <v>130</v>
       </c>
@@ -14612,7 +13594,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="155" ht="16" customHeight="1" spans="1:6">
+    <row r="155" spans="1:6" ht="16" customHeight="1">
       <c r="A155" t="s">
         <v>75</v>
       </c>
@@ -14902,7 +13884,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="171" ht="16" customHeight="1" spans="1:6">
+    <row r="171" spans="1:6" ht="16" customHeight="1">
       <c r="A171" t="s">
         <v>170</v>
       </c>
@@ -16830,7 +15812,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="274" ht="15" customHeight="1" spans="1:6">
+    <row r="274" spans="1:6" ht="15" customHeight="1">
       <c r="A274" s="15" t="s">
         <v>196</v>
       </c>
@@ -16850,7 +15832,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="275" ht="15" customHeight="1" spans="1:6">
+    <row r="275" spans="1:6" ht="15" customHeight="1">
       <c r="A275" s="15" t="s">
         <v>196</v>
       </c>
@@ -16870,7 +15852,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="276" ht="15" customHeight="1" spans="1:6">
+    <row r="276" spans="1:6" ht="15" customHeight="1">
       <c r="A276" s="15" t="s">
         <v>196</v>
       </c>
@@ -16890,7 +15872,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="277" ht="15" customHeight="1" spans="1:6">
+    <row r="277" spans="1:6" ht="15" customHeight="1">
       <c r="A277" s="15" t="s">
         <v>196</v>
       </c>
@@ -16910,7 +15892,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="278" ht="15" customHeight="1" spans="1:6">
+    <row r="278" spans="1:6" ht="15" customHeight="1">
       <c r="A278" s="15" t="s">
         <v>196</v>
       </c>
@@ -16930,7 +15912,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="279" ht="15" customHeight="1" spans="1:6">
+    <row r="279" spans="1:6" ht="15" customHeight="1">
       <c r="A279" s="15" t="s">
         <v>196</v>
       </c>
@@ -16950,7 +15932,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="280" ht="15" customHeight="1" spans="1:6">
+    <row r="280" spans="1:6" ht="15" customHeight="1">
       <c r="A280" s="15" t="s">
         <v>196</v>
       </c>
@@ -20270,7 +19252,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="458" spans="1:6">
+    <row r="458" spans="1:6" ht="16">
       <c r="A458" t="s">
         <v>268</v>
       </c>
@@ -20485,259 +19467,258 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F468" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:F468" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.acfun.cn/v/ac47931167" tooltip="https://www.acfun.cn/v/ac47931167"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://www.acfun.cn/v/ac47931167_2"/>
-    <hyperlink ref="F7" r:id="rId3" display="https://www.acfun.cn/v/ac47931167_3"/>
-    <hyperlink ref="F8" r:id="rId4" display="https://www.acfun.cn/v/ac47931167_4"/>
-    <hyperlink ref="F9" r:id="rId5" display="https://www.acfun.cn/v/ac47931167_5"/>
-    <hyperlink ref="F10" r:id="rId6" display="https://www.acfun.cn/v/ac47931167_6"/>
-    <hyperlink ref="F12" r:id="rId7" display="https://www.acfun.cn/v/ac47931167_7"/>
-    <hyperlink ref="F14" r:id="rId8" display="https://www.acfun.cn/v/ac47934758"/>
-    <hyperlink ref="F15" r:id="rId9" display="https://www.acfun.cn/v/ac47934758_2"/>
-    <hyperlink ref="F16" r:id="rId10" display="https://www.acfun.cn/v/ac47934758_3"/>
-    <hyperlink ref="F18" r:id="rId11" display="https://www.acfun.cn/v/ac47934758_4"/>
-    <hyperlink ref="F20" r:id="rId12" display="https://www.acfun.cn/v/ac47934758_5"/>
-    <hyperlink ref="F22" r:id="rId13" display="https://www.acfun.cn/v/ac47934758_6"/>
-    <hyperlink ref="F23" r:id="rId14" display="https://www.acfun.cn/v/ac47934758_7"/>
-    <hyperlink ref="F24" r:id="rId15" display="https://www.acfun.cn/v/ac47934758_8"/>
-    <hyperlink ref="F25" r:id="rId16" display="https://www.acfun.cn/v/ac47934758_9"/>
-    <hyperlink ref="F27" r:id="rId17" display="https://www.acfun.cn/v/ac47934758_10"/>
-    <hyperlink ref="F28" r:id="rId18" display="https://www.acfun.cn/v/ac47934815"/>
-    <hyperlink ref="F29" r:id="rId19" display="https://www.acfun.cn/v/ac47934815_2"/>
-    <hyperlink ref="F31" r:id="rId20" display="https://www.acfun.cn/v/ac47934815_3"/>
-    <hyperlink ref="F32" r:id="rId21" display="https://www.acfun.cn/v/ac47934815_4"/>
-    <hyperlink ref="F33" r:id="rId22" display="https://www.acfun.cn/v/ac47934815_5"/>
-    <hyperlink ref="F34" r:id="rId23" display="https://www.acfun.cn/v/ac47934815_6"/>
-    <hyperlink ref="F39" r:id="rId24" display="https://www.acfun.cn/v/ac47934815_7"/>
-    <hyperlink ref="F69" r:id="rId25" display="https://www.acfun.cn/v/ac47935101_2"/>
-    <hyperlink ref="F71" r:id="rId26" display="https://www.acfun.cn/v/ac47935101_3"/>
-    <hyperlink ref="F73" r:id="rId27" display="https://www.acfun.cn/v/ac47935101_4"/>
-    <hyperlink ref="F74" r:id="rId28" display="https://www.acfun.cn/v/ac47935101_5"/>
-    <hyperlink ref="F75" r:id="rId29" display="https://www.acfun.cn/v/ac47935101_6"/>
-    <hyperlink ref="F76" r:id="rId30" display="https://www.acfun.cn/v/ac47935101_7"/>
-    <hyperlink ref="F77" r:id="rId31" display="https://www.acfun.cn/v/ac47935101_8"/>
-    <hyperlink ref="F78" r:id="rId32" display="https://www.acfun.cn/v/ac47935101_9"/>
-    <hyperlink ref="F80" r:id="rId33" display="https://www.acfun.cn/v/ac47935101_10"/>
-    <hyperlink ref="F87" r:id="rId34" display="https://www.acfun.cn/v/ac48752881_2"/>
-    <hyperlink ref="F101" r:id="rId35" display="https://www.acfun.cn/v/ac47924476_8"/>
-    <hyperlink ref="F105" r:id="rId36" display="https://www.acfun.cn/v/ac47935303"/>
-    <hyperlink ref="F106" r:id="rId37" display="https://www.acfun.cn/v/ac47935303_2"/>
-    <hyperlink ref="F107" r:id="rId38" display="https://www.acfun.cn/v/ac47935303_3"/>
-    <hyperlink ref="F109" r:id="rId39" display="https://www.acfun.cn/v/ac47935303_4"/>
-    <hyperlink ref="F113" r:id="rId40" display="https://www.acfun.cn/v/ac47935303_5"/>
-    <hyperlink ref="F114" r:id="rId41" display="https://www.acfun.cn/v/ac47935303_6"/>
-    <hyperlink ref="F115" r:id="rId42" display="https://www.acfun.cn/v/ac47935303_7"/>
-    <hyperlink ref="F116" r:id="rId43" display="https://www.acfun.cn/v/ac47935303_8"/>
-    <hyperlink ref="F118" r:id="rId44" display="https://www.acfun.cn/v/ac47935303_9"/>
-    <hyperlink ref="F119" r:id="rId45" display="https://www.acfun.cn/v/ac47935303_10"/>
-    <hyperlink ref="F120" r:id="rId46" display="https://www.acfun.cn/v/ac48116488"/>
-    <hyperlink ref="F122" r:id="rId47" display="https://www.acfun.cn/v/ac48116488_2"/>
-    <hyperlink ref="F128" r:id="rId48" display="https://www.acfun.cn/v/ac48116488_3"/>
-    <hyperlink ref="F129" r:id="rId49" display="https://www.acfun.cn/v/ac48116488_4"/>
-    <hyperlink ref="F133" r:id="rId50" display="https://www.acfun.cn/v/ac48116488_5"/>
-    <hyperlink ref="F134" r:id="rId51" display="https://www.acfun.cn/v/ac47934950"/>
-    <hyperlink ref="F135" r:id="rId52" display="https://www.acfun.cn/v/ac47934950_2"/>
-    <hyperlink ref="F136" r:id="rId53" display="https://www.acfun.cn/v/ac47934950_3"/>
-    <hyperlink ref="F138" r:id="rId54" display="https://www.acfun.cn/v/ac47934950_4"/>
-    <hyperlink ref="F140" r:id="rId55" display="https://www.acfun.cn/v/ac47934950_5"/>
-    <hyperlink ref="F141" r:id="rId56" display="https://www.acfun.cn/v/ac47934950_6"/>
-    <hyperlink ref="F142" r:id="rId57" display="https://www.acfun.cn/v/ac47934950_7"/>
-    <hyperlink ref="F143" r:id="rId58" display="https://www.acfun.cn/v/ac47934950_8"/>
-    <hyperlink ref="F149" r:id="rId59" display="https://www.acfun.cn/v/ac47934950_9"/>
-    <hyperlink ref="F167" r:id="rId60" display="https://www.acfun.cn/v/ac48115972_7"/>
-    <hyperlink ref="F168" r:id="rId61" display="https://www.acfun.cn/v/ac47931569" tooltip="https://www.acfun.cn/v/ac47931569"/>
-    <hyperlink ref="F170" r:id="rId62" display="https://www.acfun.cn/v/ac47931569_2"/>
-    <hyperlink ref="F171" r:id="rId63" display="https://www.acfun.cn/v/ac47931569_3"/>
-    <hyperlink ref="F172" r:id="rId64" display="https://www.acfun.cn/v/ac47931569_4"/>
-    <hyperlink ref="F173" r:id="rId65" display="https://www.acfun.cn/v/ac47931569_5"/>
-    <hyperlink ref="F174" r:id="rId66" display="https://www.acfun.cn/v/ac47931569_6"/>
-    <hyperlink ref="F175" r:id="rId67" display="https://www.acfun.cn/v/ac47931569_7"/>
-    <hyperlink ref="F176" r:id="rId68" display="https://www.acfun.cn/v/ac47931569_8"/>
-    <hyperlink ref="F177" r:id="rId69" display="https://www.acfun.cn/v/ac47931569_9"/>
-    <hyperlink ref="F178" r:id="rId70" display="https://www.acfun.cn/v/ac47931569_10"/>
-    <hyperlink ref="F179" r:id="rId71" display="https://www.acfun.cn/v/ac47931603" tooltip="https://www.acfun.cn/v/ac47931603"/>
-    <hyperlink ref="F181" r:id="rId72" display="https://www.acfun.cn/v/ac47931603_2"/>
-    <hyperlink ref="F183" r:id="rId73" display="https://www.acfun.cn/v/ac47931603_3"/>
-    <hyperlink ref="F184" r:id="rId74" display="https://www.acfun.cn/v/ac47931603_4"/>
-    <hyperlink ref="F186" r:id="rId75" display="https://www.acfun.cn/v/ac47931603_5"/>
-    <hyperlink ref="F192" r:id="rId76" display="https://www.acfun.cn/v/ac47931603_6"/>
-    <hyperlink ref="F193" r:id="rId77" display="https://www.acfun.cn/v/ac47931603_7"/>
-    <hyperlink ref="F198" r:id="rId78" display="https://www.acfun.cn/v/ac47931603_8"/>
-    <hyperlink ref="F199" r:id="rId79" display="https://www.acfun.cn/v/ac47933063"/>
-    <hyperlink ref="F201" r:id="rId80" display="https://www.acfun.cn/v/ac47933063_2"/>
-    <hyperlink ref="F202" r:id="rId81" display="https://www.acfun.cn/v/ac47933063_3"/>
-    <hyperlink ref="F203" r:id="rId82" display="https://www.acfun.cn/v/ac47933063_4"/>
-    <hyperlink ref="F204" r:id="rId83" display="https://www.acfun.cn/v/ac47933063_5"/>
-    <hyperlink ref="F206" r:id="rId84" display="https://www.acfun.cn/v/ac47933063_6"/>
-    <hyperlink ref="F207" r:id="rId85" display="https://www.acfun.cn/v/ac47933063_7"/>
-    <hyperlink ref="F208" r:id="rId86" display="https://www.acfun.cn/v/ac47933063_8"/>
-    <hyperlink ref="F209" r:id="rId87" display="https://www.acfun.cn/v/ac47933063_9"/>
-    <hyperlink ref="F211" r:id="rId88" display="https://www.acfun.cn/v/ac47933063_10"/>
-    <hyperlink ref="F213" r:id="rId89" display="https://www.acfun.cn/v/ac48409409_1" tooltip="https://www.acfun.cn/v/ac48409409_1"/>
-    <hyperlink ref="F219" r:id="rId90" display="https://www.acfun.cn/v/ac48409409_2"/>
-    <hyperlink ref="F220" r:id="rId91" display="https://www.acfun.cn/v/ac48409409_3"/>
-    <hyperlink ref="F225" r:id="rId92" display="https://www.acfun.cn/v/ac48409409_4"/>
-    <hyperlink ref="F235" r:id="rId93" display="https://www.acfun.cn/v/ac47931075"/>
-    <hyperlink ref="F236" r:id="rId94" display="https://www.acfun.cn/v/ac47931075_2"/>
-    <hyperlink ref="F238" r:id="rId95" display="https://www.acfun.cn/v/ac47931075_3"/>
-    <hyperlink ref="F240" r:id="rId96" display="https://www.acfun.cn/v/ac47931075_4"/>
-    <hyperlink ref="F241" r:id="rId97" display="https://www.acfun.cn/v/ac47931075_5"/>
-    <hyperlink ref="F242" r:id="rId98" display="https://www.acfun.cn/v/ac47931075_6"/>
-    <hyperlink ref="F244" r:id="rId99" display="https://www.acfun.cn/v/ac47933675"/>
-    <hyperlink ref="F246" r:id="rId100" display="https://www.acfun.cn/v/ac47933675_2"/>
-    <hyperlink ref="F248" r:id="rId101" display="https://www.acfun.cn/v/ac47933675_3"/>
-    <hyperlink ref="F249" r:id="rId102" display="https://www.acfun.cn/v/ac47933675_4"/>
-    <hyperlink ref="F250" r:id="rId103" display="https://www.acfun.cn/v/ac47933675_5"/>
-    <hyperlink ref="F251" r:id="rId104" display="https://www.acfun.cn/v/ac47933675_6"/>
-    <hyperlink ref="F252" r:id="rId105" display="https://www.acfun.cn/v/ac47933675_7"/>
-    <hyperlink ref="F257" r:id="rId106" display="https://www.acfun.cn/v/ac47933675_8"/>
-    <hyperlink ref="F259" r:id="rId107" display="https://www.acfun.cn/v/ac47934854"/>
-    <hyperlink ref="F260" r:id="rId108" display="https://www.acfun.cn/v/ac47934854_2"/>
-    <hyperlink ref="F261" r:id="rId109" display="https://www.acfun.cn/v/ac47934854_3"/>
-    <hyperlink ref="F262" r:id="rId110" display="https://www.acfun.cn/v/ac47934854_4"/>
-    <hyperlink ref="F263" r:id="rId111" display="https://www.acfun.cn/v/ac47934854_5"/>
-    <hyperlink ref="F264" r:id="rId112" display="https://www.acfun.cn/v/ac47934854_6"/>
-    <hyperlink ref="F266" r:id="rId113" display="https://www.acfun.cn/v/ac47934854_7"/>
-    <hyperlink ref="F272" r:id="rId114" display="https://www.acfun.cn/v/ac47934854_8"/>
-    <hyperlink ref="F274" r:id="rId115" display="https://www.acfun.cn/v/ac47933636"/>
-    <hyperlink ref="F275" r:id="rId116" display="https://www.acfun.cn/v/ac47933636_2"/>
-    <hyperlink ref="F276" r:id="rId117" display="https://www.acfun.cn/v/ac47933636_3"/>
-    <hyperlink ref="F277" r:id="rId118" display="https://www.acfun.cn/v/ac47933636_4"/>
-    <hyperlink ref="F278" r:id="rId119" display="https://www.acfun.cn/v/ac47933636_5"/>
-    <hyperlink ref="F279" r:id="rId120" display="https://www.acfun.cn/v/ac47933636_6"/>
-    <hyperlink ref="F281" r:id="rId121" display="https://www.acfun.cn/v/ac47930865"/>
-    <hyperlink ref="F282" r:id="rId122" display="https://www.acfun.cn/v/ac47930865_2"/>
-    <hyperlink ref="F284" r:id="rId123" display="https://www.acfun.cn/v/ac47930865_3"/>
-    <hyperlink ref="F286" r:id="rId124" display="https://www.acfun.cn/v/ac47930865_4"/>
-    <hyperlink ref="F291" r:id="rId125" display="https://www.acfun.cn/v/ac47930865_5"/>
-    <hyperlink ref="F292" r:id="rId126" display="https://www.acfun.cn/v/ac47930865_6"/>
-    <hyperlink ref="F296" r:id="rId127" display="https://www.acfun.cn/v/ac47932379"/>
-    <hyperlink ref="F297" r:id="rId128" display="https://www.acfun.cn/v/ac47932379_2"/>
-    <hyperlink ref="F298" r:id="rId129" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="F299" r:id="rId130" display="https://www.acfun.cn/v/ac47932379_4"/>
-    <hyperlink ref="F300" r:id="rId131" display="https://www.acfun.cn/v/ac47932379_5"/>
-    <hyperlink ref="F301" r:id="rId132" display="https://www.acfun.cn/v/ac47932379_6"/>
-    <hyperlink ref="F304" r:id="rId133" display="https://www.acfun.cn/v/ac47932379_7"/>
-    <hyperlink ref="F306" r:id="rId134" display="https://www.acfun.cn/v/ac47932379_8"/>
-    <hyperlink ref="F307" r:id="rId135" display="https://www.acfun.cn/v/ac47932379_9"/>
-    <hyperlink ref="F308" r:id="rId136" display="https://www.acfun.cn/v/ac47932379_10"/>
-    <hyperlink ref="F309" r:id="rId137" display="https://www.acfun.cn/v/ac48055738"/>
-    <hyperlink ref="F310" r:id="rId138" display="https://www.acfun.cn/v/ac48055738_2"/>
-    <hyperlink ref="F311" r:id="rId139" display="https://www.acfun.cn/v/ac48055738_3"/>
-    <hyperlink ref="F312" r:id="rId140" display="https://www.acfun.cn/v/ac48055738_4"/>
-    <hyperlink ref="F313" r:id="rId141" display="https://www.acfun.cn/v/ac48055738_5"/>
-    <hyperlink ref="F314" r:id="rId142" display="https://www.acfun.cn/v/ac48055738_6"/>
-    <hyperlink ref="F316" r:id="rId143" display="https://www.acfun.cn/v/ac48055738_7"/>
-    <hyperlink ref="F317" r:id="rId144" display="https://www.acfun.cn/v/ac48055738_8"/>
-    <hyperlink ref="F319" r:id="rId145" display="https://www.acfun.cn/v/ac48055738_9"/>
-    <hyperlink ref="F325" r:id="rId146" display="https://www.acfun.cn/v/ac48751334"/>
-    <hyperlink ref="F326" r:id="rId147" display="https://www.acfun.cn/v/ac48751334_2"/>
-    <hyperlink ref="F331" r:id="rId148" display="https://www.acfun.cn/v/ac48751334_3" tooltip="https://www.acfun.cn/v/ac48751334_3"/>
-    <hyperlink ref="F332" r:id="rId149" display="https://www.acfun.cn/v/ac47931260"/>
-    <hyperlink ref="F333" r:id="rId150" display="https://www.acfun.cn/v/ac47931260_2"/>
-    <hyperlink ref="F335" r:id="rId151" display="https://www.acfun.cn/v/ac47931260_3"/>
-    <hyperlink ref="F336" r:id="rId152" display="https://www.acfun.cn/v/ac47931260_4"/>
-    <hyperlink ref="F337" r:id="rId153" display="https://www.acfun.cn/v/ac47931260_5"/>
-    <hyperlink ref="F338" r:id="rId154" display="https://www.acfun.cn/v/ac47931260_6"/>
-    <hyperlink ref="F339" r:id="rId155" display="https://www.acfun.cn/v/ac47931260_7"/>
-    <hyperlink ref="F345" r:id="rId156" display="https://www.acfun.cn/v/ac47931260_8"/>
-    <hyperlink ref="F346" r:id="rId157" display="https://www.acfun.cn/v/ac47932208"/>
-    <hyperlink ref="F347" r:id="rId158" display="https://www.acfun.cn/v/ac47932208_2"/>
-    <hyperlink ref="F348" r:id="rId159" display="https://www.acfun.cn/v/ac47932208_3"/>
-    <hyperlink ref="F349" r:id="rId160" display="https://www.acfun.cn/v/ac47932208_4"/>
-    <hyperlink ref="F350" r:id="rId161" display="https://www.acfun.cn/v/ac47932208_5"/>
-    <hyperlink ref="F351" r:id="rId162" display="https://www.acfun.cn/v/ac47932208_6"/>
-    <hyperlink ref="F352" r:id="rId163" display="https://www.acfun.cn/v/ac47932208_7"/>
-    <hyperlink ref="F358" r:id="rId164" display="https://www.acfun.cn/v/ac47932208_8"/>
-    <hyperlink ref="F359" r:id="rId165" display="https://www.acfun.cn/v/ac47932208_9"/>
-    <hyperlink ref="F363" r:id="rId166" display="https://www.acfun.cn/v/ac47932208_10"/>
-    <hyperlink ref="F364" r:id="rId167" display="https://www.acfun.cn/v/ac47931830"/>
-    <hyperlink ref="F365" r:id="rId168" display="https://www.acfun.cn/v/ac47931830_2"/>
-    <hyperlink ref="F368" r:id="rId169" display="https://www.acfun.cn/v/ac47931830_3"/>
-    <hyperlink ref="F369" r:id="rId170" display="https://www.acfun.cn/v/ac47931830_4"/>
-    <hyperlink ref="F370" r:id="rId171" display="https://www.acfun.cn/v/ac47931830_5"/>
-    <hyperlink ref="F372" r:id="rId172" display="https://www.acfun.cn/v/ac47931830_6"/>
-    <hyperlink ref="F373" r:id="rId173" display="https://www.acfun.cn/v/ac47931830_7"/>
-    <hyperlink ref="F374" r:id="rId174" display="https://www.acfun.cn/v/ac47931830_8"/>
-    <hyperlink ref="F376" r:id="rId175" display="https://www.acfun.cn/v/ac47931830_9"/>
-    <hyperlink ref="F378" r:id="rId176" display="https://www.acfun.cn/v/ac47931830_10"/>
-    <hyperlink ref="F384" r:id="rId177" display="https://www.acfun.cn/v/ac48751840"/>
-    <hyperlink ref="F385" r:id="rId178" display="https://www.acfun.cn/v/ac48751840_2"/>
-    <hyperlink ref="F389" r:id="rId179" display="https://www.acfun.cn/v/ac48751840_3"/>
-    <hyperlink ref="F390" r:id="rId180" display="https://www.acfun.cn/v/ac47931318"/>
-    <hyperlink ref="F391" r:id="rId181" display="https://www.acfun.cn/v/ac47931318_2"/>
-    <hyperlink ref="F395" r:id="rId182" display="https://www.acfun.cn/v/ac47931318_3"/>
-    <hyperlink ref="F396" r:id="rId183" display="https://www.acfun.cn/v/ac47931318_4"/>
-    <hyperlink ref="F397" r:id="rId184" display="https://www.acfun.cn/v/ac47931318_5"/>
-    <hyperlink ref="F398" r:id="rId185" display="https://www.acfun.cn/v/ac47931318_6"/>
-    <hyperlink ref="F399" r:id="rId186" display="https://www.acfun.cn/v/ac47931318_7"/>
-    <hyperlink ref="F400" r:id="rId187" display="https://www.acfun.cn/v/ac47931318_8"/>
-    <hyperlink ref="F401" r:id="rId188" display="https://www.acfun.cn/v/ac47931318_9"/>
-    <hyperlink ref="F402" r:id="rId189" display="https://www.acfun.cn/v/ac47931318_10"/>
-    <hyperlink ref="F403" r:id="rId190" display="https://www.acfun.cn/v/ac48311717"/>
-    <hyperlink ref="F405" r:id="rId191" display="https://www.acfun.cn/v/ac48311717_2"/>
-    <hyperlink ref="F406" r:id="rId192" display="https://www.acfun.cn/v/ac48311717_3"/>
-    <hyperlink ref="F408" r:id="rId193" display="https://www.acfun.cn/v/ac48311717_4"/>
-    <hyperlink ref="F414" r:id="rId194" display="https://www.acfun.cn/v/ac48311717_5"/>
-    <hyperlink ref="F415" r:id="rId195" display="https://www.acfun.cn/v/ac48311717_6"/>
-    <hyperlink ref="F420" r:id="rId196" display="https://www.acfun.cn/v/ac48311717_7"/>
-    <hyperlink ref="F421" r:id="rId197" display="https://www.acfun.cn/v/ac47932123"/>
-    <hyperlink ref="F422" r:id="rId198" display="https://www.acfun.cn/v/ac47932123_2"/>
-    <hyperlink ref="F424" r:id="rId199" display="https://www.acfun.cn/v/ac47932123_3"/>
-    <hyperlink ref="F425" r:id="rId200" display="https://www.acfun.cn/v/ac47932123_4" tooltip="https://www.acfun.cn/v/ac47932123_4"/>
-    <hyperlink ref="F426" r:id="rId201" display="https://www.acfun.cn/v/ac47932123_5"/>
-    <hyperlink ref="F427" r:id="rId202" display="https://www.acfun.cn/v/ac47932123_6"/>
-    <hyperlink ref="F428" r:id="rId203" display="https://www.acfun.cn/v/ac47932123_7"/>
-    <hyperlink ref="F430" r:id="rId204" display="https://www.acfun.cn/v/ac47932123_8"/>
-    <hyperlink ref="F434" r:id="rId205" display="https://www.acfun.cn/v/ac47930836"/>
-    <hyperlink ref="F435" r:id="rId206" display="https://www.acfun.cn/v/ac47930836_2"/>
-    <hyperlink ref="F436" r:id="rId207" display="https://www.acfun.cn/v/ac47930836_3"/>
-    <hyperlink ref="F438" r:id="rId208" display="https://www.acfun.cn/v/ac47930836_4"/>
-    <hyperlink ref="F440" r:id="rId209" display="https://www.acfun.cn/v/ac47930836_5"/>
-    <hyperlink ref="F441" r:id="rId210" display="https://www.acfun.cn/v/ac47930836_6"/>
-    <hyperlink ref="F447" r:id="rId211" display="https://www.acfun.cn/v/ac47930836_7"/>
-    <hyperlink ref="F448" r:id="rId212" display="https://www.acfun.cn/v/ac47930836_8"/>
-    <hyperlink ref="F451" r:id="rId213" display="https://www.acfun.cn/v/ac47935835"/>
-    <hyperlink ref="F452" r:id="rId214" display="https://www.acfun.cn/v/ac47935862" tooltip="https://www.acfun.cn/v/ac47935862"/>
-    <hyperlink ref="F453" r:id="rId215" display="https://www.acfun.cn/v/ac47932937" tooltip="https://www.acfun.cn/v/ac47932937"/>
-    <hyperlink ref="F454" r:id="rId216" display="https://www.acfun.cn/v/ac47932937_2"/>
-    <hyperlink ref="F455" r:id="rId217" display="https://www.acfun.cn/v/ac47932937_3"/>
-    <hyperlink ref="F457" r:id="rId218" display="https://www.acfun.cn/v/ac47932937_4"/>
-    <hyperlink ref="F458" r:id="rId219" display="https://www.acfun.cn/v/ac47932937_5"/>
-    <hyperlink ref="F459" r:id="rId220" display="https://www.acfun.cn/v/ac47932763" tooltip="https://www.acfun.cn/v/ac47932763"/>
-    <hyperlink ref="F460" r:id="rId221" display="https://www.acfun.cn/v/ac47932763_2"/>
-    <hyperlink ref="F461" r:id="rId222" display="https://www.acfun.cn/v/ac47932763_3"/>
-    <hyperlink ref="F463" r:id="rId223" display="https://www.acfun.cn/v/ac47932763_4"/>
-    <hyperlink ref="F464" r:id="rId224" display="https://www.acfun.cn/v/ac47931710" tooltip="https://www.acfun.cn/v/ac47931710"/>
-    <hyperlink ref="F465" r:id="rId225" display="https://www.acfun.cn/v/ac47931710_2"/>
-    <hyperlink ref="F466" r:id="rId226" display="https://www.acfun.cn/v/ac47931710_3"/>
-    <hyperlink ref="F468" r:id="rId227" display="https://www.acfun.cn/v/ac47931710_4"/>
+    <hyperlink ref="F2" r:id="rId1" tooltip="https://www.acfun.cn/v/ac47931167" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{00000000-0004-0000-0300-000005000000}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{00000000-0004-0000-0300-000006000000}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{00000000-0004-0000-0300-000007000000}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{00000000-0004-0000-0300-000008000000}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{00000000-0004-0000-0300-000009000000}"/>
+    <hyperlink ref="F18" r:id="rId11" xr:uid="{00000000-0004-0000-0300-00000A000000}"/>
+    <hyperlink ref="F20" r:id="rId12" xr:uid="{00000000-0004-0000-0300-00000B000000}"/>
+    <hyperlink ref="F22" r:id="rId13" xr:uid="{00000000-0004-0000-0300-00000C000000}"/>
+    <hyperlink ref="F23" r:id="rId14" xr:uid="{00000000-0004-0000-0300-00000D000000}"/>
+    <hyperlink ref="F24" r:id="rId15" xr:uid="{00000000-0004-0000-0300-00000E000000}"/>
+    <hyperlink ref="F25" r:id="rId16" xr:uid="{00000000-0004-0000-0300-00000F000000}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{00000000-0004-0000-0300-000010000000}"/>
+    <hyperlink ref="F28" r:id="rId18" xr:uid="{00000000-0004-0000-0300-000011000000}"/>
+    <hyperlink ref="F29" r:id="rId19" xr:uid="{00000000-0004-0000-0300-000012000000}"/>
+    <hyperlink ref="F31" r:id="rId20" xr:uid="{00000000-0004-0000-0300-000013000000}"/>
+    <hyperlink ref="F32" r:id="rId21" xr:uid="{00000000-0004-0000-0300-000014000000}"/>
+    <hyperlink ref="F33" r:id="rId22" xr:uid="{00000000-0004-0000-0300-000015000000}"/>
+    <hyperlink ref="F34" r:id="rId23" xr:uid="{00000000-0004-0000-0300-000016000000}"/>
+    <hyperlink ref="F39" r:id="rId24" xr:uid="{00000000-0004-0000-0300-000017000000}"/>
+    <hyperlink ref="F69" r:id="rId25" xr:uid="{00000000-0004-0000-0300-000018000000}"/>
+    <hyperlink ref="F71" r:id="rId26" xr:uid="{00000000-0004-0000-0300-000019000000}"/>
+    <hyperlink ref="F73" r:id="rId27" xr:uid="{00000000-0004-0000-0300-00001A000000}"/>
+    <hyperlink ref="F74" r:id="rId28" xr:uid="{00000000-0004-0000-0300-00001B000000}"/>
+    <hyperlink ref="F75" r:id="rId29" xr:uid="{00000000-0004-0000-0300-00001C000000}"/>
+    <hyperlink ref="F76" r:id="rId30" xr:uid="{00000000-0004-0000-0300-00001D000000}"/>
+    <hyperlink ref="F77" r:id="rId31" xr:uid="{00000000-0004-0000-0300-00001E000000}"/>
+    <hyperlink ref="F78" r:id="rId32" xr:uid="{00000000-0004-0000-0300-00001F000000}"/>
+    <hyperlink ref="F80" r:id="rId33" xr:uid="{00000000-0004-0000-0300-000020000000}"/>
+    <hyperlink ref="F87" r:id="rId34" xr:uid="{00000000-0004-0000-0300-000021000000}"/>
+    <hyperlink ref="F101" r:id="rId35" xr:uid="{00000000-0004-0000-0300-000022000000}"/>
+    <hyperlink ref="F105" r:id="rId36" xr:uid="{00000000-0004-0000-0300-000023000000}"/>
+    <hyperlink ref="F106" r:id="rId37" xr:uid="{00000000-0004-0000-0300-000024000000}"/>
+    <hyperlink ref="F107" r:id="rId38" xr:uid="{00000000-0004-0000-0300-000025000000}"/>
+    <hyperlink ref="F109" r:id="rId39" xr:uid="{00000000-0004-0000-0300-000026000000}"/>
+    <hyperlink ref="F113" r:id="rId40" xr:uid="{00000000-0004-0000-0300-000027000000}"/>
+    <hyperlink ref="F114" r:id="rId41" xr:uid="{00000000-0004-0000-0300-000028000000}"/>
+    <hyperlink ref="F115" r:id="rId42" xr:uid="{00000000-0004-0000-0300-000029000000}"/>
+    <hyperlink ref="F116" r:id="rId43" xr:uid="{00000000-0004-0000-0300-00002A000000}"/>
+    <hyperlink ref="F118" r:id="rId44" xr:uid="{00000000-0004-0000-0300-00002B000000}"/>
+    <hyperlink ref="F119" r:id="rId45" xr:uid="{00000000-0004-0000-0300-00002C000000}"/>
+    <hyperlink ref="F120" r:id="rId46" xr:uid="{00000000-0004-0000-0300-00002D000000}"/>
+    <hyperlink ref="F122" r:id="rId47" xr:uid="{00000000-0004-0000-0300-00002E000000}"/>
+    <hyperlink ref="F128" r:id="rId48" xr:uid="{00000000-0004-0000-0300-00002F000000}"/>
+    <hyperlink ref="F129" r:id="rId49" xr:uid="{00000000-0004-0000-0300-000030000000}"/>
+    <hyperlink ref="F133" r:id="rId50" xr:uid="{00000000-0004-0000-0300-000031000000}"/>
+    <hyperlink ref="F134" r:id="rId51" xr:uid="{00000000-0004-0000-0300-000032000000}"/>
+    <hyperlink ref="F135" r:id="rId52" xr:uid="{00000000-0004-0000-0300-000033000000}"/>
+    <hyperlink ref="F136" r:id="rId53" xr:uid="{00000000-0004-0000-0300-000034000000}"/>
+    <hyperlink ref="F138" r:id="rId54" xr:uid="{00000000-0004-0000-0300-000035000000}"/>
+    <hyperlink ref="F140" r:id="rId55" xr:uid="{00000000-0004-0000-0300-000036000000}"/>
+    <hyperlink ref="F141" r:id="rId56" xr:uid="{00000000-0004-0000-0300-000037000000}"/>
+    <hyperlink ref="F142" r:id="rId57" xr:uid="{00000000-0004-0000-0300-000038000000}"/>
+    <hyperlink ref="F143" r:id="rId58" xr:uid="{00000000-0004-0000-0300-000039000000}"/>
+    <hyperlink ref="F149" r:id="rId59" xr:uid="{00000000-0004-0000-0300-00003A000000}"/>
+    <hyperlink ref="F167" r:id="rId60" xr:uid="{00000000-0004-0000-0300-00003B000000}"/>
+    <hyperlink ref="F168" r:id="rId61" tooltip="https://www.acfun.cn/v/ac47931569" xr:uid="{00000000-0004-0000-0300-00003C000000}"/>
+    <hyperlink ref="F170" r:id="rId62" xr:uid="{00000000-0004-0000-0300-00003D000000}"/>
+    <hyperlink ref="F171" r:id="rId63" xr:uid="{00000000-0004-0000-0300-00003E000000}"/>
+    <hyperlink ref="F172" r:id="rId64" xr:uid="{00000000-0004-0000-0300-00003F000000}"/>
+    <hyperlink ref="F173" r:id="rId65" xr:uid="{00000000-0004-0000-0300-000040000000}"/>
+    <hyperlink ref="F174" r:id="rId66" xr:uid="{00000000-0004-0000-0300-000041000000}"/>
+    <hyperlink ref="F175" r:id="rId67" xr:uid="{00000000-0004-0000-0300-000042000000}"/>
+    <hyperlink ref="F176" r:id="rId68" xr:uid="{00000000-0004-0000-0300-000043000000}"/>
+    <hyperlink ref="F177" r:id="rId69" xr:uid="{00000000-0004-0000-0300-000044000000}"/>
+    <hyperlink ref="F178" r:id="rId70" xr:uid="{00000000-0004-0000-0300-000045000000}"/>
+    <hyperlink ref="F179" r:id="rId71" tooltip="https://www.acfun.cn/v/ac47931603" xr:uid="{00000000-0004-0000-0300-000046000000}"/>
+    <hyperlink ref="F181" r:id="rId72" xr:uid="{00000000-0004-0000-0300-000047000000}"/>
+    <hyperlink ref="F183" r:id="rId73" xr:uid="{00000000-0004-0000-0300-000048000000}"/>
+    <hyperlink ref="F184" r:id="rId74" xr:uid="{00000000-0004-0000-0300-000049000000}"/>
+    <hyperlink ref="F186" r:id="rId75" xr:uid="{00000000-0004-0000-0300-00004A000000}"/>
+    <hyperlink ref="F192" r:id="rId76" xr:uid="{00000000-0004-0000-0300-00004B000000}"/>
+    <hyperlink ref="F193" r:id="rId77" xr:uid="{00000000-0004-0000-0300-00004C000000}"/>
+    <hyperlink ref="F198" r:id="rId78" xr:uid="{00000000-0004-0000-0300-00004D000000}"/>
+    <hyperlink ref="F199" r:id="rId79" xr:uid="{00000000-0004-0000-0300-00004E000000}"/>
+    <hyperlink ref="F201" r:id="rId80" xr:uid="{00000000-0004-0000-0300-00004F000000}"/>
+    <hyperlink ref="F202" r:id="rId81" xr:uid="{00000000-0004-0000-0300-000050000000}"/>
+    <hyperlink ref="F203" r:id="rId82" xr:uid="{00000000-0004-0000-0300-000051000000}"/>
+    <hyperlink ref="F204" r:id="rId83" xr:uid="{00000000-0004-0000-0300-000052000000}"/>
+    <hyperlink ref="F206" r:id="rId84" xr:uid="{00000000-0004-0000-0300-000053000000}"/>
+    <hyperlink ref="F207" r:id="rId85" xr:uid="{00000000-0004-0000-0300-000054000000}"/>
+    <hyperlink ref="F208" r:id="rId86" xr:uid="{00000000-0004-0000-0300-000055000000}"/>
+    <hyperlink ref="F209" r:id="rId87" xr:uid="{00000000-0004-0000-0300-000056000000}"/>
+    <hyperlink ref="F211" r:id="rId88" xr:uid="{00000000-0004-0000-0300-000057000000}"/>
+    <hyperlink ref="F213" r:id="rId89" tooltip="https://www.acfun.cn/v/ac48409409_1" xr:uid="{00000000-0004-0000-0300-000058000000}"/>
+    <hyperlink ref="F219" r:id="rId90" xr:uid="{00000000-0004-0000-0300-000059000000}"/>
+    <hyperlink ref="F220" r:id="rId91" xr:uid="{00000000-0004-0000-0300-00005A000000}"/>
+    <hyperlink ref="F225" r:id="rId92" xr:uid="{00000000-0004-0000-0300-00005B000000}"/>
+    <hyperlink ref="F235" r:id="rId93" xr:uid="{00000000-0004-0000-0300-00005C000000}"/>
+    <hyperlink ref="F236" r:id="rId94" xr:uid="{00000000-0004-0000-0300-00005D000000}"/>
+    <hyperlink ref="F238" r:id="rId95" xr:uid="{00000000-0004-0000-0300-00005E000000}"/>
+    <hyperlink ref="F240" r:id="rId96" xr:uid="{00000000-0004-0000-0300-00005F000000}"/>
+    <hyperlink ref="F241" r:id="rId97" xr:uid="{00000000-0004-0000-0300-000060000000}"/>
+    <hyperlink ref="F242" r:id="rId98" xr:uid="{00000000-0004-0000-0300-000061000000}"/>
+    <hyperlink ref="F244" r:id="rId99" xr:uid="{00000000-0004-0000-0300-000062000000}"/>
+    <hyperlink ref="F246" r:id="rId100" xr:uid="{00000000-0004-0000-0300-000063000000}"/>
+    <hyperlink ref="F248" r:id="rId101" xr:uid="{00000000-0004-0000-0300-000064000000}"/>
+    <hyperlink ref="F249" r:id="rId102" xr:uid="{00000000-0004-0000-0300-000065000000}"/>
+    <hyperlink ref="F250" r:id="rId103" xr:uid="{00000000-0004-0000-0300-000066000000}"/>
+    <hyperlink ref="F251" r:id="rId104" xr:uid="{00000000-0004-0000-0300-000067000000}"/>
+    <hyperlink ref="F252" r:id="rId105" xr:uid="{00000000-0004-0000-0300-000068000000}"/>
+    <hyperlink ref="F257" r:id="rId106" xr:uid="{00000000-0004-0000-0300-000069000000}"/>
+    <hyperlink ref="F259" r:id="rId107" xr:uid="{00000000-0004-0000-0300-00006A000000}"/>
+    <hyperlink ref="F260" r:id="rId108" xr:uid="{00000000-0004-0000-0300-00006B000000}"/>
+    <hyperlink ref="F261" r:id="rId109" xr:uid="{00000000-0004-0000-0300-00006C000000}"/>
+    <hyperlink ref="F262" r:id="rId110" xr:uid="{00000000-0004-0000-0300-00006D000000}"/>
+    <hyperlink ref="F263" r:id="rId111" xr:uid="{00000000-0004-0000-0300-00006E000000}"/>
+    <hyperlink ref="F264" r:id="rId112" xr:uid="{00000000-0004-0000-0300-00006F000000}"/>
+    <hyperlink ref="F266" r:id="rId113" xr:uid="{00000000-0004-0000-0300-000070000000}"/>
+    <hyperlink ref="F272" r:id="rId114" xr:uid="{00000000-0004-0000-0300-000071000000}"/>
+    <hyperlink ref="F274" r:id="rId115" xr:uid="{00000000-0004-0000-0300-000072000000}"/>
+    <hyperlink ref="F275" r:id="rId116" xr:uid="{00000000-0004-0000-0300-000073000000}"/>
+    <hyperlink ref="F276" r:id="rId117" xr:uid="{00000000-0004-0000-0300-000074000000}"/>
+    <hyperlink ref="F277" r:id="rId118" xr:uid="{00000000-0004-0000-0300-000075000000}"/>
+    <hyperlink ref="F278" r:id="rId119" xr:uid="{00000000-0004-0000-0300-000076000000}"/>
+    <hyperlink ref="F279" r:id="rId120" xr:uid="{00000000-0004-0000-0300-000077000000}"/>
+    <hyperlink ref="F281" r:id="rId121" xr:uid="{00000000-0004-0000-0300-000078000000}"/>
+    <hyperlink ref="F282" r:id="rId122" xr:uid="{00000000-0004-0000-0300-000079000000}"/>
+    <hyperlink ref="F284" r:id="rId123" xr:uid="{00000000-0004-0000-0300-00007A000000}"/>
+    <hyperlink ref="F286" r:id="rId124" xr:uid="{00000000-0004-0000-0300-00007B000000}"/>
+    <hyperlink ref="F291" r:id="rId125" xr:uid="{00000000-0004-0000-0300-00007C000000}"/>
+    <hyperlink ref="F292" r:id="rId126" xr:uid="{00000000-0004-0000-0300-00007D000000}"/>
+    <hyperlink ref="F296" r:id="rId127" xr:uid="{00000000-0004-0000-0300-00007E000000}"/>
+    <hyperlink ref="F297" r:id="rId128" xr:uid="{00000000-0004-0000-0300-00007F000000}"/>
+    <hyperlink ref="F298" r:id="rId129" xr:uid="{00000000-0004-0000-0300-000080000000}"/>
+    <hyperlink ref="F299" r:id="rId130" xr:uid="{00000000-0004-0000-0300-000081000000}"/>
+    <hyperlink ref="F300" r:id="rId131" xr:uid="{00000000-0004-0000-0300-000082000000}"/>
+    <hyperlink ref="F301" r:id="rId132" xr:uid="{00000000-0004-0000-0300-000083000000}"/>
+    <hyperlink ref="F304" r:id="rId133" xr:uid="{00000000-0004-0000-0300-000084000000}"/>
+    <hyperlink ref="F306" r:id="rId134" xr:uid="{00000000-0004-0000-0300-000085000000}"/>
+    <hyperlink ref="F307" r:id="rId135" xr:uid="{00000000-0004-0000-0300-000086000000}"/>
+    <hyperlink ref="F308" r:id="rId136" xr:uid="{00000000-0004-0000-0300-000087000000}"/>
+    <hyperlink ref="F309" r:id="rId137" xr:uid="{00000000-0004-0000-0300-000088000000}"/>
+    <hyperlink ref="F310" r:id="rId138" xr:uid="{00000000-0004-0000-0300-000089000000}"/>
+    <hyperlink ref="F311" r:id="rId139" xr:uid="{00000000-0004-0000-0300-00008A000000}"/>
+    <hyperlink ref="F312" r:id="rId140" xr:uid="{00000000-0004-0000-0300-00008B000000}"/>
+    <hyperlink ref="F313" r:id="rId141" xr:uid="{00000000-0004-0000-0300-00008C000000}"/>
+    <hyperlink ref="F314" r:id="rId142" xr:uid="{00000000-0004-0000-0300-00008D000000}"/>
+    <hyperlink ref="F316" r:id="rId143" xr:uid="{00000000-0004-0000-0300-00008E000000}"/>
+    <hyperlink ref="F317" r:id="rId144" xr:uid="{00000000-0004-0000-0300-00008F000000}"/>
+    <hyperlink ref="F319" r:id="rId145" xr:uid="{00000000-0004-0000-0300-000090000000}"/>
+    <hyperlink ref="F325" r:id="rId146" xr:uid="{00000000-0004-0000-0300-000091000000}"/>
+    <hyperlink ref="F326" r:id="rId147" xr:uid="{00000000-0004-0000-0300-000092000000}"/>
+    <hyperlink ref="F331" r:id="rId148" tooltip="https://www.acfun.cn/v/ac48751334_3" xr:uid="{00000000-0004-0000-0300-000093000000}"/>
+    <hyperlink ref="F332" r:id="rId149" xr:uid="{00000000-0004-0000-0300-000094000000}"/>
+    <hyperlink ref="F333" r:id="rId150" xr:uid="{00000000-0004-0000-0300-000095000000}"/>
+    <hyperlink ref="F335" r:id="rId151" xr:uid="{00000000-0004-0000-0300-000096000000}"/>
+    <hyperlink ref="F336" r:id="rId152" xr:uid="{00000000-0004-0000-0300-000097000000}"/>
+    <hyperlink ref="F337" r:id="rId153" xr:uid="{00000000-0004-0000-0300-000098000000}"/>
+    <hyperlink ref="F338" r:id="rId154" xr:uid="{00000000-0004-0000-0300-000099000000}"/>
+    <hyperlink ref="F339" r:id="rId155" xr:uid="{00000000-0004-0000-0300-00009A000000}"/>
+    <hyperlink ref="F345" r:id="rId156" xr:uid="{00000000-0004-0000-0300-00009B000000}"/>
+    <hyperlink ref="F346" r:id="rId157" xr:uid="{00000000-0004-0000-0300-00009C000000}"/>
+    <hyperlink ref="F347" r:id="rId158" xr:uid="{00000000-0004-0000-0300-00009D000000}"/>
+    <hyperlink ref="F348" r:id="rId159" xr:uid="{00000000-0004-0000-0300-00009E000000}"/>
+    <hyperlink ref="F349" r:id="rId160" xr:uid="{00000000-0004-0000-0300-00009F000000}"/>
+    <hyperlink ref="F350" r:id="rId161" xr:uid="{00000000-0004-0000-0300-0000A0000000}"/>
+    <hyperlink ref="F351" r:id="rId162" xr:uid="{00000000-0004-0000-0300-0000A1000000}"/>
+    <hyperlink ref="F352" r:id="rId163" xr:uid="{00000000-0004-0000-0300-0000A2000000}"/>
+    <hyperlink ref="F358" r:id="rId164" xr:uid="{00000000-0004-0000-0300-0000A3000000}"/>
+    <hyperlink ref="F359" r:id="rId165" xr:uid="{00000000-0004-0000-0300-0000A4000000}"/>
+    <hyperlink ref="F363" r:id="rId166" xr:uid="{00000000-0004-0000-0300-0000A5000000}"/>
+    <hyperlink ref="F364" r:id="rId167" xr:uid="{00000000-0004-0000-0300-0000A6000000}"/>
+    <hyperlink ref="F365" r:id="rId168" xr:uid="{00000000-0004-0000-0300-0000A7000000}"/>
+    <hyperlink ref="F368" r:id="rId169" xr:uid="{00000000-0004-0000-0300-0000A8000000}"/>
+    <hyperlink ref="F369" r:id="rId170" xr:uid="{00000000-0004-0000-0300-0000A9000000}"/>
+    <hyperlink ref="F370" r:id="rId171" xr:uid="{00000000-0004-0000-0300-0000AA000000}"/>
+    <hyperlink ref="F372" r:id="rId172" xr:uid="{00000000-0004-0000-0300-0000AB000000}"/>
+    <hyperlink ref="F373" r:id="rId173" xr:uid="{00000000-0004-0000-0300-0000AC000000}"/>
+    <hyperlink ref="F374" r:id="rId174" xr:uid="{00000000-0004-0000-0300-0000AD000000}"/>
+    <hyperlink ref="F376" r:id="rId175" xr:uid="{00000000-0004-0000-0300-0000AE000000}"/>
+    <hyperlink ref="F378" r:id="rId176" xr:uid="{00000000-0004-0000-0300-0000AF000000}"/>
+    <hyperlink ref="F384" r:id="rId177" xr:uid="{00000000-0004-0000-0300-0000B0000000}"/>
+    <hyperlink ref="F385" r:id="rId178" xr:uid="{00000000-0004-0000-0300-0000B1000000}"/>
+    <hyperlink ref="F389" r:id="rId179" xr:uid="{00000000-0004-0000-0300-0000B2000000}"/>
+    <hyperlink ref="F390" r:id="rId180" xr:uid="{00000000-0004-0000-0300-0000B3000000}"/>
+    <hyperlink ref="F391" r:id="rId181" xr:uid="{00000000-0004-0000-0300-0000B4000000}"/>
+    <hyperlink ref="F395" r:id="rId182" xr:uid="{00000000-0004-0000-0300-0000B5000000}"/>
+    <hyperlink ref="F396" r:id="rId183" xr:uid="{00000000-0004-0000-0300-0000B6000000}"/>
+    <hyperlink ref="F397" r:id="rId184" xr:uid="{00000000-0004-0000-0300-0000B7000000}"/>
+    <hyperlink ref="F398" r:id="rId185" xr:uid="{00000000-0004-0000-0300-0000B8000000}"/>
+    <hyperlink ref="F399" r:id="rId186" xr:uid="{00000000-0004-0000-0300-0000B9000000}"/>
+    <hyperlink ref="F400" r:id="rId187" xr:uid="{00000000-0004-0000-0300-0000BA000000}"/>
+    <hyperlink ref="F401" r:id="rId188" xr:uid="{00000000-0004-0000-0300-0000BB000000}"/>
+    <hyperlink ref="F402" r:id="rId189" xr:uid="{00000000-0004-0000-0300-0000BC000000}"/>
+    <hyperlink ref="F403" r:id="rId190" xr:uid="{00000000-0004-0000-0300-0000BD000000}"/>
+    <hyperlink ref="F405" r:id="rId191" xr:uid="{00000000-0004-0000-0300-0000BE000000}"/>
+    <hyperlink ref="F406" r:id="rId192" xr:uid="{00000000-0004-0000-0300-0000BF000000}"/>
+    <hyperlink ref="F408" r:id="rId193" xr:uid="{00000000-0004-0000-0300-0000C0000000}"/>
+    <hyperlink ref="F414" r:id="rId194" xr:uid="{00000000-0004-0000-0300-0000C1000000}"/>
+    <hyperlink ref="F415" r:id="rId195" xr:uid="{00000000-0004-0000-0300-0000C2000000}"/>
+    <hyperlink ref="F420" r:id="rId196" xr:uid="{00000000-0004-0000-0300-0000C3000000}"/>
+    <hyperlink ref="F421" r:id="rId197" xr:uid="{00000000-0004-0000-0300-0000C4000000}"/>
+    <hyperlink ref="F422" r:id="rId198" xr:uid="{00000000-0004-0000-0300-0000C5000000}"/>
+    <hyperlink ref="F424" r:id="rId199" xr:uid="{00000000-0004-0000-0300-0000C6000000}"/>
+    <hyperlink ref="F425" r:id="rId200" tooltip="https://www.acfun.cn/v/ac47932123_4" xr:uid="{00000000-0004-0000-0300-0000C7000000}"/>
+    <hyperlink ref="F426" r:id="rId201" xr:uid="{00000000-0004-0000-0300-0000C8000000}"/>
+    <hyperlink ref="F427" r:id="rId202" xr:uid="{00000000-0004-0000-0300-0000C9000000}"/>
+    <hyperlink ref="F428" r:id="rId203" xr:uid="{00000000-0004-0000-0300-0000CA000000}"/>
+    <hyperlink ref="F430" r:id="rId204" xr:uid="{00000000-0004-0000-0300-0000CB000000}"/>
+    <hyperlink ref="F434" r:id="rId205" xr:uid="{00000000-0004-0000-0300-0000CC000000}"/>
+    <hyperlink ref="F435" r:id="rId206" xr:uid="{00000000-0004-0000-0300-0000CD000000}"/>
+    <hyperlink ref="F436" r:id="rId207" xr:uid="{00000000-0004-0000-0300-0000CE000000}"/>
+    <hyperlink ref="F438" r:id="rId208" xr:uid="{00000000-0004-0000-0300-0000CF000000}"/>
+    <hyperlink ref="F440" r:id="rId209" xr:uid="{00000000-0004-0000-0300-0000D0000000}"/>
+    <hyperlink ref="F441" r:id="rId210" xr:uid="{00000000-0004-0000-0300-0000D1000000}"/>
+    <hyperlink ref="F447" r:id="rId211" xr:uid="{00000000-0004-0000-0300-0000D2000000}"/>
+    <hyperlink ref="F448" r:id="rId212" xr:uid="{00000000-0004-0000-0300-0000D3000000}"/>
+    <hyperlink ref="F451" r:id="rId213" xr:uid="{00000000-0004-0000-0300-0000D4000000}"/>
+    <hyperlink ref="F452" r:id="rId214" tooltip="https://www.acfun.cn/v/ac47935862" xr:uid="{00000000-0004-0000-0300-0000D5000000}"/>
+    <hyperlink ref="F453" r:id="rId215" tooltip="https://www.acfun.cn/v/ac47932937" xr:uid="{00000000-0004-0000-0300-0000D6000000}"/>
+    <hyperlink ref="F454" r:id="rId216" xr:uid="{00000000-0004-0000-0300-0000D7000000}"/>
+    <hyperlink ref="F455" r:id="rId217" xr:uid="{00000000-0004-0000-0300-0000D8000000}"/>
+    <hyperlink ref="F457" r:id="rId218" xr:uid="{00000000-0004-0000-0300-0000D9000000}"/>
+    <hyperlink ref="F458" r:id="rId219" xr:uid="{00000000-0004-0000-0300-0000DA000000}"/>
+    <hyperlink ref="F459" r:id="rId220" tooltip="https://www.acfun.cn/v/ac47932763" xr:uid="{00000000-0004-0000-0300-0000DB000000}"/>
+    <hyperlink ref="F460" r:id="rId221" xr:uid="{00000000-0004-0000-0300-0000DC000000}"/>
+    <hyperlink ref="F461" r:id="rId222" xr:uid="{00000000-0004-0000-0300-0000DD000000}"/>
+    <hyperlink ref="F463" r:id="rId223" xr:uid="{00000000-0004-0000-0300-0000DE000000}"/>
+    <hyperlink ref="F464" r:id="rId224" tooltip="https://www.acfun.cn/v/ac47931710" xr:uid="{00000000-0004-0000-0300-0000DF000000}"/>
+    <hyperlink ref="F465" r:id="rId225" xr:uid="{00000000-0004-0000-0300-0000E0000000}"/>
+    <hyperlink ref="F466" r:id="rId226" xr:uid="{00000000-0004-0000-0300-0000E1000000}"/>
+    <hyperlink ref="F468" r:id="rId227" xr:uid="{00000000-0004-0000-0300-0000E2000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="52.4545454545455" style="11" customWidth="1"/>
+    <col min="1" max="1" width="52.453125" style="11" customWidth="1"/>
     <col min="2" max="2" width="20" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.4545454545455" style="11" customWidth="1"/>
-    <col min="4" max="4" width="30.8181818181818" style="11" customWidth="1"/>
-    <col min="5" max="5" width="28.6363636363636" style="11" customWidth="1"/>
-    <col min="6" max="6" width="48.0909090909091" style="11" customWidth="1"/>
-    <col min="7" max="7" width="13.5454545454545" style="11" customWidth="1"/>
+    <col min="3" max="3" width="38.453125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="48.08984375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="11" customWidth="1"/>
     <col min="8" max="8" width="14" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.4545454545455" style="11" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="9" style="11" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -20798,7 +19779,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" ht="16">
       <c r="A3" s="11" t="s">
         <v>440</v>
       </c>
@@ -20908,7 +19889,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="16" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>69</v>
       </c>
@@ -22040,42 +21021,37 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H48" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:H48">
-      <sortCondition ref="B1"/>
-    </sortState>
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:H48" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F10" r:id="rId1" display="https://www.acfun.cn/v/ac48796276"/>
-    <hyperlink ref="F15" r:id="rId2" display="https://www.bilibili.com/video/BV1aAZYYAEEQ"/>
-    <hyperlink ref="F17" r:id="rId3" display="https://www.bilibili.com/video/BV1RV2eBeEAd"/>
-    <hyperlink ref="F19" r:id="rId4" display="https://www.bilibili.com/video/BV1pB3izpExm"/>
-    <hyperlink ref="F28" r:id="rId5" display="https://www.bilibili.com/video/BV19Y3g6SEqY"/>
-    <hyperlink ref="F29" r:id="rId6" display="https://www.bilibili.com/video/BV19Y3g6SEqY/?p=2"/>
-    <hyperlink ref="F34" r:id="rId7" display="https://www.bilibili.com/video/BV1TFJW6FEeP"/>
-    <hyperlink ref="F36" r:id="rId8" display="https://www.bilibili.com/video/BV18RdHBnELz"/>
-    <hyperlink ref="F48" r:id="rId9" display="https://www.bilibili.com/video/BV1zPbR6FEo3/"/>
+    <hyperlink ref="F10" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="F15" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="F17" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="F19" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="F28" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="F29" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="F34" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="F36" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="F48" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:H281"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="81.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="10.2727272727273" customWidth="1"/>
-    <col min="3" max="3" width="39.7272727272727" customWidth="1"/>
-    <col min="4" max="4" width="16.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="15.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="29.7272727272727" customWidth="1"/>
-    <col min="8" max="8" width="39.4545454545455" style="12" customWidth="1"/>
+    <col min="1" max="1" width="81.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="45.90625" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="7" max="7" width="29.7265625" customWidth="1"/>
+    <col min="8" max="8" width="39.453125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -22989,7 +21965,7 @@
         <v>https://www.acfun.cn/v/ac47934854_2</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" ht="15">
       <c r="A44" t="s">
         <v>566</v>
       </c>
@@ -24900,7 +23876,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" ht="15">
       <c r="A137" s="11" t="s">
         <v>191</v>
       </c>
@@ -25364,7 +24340,7 @@
         <v>https://www.acfun.cn/v/ac47934854_3</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" ht="15">
       <c r="A160" s="11" t="s">
         <v>213</v>
       </c>
@@ -26640,7 +25616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" ht="18" customHeight="1" spans="1:8">
+    <row r="223" spans="1:8" ht="18" customHeight="1">
       <c r="A223" t="s">
         <v>207</v>
       </c>
@@ -26740,7 +25716,7 @@
         <v>https://www.acfun.cn/v/ac47930865</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" ht="15">
       <c r="A227" t="s">
         <v>207</v>
       </c>
@@ -27089,7 +26065,7 @@
         <v>https://www.acfun.cn/v/ac47931569_9</v>
       </c>
     </row>
-    <row r="243" ht="18" customHeight="1" spans="1:8">
+    <row r="243" spans="1:8" ht="18" customHeight="1">
       <c r="A243" t="s">
         <v>463</v>
       </c>
@@ -27189,7 +26165,7 @@
         <v>https://www.acfun.cn/v/ac47930865_2</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" ht="15">
       <c r="A247" t="s">
         <v>463</v>
       </c>
@@ -27532,7 +26508,7 @@
         <v>https://www.acfun.cn/v/ac47931569_10</v>
       </c>
     </row>
-    <row r="263" ht="13.5" customHeight="1" spans="1:8">
+    <row r="263" spans="1:8" ht="13.5" customHeight="1">
       <c r="A263" t="s">
         <v>552</v>
       </c>
@@ -27948,28 +26924,28 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H163" r:id="rId1" display="https://www.acfun.cn/v/ac47932379_3"/>
-    <hyperlink ref="H177" r:id="rId2" display="https://www.acfun.cn/v/ac47932379_4"/>
+    <hyperlink ref="H163" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="H177" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="45.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="46.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="17.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="55.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="47.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="14.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="17.9090909090909" customWidth="1"/>
+    <col min="1" max="1" width="45.90625" customWidth="1"/>
+    <col min="2" max="2" width="46.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="55.08984375" customWidth="1"/>
+    <col min="5" max="5" width="47.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -28498,7 +27474,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:7">
+    <row r="24" spans="1:7" ht="16.5" customHeight="1">
       <c r="A24" t="s">
         <v>524</v>
       </c>
@@ -28567,7 +27543,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:7">
+    <row r="27" spans="1:7" ht="16.5" customHeight="1">
       <c r="A27" t="s">
         <v>524</v>
       </c>
@@ -28590,7 +27566,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1" spans="1:7">
+    <row r="28" spans="1:7" ht="28" customHeight="1">
       <c r="A28" t="s">
         <v>524</v>
       </c>
@@ -28613,7 +27589,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1" spans="1:7">
+    <row r="29" spans="1:7" ht="42" customHeight="1">
       <c r="A29" t="s">
         <v>524</v>
       </c>
@@ -28659,7 +27635,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="31" ht="47" customHeight="1" spans="1:7">
+    <row r="31" spans="1:7" ht="47" customHeight="1">
       <c r="A31" t="s">
         <v>524</v>
       </c>
@@ -28817,7 +27793,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="38" ht="33" customHeight="1" spans="1:7">
+    <row r="38" spans="1:7" ht="33" customHeight="1">
       <c r="A38" t="s">
         <v>524</v>
       </c>
@@ -28840,7 +27816,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="39" ht="30.5" customHeight="1" spans="1:7">
+    <row r="39" spans="1:7" ht="30.5" customHeight="1">
       <c r="A39" t="s">
         <v>524</v>
       </c>
@@ -28863,7 +27839,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="40" ht="47" customHeight="1" spans="1:7">
+    <row r="40" spans="1:7" ht="47" customHeight="1">
       <c r="A40" t="s">
         <v>524</v>
       </c>
@@ -28986,7 +27962,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="46" s="9" customFormat="1" spans="1:7">
+    <row r="46" spans="1:7" s="9" customFormat="1">
       <c r="A46" s="9" t="s">
         <v>526</v>
       </c>
@@ -29325,7 +28301,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="61" ht="28" customHeight="1" spans="1:7">
+    <row r="61" spans="1:7" ht="28" customHeight="1">
       <c r="A61" t="s">
         <v>526</v>
       </c>
@@ -29371,7 +28347,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="63" ht="44.5" customHeight="1" spans="1:7">
+    <row r="63" spans="1:7" ht="44.5" customHeight="1">
       <c r="A63" t="s">
         <v>526</v>
       </c>
@@ -29391,7 +28367,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1" spans="1:7">
+    <row r="64" spans="1:7" ht="22.5" customHeight="1">
       <c r="A64" t="s">
         <v>526</v>
       </c>
@@ -29477,7 +28453,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="68" ht="49.5" customHeight="1" spans="1:7">
+    <row r="68" spans="1:7" ht="49.5" customHeight="1">
       <c r="A68" t="s">
         <v>526</v>
       </c>
@@ -29500,7 +28476,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="69" ht="49.5" customHeight="1" spans="1:7">
+    <row r="69" spans="1:7" ht="49.5" customHeight="1">
       <c r="A69" t="s">
         <v>526</v>
       </c>
@@ -29523,7 +28499,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="70" ht="30.5" customHeight="1" spans="1:7">
+    <row r="70" spans="1:7" ht="30.5" customHeight="1">
       <c r="A70" t="s">
         <v>526</v>
       </c>
@@ -29841,42 +28817,42 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" display="https://x.com/bang_dream_info/status/2088182616268910792?s=20"/>
-    <hyperlink ref="E23" r:id="rId2" display="https://x.com/Watase_Yuzuki/status/2088065379088347150?s=20"/>
-    <hyperlink ref="E24" r:id="rId3" display="https://x.com/Watase_Yuzuki/status/2088179201157537898?s=20"/>
-    <hyperlink ref="E25" r:id="rId4" display="https://x.com/Watase_Yuzuki/status/2088786673832538180?s=20"/>
-    <hyperlink ref="E26" r:id="rId5" display="https://x.com/sasakirico/status/2087837294204240082?s=20"/>
-    <hyperlink ref="E27" r:id="rId6" display="https://x.com/sasakirico/status/2088071499219644718?s=20"/>
-    <hyperlink ref="E28" r:id="rId7" display="https://x.com/sasakirico/status/2088175045470458281?s=20"/>
-    <hyperlink ref="E29" r:id="rId8" display="https://x.com/sasakirico/status/2088789235675627903?s=20"/>
-    <hyperlink ref="E39" r:id="rId9" display="https://x.com/Kanon_Takao/status/2088627188316930108?s=20"/>
-    <hyperlink ref="E40" r:id="rId10" display="https://x.com/Kanon_Takao/status/2088823105057853755?s=20"/>
-    <hyperlink ref="E41" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E42" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E43" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E44" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E45" r:id="rId11" display="https://www.instagram.com/p/DcGopDjj59f/?img_index=6&amp;igsi=c20wcmhuZjg3cHhr"/>
-    <hyperlink ref="E47" r:id="rId12" display="https://x.com/BABYMETAL_JAPAN/status/2089290445172125822?s=20"/>
-    <hyperlink ref="E61" r:id="rId13" display="https://x.com/Watase_Yuzuki/status/2088894872896061845?s=20"/>
-    <hyperlink ref="E62" r:id="rId14" display="https://x.com/Watase_Yuzuki/status/2089309227349320029?s=20"/>
-    <hyperlink ref="E63" r:id="rId15" display="https://x.com/sasakirico/status/2088912851788599553?s=20"/>
-    <hyperlink ref="E71" r:id="rId16" display="https://spice.eplus.jp/articles/331632"/>
-    <hyperlink ref="E72" r:id="rId17" display="https://natalie.mu/comic/gallery/news/588794/2400212"/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="E23" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="E24" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="E25" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
+    <hyperlink ref="E26" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="E27" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="E28" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
+    <hyperlink ref="E29" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
+    <hyperlink ref="E39" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
+    <hyperlink ref="E40" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="E41" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
+    <hyperlink ref="E42" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
+    <hyperlink ref="E43" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
+    <hyperlink ref="E44" r:id="rId14" xr:uid="{00000000-0004-0000-0600-00000D000000}"/>
+    <hyperlink ref="E45" r:id="rId15" xr:uid="{00000000-0004-0000-0600-00000E000000}"/>
+    <hyperlink ref="E47" r:id="rId16" xr:uid="{00000000-0004-0000-0600-00000F000000}"/>
+    <hyperlink ref="E61" r:id="rId17" xr:uid="{00000000-0004-0000-0600-000010000000}"/>
+    <hyperlink ref="E62" r:id="rId18" xr:uid="{00000000-0004-0000-0600-000011000000}"/>
+    <hyperlink ref="E63" r:id="rId19" xr:uid="{00000000-0004-0000-0600-000012000000}"/>
+    <hyperlink ref="E71" r:id="rId20" xr:uid="{00000000-0004-0000-0600-000013000000}"/>
+    <hyperlink ref="E72" r:id="rId21" xr:uid="{00000000-0004-0000-0600-000014000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:E115"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="31.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="16.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30479,25 +29455,25 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J268"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.8181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="61.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="7.18181818181818" customWidth="1"/>
-    <col min="7" max="7" width="22.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="12.7272727272727" customWidth="1"/>
-    <col min="9" max="9" width="111.818181818182" customWidth="1"/>
-    <col min="10" max="10" width="21.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" customWidth="1"/>
+    <col min="4" max="4" width="61.26953125" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" customWidth="1"/>
+    <col min="7" max="7" width="22.81640625" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="111.81640625" customWidth="1"/>
+    <col min="10" max="10" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -30532,7 +29508,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:10">
+    <row r="2" spans="1:10" hidden="1">
       <c r="A2" s="2">
         <v>45081</v>
       </c>
@@ -30558,7 +29534,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:10">
+    <row r="3" spans="1:10" hidden="1">
       <c r="A3" s="2" t="s">
         <v>1321</v>
       </c>
@@ -30584,7 +29560,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:10">
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="2" t="s">
         <v>1324</v>
       </c>
@@ -30610,7 +29586,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:10">
+    <row r="5" spans="1:10" hidden="1">
       <c r="A5" s="2" t="s">
         <v>1324</v>
       </c>
@@ -30636,7 +29612,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:10">
+    <row r="6" spans="1:10" hidden="1">
       <c r="A6" s="2" t="s">
         <v>1324</v>
       </c>
@@ -30662,7 +29638,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:10">
+    <row r="7" spans="1:10" hidden="1">
       <c r="A7" s="2" t="s">
         <v>1329</v>
       </c>
@@ -30688,7 +29664,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:10">
+    <row r="8" spans="1:10" hidden="1">
       <c r="A8" s="2" t="s">
         <v>1329</v>
       </c>
@@ -30714,7 +29690,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:10">
+    <row r="9" spans="1:10" hidden="1">
       <c r="A9" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30740,7 +29716,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:10">
+    <row r="10" spans="1:10" hidden="1">
       <c r="A10" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30766,7 +29742,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:10">
+    <row r="11" spans="1:10" hidden="1">
       <c r="A11" s="2" t="s">
         <v>1340</v>
       </c>
@@ -30792,7 +29768,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:10">
+    <row r="12" spans="1:10" hidden="1">
       <c r="A12" s="2" t="s">
         <v>1340</v>
       </c>
@@ -30818,7 +29794,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:10">
+    <row r="13" spans="1:10" hidden="1">
       <c r="A13" s="2" t="s">
         <v>1345</v>
       </c>
@@ -30844,7 +29820,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:10">
+    <row r="14" spans="1:10" hidden="1">
       <c r="A14" s="2" t="s">
         <v>1345</v>
       </c>
@@ -30870,7 +29846,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:10">
+    <row r="15" spans="1:10" hidden="1">
       <c r="A15" s="2" t="s">
         <v>1350</v>
       </c>
@@ -30896,7 +29872,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:10">
+    <row r="16" spans="1:10" hidden="1">
       <c r="A16" s="2" t="s">
         <v>1350</v>
       </c>
@@ -30922,7 +29898,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:10">
+    <row r="17" spans="1:10" hidden="1">
       <c r="A17" s="2" t="s">
         <v>1355</v>
       </c>
@@ -30948,7 +29924,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:10">
+    <row r="18" spans="1:10" hidden="1">
       <c r="A18" s="2" t="s">
         <v>1355</v>
       </c>
@@ -30974,7 +29950,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:10">
+    <row r="19" spans="1:10" hidden="1">
       <c r="A19" s="2" t="s">
         <v>1355</v>
       </c>
@@ -31098,7 +30074,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="24" ht="124" customHeight="1" spans="1:10">
+    <row r="24" spans="1:10" ht="124" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31121,7 +30097,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="25" ht="124" customHeight="1" spans="1:10">
+    <row r="25" spans="1:10" ht="124" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31144,7 +30120,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="26" ht="124" customHeight="1" spans="1:10">
+    <row r="26" spans="1:10" ht="124" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31167,7 +30143,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="27" ht="124" customHeight="1" spans="1:10">
+    <row r="27" spans="1:10" ht="124" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31190,7 +30166,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="28" ht="124" customHeight="1" spans="1:10">
+    <row r="28" spans="1:10" ht="124" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31213,7 +30189,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="29" ht="124" customHeight="1" spans="1:10">
+    <row r="29" spans="1:10" ht="124" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31236,7 +30212,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="30" ht="124" customHeight="1" spans="1:10">
+    <row r="30" spans="1:10" ht="124" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31259,7 +30235,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="31" ht="124" customHeight="1" spans="1:10">
+    <row r="31" spans="1:10" ht="124" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31285,7 +30261,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="32" ht="124" customHeight="1" spans="1:10">
+    <row r="32" spans="1:10" ht="124" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>1375</v>
       </c>
@@ -31311,7 +30287,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="33" ht="197.5" customHeight="1" spans="1:10">
+    <row r="33" spans="1:10" ht="197.5" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31334,7 +30310,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="34" ht="197.5" customHeight="1" spans="1:10">
+    <row r="34" spans="1:10" ht="197.5" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31357,7 +30333,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="35" ht="197.5" customHeight="1" spans="1:10">
+    <row r="35" spans="1:10" ht="197.5" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31380,7 +30356,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="36" ht="197.5" customHeight="1" spans="1:10">
+    <row r="36" spans="1:10" ht="197.5" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31403,7 +30379,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="37" ht="197.5" customHeight="1" spans="1:10">
+    <row r="37" spans="1:10" ht="197.5" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31426,7 +30402,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="38" ht="197.5" customHeight="1" spans="1:10">
+    <row r="38" spans="1:10" ht="197.5" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31449,7 +30425,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="39" ht="197.5" customHeight="1" spans="1:10">
+    <row r="39" spans="1:10" ht="197.5" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31472,7 +30448,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="40" ht="197.5" customHeight="1" spans="1:10">
+    <row r="40" spans="1:10" ht="197.5" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31495,7 +30471,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="41" ht="197.5" customHeight="1" spans="1:10">
+    <row r="41" spans="1:10" ht="197.5" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>1387</v>
       </c>
@@ -31521,7 +30497,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="42" ht="58.5" customHeight="1" spans="1:10">
+    <row r="42" spans="1:10" ht="58.5" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>1399</v>
       </c>
@@ -31544,7 +30520,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="43" ht="58.5" customHeight="1" spans="1:10">
+    <row r="43" spans="1:10" ht="58.5" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>1399</v>
       </c>
@@ -31570,7 +30546,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="44" ht="84" customHeight="1" spans="1:10">
+    <row r="44" spans="1:10" ht="84" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>1404</v>
       </c>
@@ -31593,7 +30569,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="45" ht="84" customHeight="1" spans="1:10">
+    <row r="45" spans="1:10" ht="84" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>1404</v>
       </c>
@@ -31616,7 +30592,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="46" ht="84" customHeight="1" spans="1:10">
+    <row r="46" spans="1:10" ht="84" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>1404</v>
       </c>
@@ -31639,7 +30615,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="47" ht="84" customHeight="1" spans="1:10">
+    <row r="47" spans="1:10" ht="84" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>1404</v>
       </c>
@@ -31662,7 +30638,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="48" ht="84" customHeight="1" spans="1:10">
+    <row r="48" spans="1:10" ht="84" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>1404</v>
       </c>
@@ -31688,7 +30664,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="49" ht="84" customHeight="1" spans="1:10">
+    <row r="49" spans="1:10" ht="84" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>1404</v>
       </c>
@@ -31714,7 +30690,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="50" ht="105.5" customHeight="1" spans="1:10">
+    <row r="50" spans="1:10" ht="105.5" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>1413</v>
       </c>
@@ -31737,7 +30713,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="51" ht="105.5" customHeight="1" spans="1:10">
+    <row r="51" spans="1:10" ht="105.5" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>1413</v>
       </c>
@@ -31760,7 +30736,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="52" ht="105.5" customHeight="1" spans="1:10">
+    <row r="52" spans="1:10" ht="105.5" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>1413</v>
       </c>
@@ -31786,7 +30762,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="53" ht="126" customHeight="1" spans="1:10">
+    <row r="53" spans="1:10" ht="126" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>1419</v>
       </c>
@@ -31809,7 +30785,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="54" ht="126" customHeight="1" spans="1:10">
+    <row r="54" spans="1:10" ht="126" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>1419</v>
       </c>
@@ -31832,7 +30808,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="55" ht="126" customHeight="1" spans="1:10">
+    <row r="55" spans="1:10" ht="126" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>1419</v>
       </c>
@@ -31855,7 +30831,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="56" ht="126" customHeight="1" spans="1:10">
+    <row r="56" spans="1:10" ht="126" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>1419</v>
       </c>
@@ -31878,7 +30854,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="57" ht="126" customHeight="1" spans="1:10">
+    <row r="57" spans="1:10" ht="126" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>1419</v>
       </c>
@@ -31904,7 +30880,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="58" ht="47" customHeight="1" spans="1:10">
+    <row r="58" spans="1:10" ht="47" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>1427</v>
       </c>
@@ -31927,7 +30903,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="59" ht="47" customHeight="1" spans="1:10">
+    <row r="59" spans="1:10" ht="47" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>1427</v>
       </c>
@@ -31950,7 +30926,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="60" ht="47" customHeight="1" spans="1:10">
+    <row r="60" spans="1:10" ht="47" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>1427</v>
       </c>
@@ -32097,7 +31073,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="66" ht="84" customHeight="1" spans="1:10">
+    <row r="66" spans="1:10" ht="84" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>1441</v>
       </c>
@@ -32120,7 +31096,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="67" ht="84" customHeight="1" spans="1:10">
+    <row r="67" spans="1:10" ht="84" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>1441</v>
       </c>
@@ -32143,7 +31119,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="68" ht="84" customHeight="1" spans="1:10">
+    <row r="68" spans="1:10" ht="84" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>1441</v>
       </c>
@@ -32166,7 +31142,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="69" ht="84" customHeight="1" spans="1:10">
+    <row r="69" spans="1:10" ht="84" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>1441</v>
       </c>
@@ -32189,7 +31165,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="70" ht="84" customHeight="1" spans="1:10">
+    <row r="70" spans="1:10" ht="84" customHeight="1">
       <c r="A70" s="2" t="s">
         <v>1441</v>
       </c>
@@ -32215,7 +31191,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="71" ht="154" customHeight="1" spans="1:10">
+    <row r="71" spans="1:10" ht="154" customHeight="1">
       <c r="A71" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32238,7 +31214,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="72" ht="154" customHeight="1" spans="1:10">
+    <row r="72" spans="1:10" ht="154" customHeight="1">
       <c r="A72" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32261,7 +31237,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="73" ht="154" customHeight="1" spans="1:10">
+    <row r="73" spans="1:10" ht="154" customHeight="1">
       <c r="A73" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32284,7 +31260,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="74" ht="154" customHeight="1" spans="1:10">
+    <row r="74" spans="1:10" ht="154" customHeight="1">
       <c r="A74" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32307,7 +31283,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="75" ht="154" customHeight="1" spans="1:10">
+    <row r="75" spans="1:10" ht="154" customHeight="1">
       <c r="A75" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32330,7 +31306,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="76" ht="154" customHeight="1" spans="1:10">
+    <row r="76" spans="1:10" ht="154" customHeight="1">
       <c r="A76" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32353,7 +31329,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="77" ht="154" customHeight="1" spans="1:10">
+    <row r="77" spans="1:10" ht="154" customHeight="1">
       <c r="A77" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32379,7 +31355,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="78" ht="154" customHeight="1" spans="1:10">
+    <row r="78" spans="1:10" ht="154" customHeight="1">
       <c r="A78" s="2" t="s">
         <v>1449</v>
       </c>
@@ -32405,7 +31381,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="79" ht="140" customHeight="1" spans="1:10">
+    <row r="79" spans="1:10" ht="140" customHeight="1">
       <c r="A79" t="s">
         <v>1449</v>
       </c>
@@ -32429,7 +31405,7 @@
       </c>
       <c r="I79" s="3"/>
     </row>
-    <row r="80" ht="140" customHeight="1" spans="1:10">
+    <row r="80" spans="1:10" ht="140" customHeight="1">
       <c r="A80" t="s">
         <v>1449</v>
       </c>
@@ -32560,7 +31536,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="85" ht="98" customHeight="1" spans="1:10">
+    <row r="85" spans="1:10" ht="98" customHeight="1">
       <c r="A85" s="1">
         <v>45301</v>
       </c>
@@ -32583,7 +31559,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="86" ht="98" customHeight="1" spans="1:10">
+    <row r="86" spans="1:10" ht="98" customHeight="1">
       <c r="A86" s="1">
         <v>45301</v>
       </c>
@@ -32606,7 +31582,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="87" ht="98" customHeight="1" spans="1:10">
+    <row r="87" spans="1:10" ht="98" customHeight="1">
       <c r="A87" s="1">
         <v>45301</v>
       </c>
@@ -32632,7 +31608,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="88" ht="98" customHeight="1" spans="1:10">
+    <row r="88" spans="1:10" ht="98" customHeight="1">
       <c r="A88" s="1">
         <v>45301</v>
       </c>
@@ -32658,7 +31634,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:10">
+    <row r="89" spans="1:10" hidden="1">
       <c r="A89" s="2">
         <v>45290</v>
       </c>
@@ -32684,7 +31660,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:10">
+    <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="2">
         <v>45290</v>
       </c>
@@ -32707,7 +31683,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:10">
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="2">
         <v>45298</v>
       </c>
@@ -32733,7 +31709,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:10">
+    <row r="92" spans="1:10" hidden="1">
       <c r="A92" s="2">
         <v>45298</v>
       </c>
@@ -32756,7 +31732,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:10">
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" s="2">
         <v>45406</v>
       </c>
@@ -32782,7 +31758,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:10">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" s="2">
         <v>45406</v>
       </c>
@@ -32808,7 +31784,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:10">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" s="2">
         <v>45406</v>
       </c>
@@ -32831,7 +31807,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:10">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="2">
         <v>45451</v>
       </c>
@@ -32857,7 +31833,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:10">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97" s="2">
         <v>45451</v>
       </c>
@@ -32883,7 +31859,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:10">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98" s="2">
         <v>45451</v>
       </c>
@@ -32906,7 +31882,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:10">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99" s="2">
         <v>45480</v>
       </c>
@@ -32932,7 +31908,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:10">
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100" s="2">
         <v>45578</v>
       </c>
@@ -32958,7 +31934,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:10">
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101" s="2">
         <v>45578</v>
       </c>
@@ -32984,7 +31960,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:10">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="2">
         <v>45578</v>
       </c>
@@ -33007,7 +31983,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:10">
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103" s="2">
         <v>45360</v>
       </c>
@@ -33030,7 +32006,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:10">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104" s="2">
         <v>45486</v>
       </c>
@@ -33056,7 +32032,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:10">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105" s="2">
         <v>45486</v>
       </c>
@@ -33079,7 +32055,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:10">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106" s="2">
         <v>45487</v>
       </c>
@@ -33096,7 +32072,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:10">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107" s="2">
         <v>45534</v>
       </c>
@@ -33122,7 +32098,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:10">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108" s="2">
         <v>45534</v>
       </c>
@@ -33145,7 +32121,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:10">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109" s="2">
         <v>45186</v>
       </c>
@@ -33171,7 +32147,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:10">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110" s="2">
         <v>45186</v>
       </c>
@@ -33194,7 +32170,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:10">
+    <row r="111" spans="1:10" hidden="1">
       <c r="A111" s="2">
         <v>45389</v>
       </c>
@@ -33220,7 +32196,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:10">
+    <row r="112" spans="1:10" hidden="1">
       <c r="A112" s="2">
         <v>45389</v>
       </c>
@@ -33243,7 +32219,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:10">
+    <row r="113" spans="1:10" hidden="1">
       <c r="A113" s="2">
         <v>45430</v>
       </c>
@@ -33269,7 +32245,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:10">
+    <row r="114" spans="1:10" hidden="1">
       <c r="A114" s="2">
         <v>45430</v>
       </c>
@@ -33292,7 +32268,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:10">
+    <row r="115" spans="1:10" hidden="1">
       <c r="A115" s="2">
         <v>45458</v>
       </c>
@@ -33318,7 +32294,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:10">
+    <row r="116" spans="1:10" hidden="1">
       <c r="A116" s="2">
         <v>45458</v>
       </c>
@@ -33341,7 +32317,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:10">
+    <row r="117" spans="1:10" hidden="1">
       <c r="A117" s="2">
         <v>45481</v>
       </c>
@@ -33367,7 +32343,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:10">
+    <row r="118" spans="1:10" hidden="1">
       <c r="A118" s="2">
         <v>45481</v>
       </c>
@@ -33390,7 +32366,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:10">
+    <row r="119" spans="1:10" hidden="1">
       <c r="A119" s="2">
         <v>45534</v>
       </c>
@@ -33416,7 +32392,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:10">
+    <row r="120" spans="1:10" hidden="1">
       <c r="A120" s="2">
         <v>45534</v>
       </c>
@@ -33439,7 +32415,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:10">
+    <row r="121" spans="1:10" hidden="1">
       <c r="A121" s="2">
         <v>45567</v>
       </c>
@@ -33465,7 +32441,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:10">
+    <row r="122" spans="1:10" hidden="1">
       <c r="A122" s="2">
         <v>45567</v>
       </c>
@@ -33491,7 +32467,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:10">
+    <row r="123" spans="1:10" hidden="1">
       <c r="A123" s="2">
         <v>45567</v>
       </c>
@@ -33517,7 +32493,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:10">
+    <row r="124" spans="1:10" hidden="1">
       <c r="A124" s="2">
         <v>45567</v>
       </c>
@@ -33543,7 +32519,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:10">
+    <row r="125" spans="1:10" hidden="1">
       <c r="A125" s="2">
         <v>45567</v>
       </c>
@@ -33566,7 +32542,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:10">
+    <row r="126" spans="1:10" hidden="1">
       <c r="A126" s="2">
         <v>45483</v>
       </c>
@@ -33592,7 +32568,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:10">
+    <row r="127" spans="1:10" hidden="1">
       <c r="A127" s="2">
         <v>45483</v>
       </c>
@@ -33618,7 +32594,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:10">
+    <row r="128" spans="1:10" hidden="1">
       <c r="A128" s="2">
         <v>45483</v>
       </c>
@@ -33641,7 +32617,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:10">
+    <row r="129" spans="1:10" hidden="1">
       <c r="A129" s="2">
         <v>45640</v>
       </c>
@@ -33667,7 +32643,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:10">
+    <row r="130" spans="1:10" hidden="1">
       <c r="A130" s="2">
         <v>45640</v>
       </c>
@@ -33690,7 +32666,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:10">
+    <row r="131" spans="1:10" hidden="1">
       <c r="A131" s="2">
         <v>45641</v>
       </c>
@@ -33716,7 +32692,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:10">
+    <row r="132" spans="1:10" hidden="1">
       <c r="A132" s="2">
         <v>45641</v>
       </c>
@@ -33742,7 +32718,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:10">
+    <row r="133" spans="1:10" hidden="1">
       <c r="A133" s="2">
         <v>45641</v>
       </c>
@@ -33765,7 +32741,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:10">
+    <row r="134" spans="1:10" hidden="1">
       <c r="A134" s="2">
         <v>45619</v>
       </c>
@@ -33788,7 +32764,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:10">
+    <row r="135" spans="1:10" hidden="1">
       <c r="A135" s="2">
         <v>45619</v>
       </c>
@@ -33808,7 +32784,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:10">
+    <row r="136" spans="1:10" hidden="1">
       <c r="A136" s="2">
         <v>45627</v>
       </c>
@@ -33834,7 +32810,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="137" ht="196" customHeight="1" spans="1:10">
+    <row r="137" spans="1:10" ht="196" customHeight="1">
       <c r="A137" s="1">
         <v>45323</v>
       </c>
@@ -33857,7 +32833,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="138" ht="196" customHeight="1" spans="1:10">
+    <row r="138" spans="1:10" ht="196" customHeight="1">
       <c r="A138" s="1">
         <v>45323</v>
       </c>
@@ -33880,7 +32856,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="139" ht="196" customHeight="1" spans="1:10">
+    <row r="139" spans="1:10" ht="196" customHeight="1">
       <c r="A139" s="1">
         <v>45323</v>
       </c>
@@ -33903,7 +32879,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="140" ht="196" customHeight="1" spans="1:10">
+    <row r="140" spans="1:10" ht="196" customHeight="1">
       <c r="A140" s="1">
         <v>45323</v>
       </c>
@@ -33926,7 +32902,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="141" ht="196" customHeight="1" spans="1:10">
+    <row r="141" spans="1:10" ht="196" customHeight="1">
       <c r="A141" s="1">
         <v>45323</v>
       </c>
@@ -33949,7 +32925,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="142" ht="196" customHeight="1" spans="1:10">
+    <row r="142" spans="1:10" ht="196" customHeight="1">
       <c r="A142" s="1">
         <v>45323</v>
       </c>
@@ -33972,7 +32948,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="143" ht="196" customHeight="1" spans="1:10">
+    <row r="143" spans="1:10" ht="196" customHeight="1">
       <c r="A143" s="1">
         <v>45323</v>
       </c>
@@ -33995,7 +32971,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="144" ht="196" customHeight="1" spans="1:10">
+    <row r="144" spans="1:10" ht="196" customHeight="1">
       <c r="A144" s="1">
         <v>45323</v>
       </c>
@@ -34019,7 +32995,7 @@
       </c>
       <c r="I144" s="4"/>
     </row>
-    <row r="145" ht="196" customHeight="1" spans="1:10">
+    <row r="145" spans="1:10" ht="196" customHeight="1">
       <c r="A145" s="1">
         <v>45323</v>
       </c>
@@ -34046,7 +33022,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="146" ht="196" customHeight="1" spans="1:10">
+    <row r="146" spans="1:10" ht="196" customHeight="1">
       <c r="A146" s="1">
         <v>45323</v>
       </c>
@@ -34072,7 +33048,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="147" ht="84" customHeight="1" spans="1:10">
+    <row r="147" spans="1:10" ht="84" customHeight="1">
       <c r="A147" s="1">
         <v>45336</v>
       </c>
@@ -34098,7 +33074,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="148" ht="84" customHeight="1" spans="1:10">
+    <row r="148" spans="1:10" ht="84" customHeight="1">
       <c r="A148" s="1">
         <v>45336</v>
       </c>
@@ -34125,7 +33101,7 @@
       </c>
       <c r="I148" s="3"/>
     </row>
-    <row r="149" ht="84" customHeight="1" spans="1:10">
+    <row r="149" spans="1:10" ht="84" customHeight="1">
       <c r="A149" s="1">
         <v>45336</v>
       </c>
@@ -34151,7 +33127,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="150" ht="84" customHeight="1" spans="1:10">
+    <row r="150" spans="1:10" ht="84" customHeight="1">
       <c r="A150" s="1">
         <v>45336</v>
       </c>
@@ -34174,7 +33150,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="151" ht="84" customHeight="1" spans="1:10">
+    <row r="151" spans="1:10" ht="84" customHeight="1">
       <c r="A151" s="1">
         <v>45336</v>
       </c>
@@ -34200,7 +33176,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="152" ht="84" customHeight="1" spans="1:10">
+    <row r="152" spans="1:10" ht="84" customHeight="1">
       <c r="A152" s="1">
         <v>45336</v>
       </c>
@@ -34727,7 +33703,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="174" ht="84" customHeight="1" spans="1:10">
+    <row r="174" spans="1:10" ht="84" customHeight="1">
       <c r="A174" s="1">
         <v>45343</v>
       </c>
@@ -34750,7 +33726,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="175" ht="84" customHeight="1" spans="1:10">
+    <row r="175" spans="1:10" ht="84" customHeight="1">
       <c r="A175" s="1">
         <v>45343</v>
       </c>
@@ -34776,7 +33752,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="176" ht="84" customHeight="1" spans="1:10">
+    <row r="176" spans="1:10" ht="84" customHeight="1">
       <c r="A176" s="1">
         <v>45343</v>
       </c>
@@ -35205,7 +34181,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="194" ht="70" customHeight="1" spans="1:10">
+    <row r="194" spans="1:10" ht="70" customHeight="1">
       <c r="A194" s="1">
         <v>45360</v>
       </c>
@@ -35229,7 +34205,7 @@
       </c>
       <c r="I194" s="4"/>
     </row>
-    <row r="195" ht="70" customHeight="1" spans="1:10">
+    <row r="195" spans="1:10" ht="70" customHeight="1">
       <c r="A195" s="1">
         <v>45360</v>
       </c>
@@ -35359,7 +34335,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="200" ht="15.5" customHeight="1" spans="1:10">
+    <row r="200" spans="1:10" ht="15.5" customHeight="1">
       <c r="A200" s="1">
         <v>45374</v>
       </c>
@@ -35757,7 +34733,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="217" ht="126" customHeight="1" spans="1:10">
+    <row r="217" spans="1:10" ht="126" customHeight="1">
       <c r="A217" s="1">
         <v>45457</v>
       </c>
@@ -35781,7 +34757,7 @@
       </c>
       <c r="I217" s="3"/>
     </row>
-    <row r="218" ht="126" customHeight="1" spans="1:10">
+    <row r="218" spans="1:10" ht="126" customHeight="1">
       <c r="A218" s="1">
         <v>45457</v>
       </c>
@@ -35807,7 +34783,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="219" ht="126" customHeight="1" spans="1:10">
+    <row r="219" spans="1:10" ht="126" customHeight="1">
       <c r="A219" s="1">
         <v>45457</v>
       </c>
@@ -35833,7 +34809,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="220" ht="70" customHeight="1" spans="1:10">
+    <row r="220" spans="1:10" ht="70" customHeight="1">
       <c r="A220" s="1">
         <v>45469</v>
       </c>
@@ -35857,7 +34833,7 @@
       </c>
       <c r="I220" s="3"/>
     </row>
-    <row r="221" ht="70" customHeight="1" spans="1:10">
+    <row r="221" spans="1:10" ht="70" customHeight="1">
       <c r="A221" s="1">
         <v>45469</v>
       </c>
@@ -35881,7 +34857,7 @@
       </c>
       <c r="I221" s="3"/>
     </row>
-    <row r="222" ht="70" customHeight="1" spans="1:10">
+    <row r="222" spans="1:10" ht="70" customHeight="1">
       <c r="A222" s="1">
         <v>45469</v>
       </c>
@@ -35907,7 +34883,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="223" ht="42" customHeight="1" spans="1:10">
+    <row r="223" spans="1:10" ht="42" customHeight="1">
       <c r="A223" s="1">
         <v>45481</v>
       </c>
@@ -35930,7 +34906,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="224" ht="42" customHeight="1" spans="1:10">
+    <row r="224" spans="1:10" ht="42" customHeight="1">
       <c r="A224" s="1">
         <v>45481</v>
       </c>
@@ -35953,7 +34929,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="225" ht="42" customHeight="1" spans="1:10">
+    <row r="225" spans="1:10" ht="42" customHeight="1">
       <c r="A225" s="1">
         <v>45481</v>
       </c>
@@ -35979,7 +34955,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="226" ht="42" customHeight="1" spans="1:10">
+    <row r="226" spans="1:10" ht="42" customHeight="1">
       <c r="A226" s="1">
         <v>45481</v>
       </c>
@@ -36005,7 +34981,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="227" ht="28" customHeight="1" spans="1:10">
+    <row r="227" spans="1:10" ht="28" customHeight="1">
       <c r="A227" s="1">
         <v>45517</v>
       </c>
@@ -36031,7 +35007,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="228" ht="28" customHeight="1" spans="1:10">
+    <row r="228" spans="1:10" ht="28" customHeight="1">
       <c r="A228" s="1">
         <v>45517</v>
       </c>
@@ -36054,7 +35030,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="229" ht="98" customHeight="1" spans="1:10">
+    <row r="229" spans="1:10" ht="98" customHeight="1">
       <c r="A229" s="1">
         <v>45545</v>
       </c>
@@ -36077,7 +35053,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="230" ht="98" customHeight="1" spans="1:10">
+    <row r="230" spans="1:10" ht="98" customHeight="1">
       <c r="A230" s="1">
         <v>45545</v>
       </c>
@@ -36100,7 +35076,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="231" ht="98" customHeight="1" spans="1:10">
+    <row r="231" spans="1:10" ht="98" customHeight="1">
       <c r="A231" s="1">
         <v>45545</v>
       </c>
@@ -36323,7 +35299,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="240" ht="28" customHeight="1" spans="1:10">
+    <row r="240" spans="1:10" ht="28" customHeight="1">
       <c r="A240" s="1">
         <v>45569</v>
       </c>
@@ -36347,7 +35323,7 @@
       </c>
       <c r="I240" s="3"/>
     </row>
-    <row r="241" ht="28" customHeight="1" spans="1:10">
+    <row r="241" spans="1:10" ht="28" customHeight="1">
       <c r="A241" s="1">
         <v>45569</v>
       </c>
@@ -36373,7 +35349,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="242" ht="30.5" customHeight="1" spans="1:10">
+    <row r="242" spans="1:10" ht="30.5" customHeight="1">
       <c r="A242" s="1">
         <v>45593</v>
       </c>
@@ -36399,7 +35375,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="243" ht="30.5" customHeight="1" spans="1:10">
+    <row r="243" spans="1:10" ht="30.5" customHeight="1">
       <c r="A243" s="1">
         <v>45593</v>
       </c>
@@ -36422,7 +35398,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="244" ht="30.5" customHeight="1" spans="1:10">
+    <row r="244" spans="1:10" ht="30.5" customHeight="1">
       <c r="A244" s="1">
         <v>45593</v>
       </c>
@@ -36445,7 +35421,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="245" ht="109.5" customHeight="1" spans="1:10">
+    <row r="245" spans="1:10" ht="109.5" customHeight="1">
       <c r="A245" s="1">
         <v>45598</v>
       </c>
@@ -36468,7 +35444,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="246" ht="109.5" customHeight="1" spans="1:10">
+    <row r="246" spans="1:10" ht="109.5" customHeight="1">
       <c r="A246" s="1">
         <v>45598</v>
       </c>
@@ -36491,7 +35467,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="247" ht="109.5" customHeight="1" spans="1:10">
+    <row r="247" spans="1:10" ht="109.5" customHeight="1">
       <c r="A247" s="1">
         <v>45598</v>
       </c>
@@ -36514,7 +35490,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="248" ht="109.5" customHeight="1" spans="1:10">
+    <row r="248" spans="1:10" ht="109.5" customHeight="1">
       <c r="A248" s="1">
         <v>45598</v>
       </c>
@@ -36540,7 +35516,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="249" ht="109.5" customHeight="1" spans="1:10">
+    <row r="249" spans="1:10" ht="109.5" customHeight="1">
       <c r="A249" s="1">
         <v>45598</v>
       </c>
@@ -36566,7 +35542,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="250" ht="136" customHeight="1" spans="1:10">
+    <row r="250" spans="1:10" ht="136" customHeight="1">
       <c r="A250" s="1">
         <v>45606</v>
       </c>
@@ -36589,7 +35565,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="251" ht="136" customHeight="1" spans="1:10">
+    <row r="251" spans="1:10" ht="136" customHeight="1">
       <c r="A251" s="1">
         <v>45606</v>
       </c>
@@ -36612,7 +35588,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="252" ht="136" customHeight="1" spans="1:10">
+    <row r="252" spans="1:10" ht="136" customHeight="1">
       <c r="A252" s="1">
         <v>45606</v>
       </c>
@@ -36638,7 +35614,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="253" ht="16.5" customHeight="1" spans="1:10">
+    <row r="253" spans="1:10" ht="16.5" customHeight="1">
       <c r="A253" s="1">
         <v>45650</v>
       </c>
@@ -36661,7 +35637,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="254" ht="16.5" customHeight="1" spans="1:10">
+    <row r="254" spans="1:10" ht="16.5" customHeight="1">
       <c r="A254" s="1">
         <v>45650</v>
       </c>
@@ -36828,7 +35804,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="261" ht="77.5" customHeight="1" spans="1:10">
+    <row r="261" spans="1:10" ht="77.5" customHeight="1">
       <c r="A261" s="1">
         <v>45655</v>
       </c>
@@ -36852,7 +35828,7 @@
       </c>
       <c r="I261" s="3"/>
     </row>
-    <row r="262" ht="77.5" customHeight="1" spans="1:10">
+    <row r="262" spans="1:10" ht="77.5" customHeight="1">
       <c r="A262" s="1">
         <v>45655</v>
       </c>
@@ -36875,7 +35851,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="263" ht="77.5" customHeight="1" spans="1:10">
+    <row r="263" spans="1:10" ht="77.5" customHeight="1">
       <c r="A263" s="1">
         <v>45655</v>
       </c>
@@ -36898,7 +35874,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="264" ht="77.5" customHeight="1" spans="1:10">
+    <row r="264" spans="1:10" ht="77.5" customHeight="1">
       <c r="A264" s="1">
         <v>45655</v>
       </c>
@@ -36921,7 +35897,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="265" ht="77.5" customHeight="1" spans="1:10">
+    <row r="265" spans="1:10" ht="77.5" customHeight="1">
       <c r="A265" s="1">
         <v>45655</v>
       </c>
@@ -36970,7 +35946,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="267" ht="77.5" customHeight="1" spans="1:10">
+    <row r="267" spans="1:10" ht="77.5" customHeight="1">
       <c r="A267" s="1">
         <v>45655</v>
       </c>
@@ -36996,7 +35972,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="268" ht="197.5" customHeight="1" spans="1:10">
+    <row r="268" spans="1:10" ht="197.5" customHeight="1">
       <c r="A268" s="2" t="s">
         <v>1387</v>
       </c>
@@ -37023,20 +35999,19 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J268" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:J268" xr:uid="{00000000-0009-0000-0000-000008000000}">
     <filterColumn colId="2">
-      <customFilters>
-        <customFilter operator="equal" val="personal"/>
-      </customFilters>
+      <filters>
+        <filter val="personal"/>
+      </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I22" r:id="rId1" display="https://x.com/Kanon_Takao/status/1695354653582746087&#10;"/>
-    <hyperlink ref="I32" r:id="rId2" display="https://x.com/Kanon_Takao/status/1706878641228190181"/>
-    <hyperlink ref="I41" r:id="rId3" display="https://x.com/Kanon_Takao/status/1719212653686788414"/>
+    <hyperlink ref="I22" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="I32" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
+    <hyperlink ref="I41" r:id="rId3" xr:uid="{00000000-0004-0000-0800-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>